--- a/Documents/コメント削除機能設計書.xlsx
+++ b/Documents/コメント削除機能設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000E8C46-7A70-468D-A9D5-7EA3856F9AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F715AA-D96B-4E9F-A592-CB8BD991F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="7" xr2:uid="{73C913ED-0334-40C4-8D2F-5AD7FF49F493}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{73C913ED-0334-40C4-8D2F-5AD7FF49F493}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="128">
   <si>
     <t>ユースケース記述</t>
   </si>
@@ -530,21 +530,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>①タスク詳細画面で、消したいコメントの削除ボタンを押下する
-②削除確認画面にて、削除ボタンを押下する
-③エラー画面が表示され、メニュー画面に戻るボタンが表示される</t>
-    <rPh sb="67" eb="69">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="70" eb="71">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>コメント削除完了</t>
     <rPh sb="4" eb="6">
       <t>サクジョ</t>
@@ -811,6 +796,75 @@
   </si>
   <si>
     <t>deleteComment(CommentBean bean)</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>CommentDAO</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>①タスク詳細画面で、消したいコメントの削除ボタンを押下する
+②削除確認画面にて、削除ボタンを押下する
+③削除完了画面でブラウザバックし、もう一度削除ボタンを押下する
+④削除失敗画面が表示される</t>
+    <rPh sb="84" eb="86">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>コメント削除画面からタスク詳細画面に戻る</t>
+    <rPh sb="4" eb="6">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>No.2のテストが成功している</t>
+    <rPh sb="9" eb="11">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>いいえボタンを押下する</t>
+    <rPh sb="7" eb="9">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>タスク詳細画面が表示される</t>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -1910,7 +1964,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="298">
+  <cellXfs count="303">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2802,6 +2856,21 @@
     </xf>
     <xf numFmtId="56" fontId="3" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -3581,7 +3650,7 @@
       </c>
       <c r="C11" s="92"/>
       <c r="D11" s="88" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="E11" s="89"/>
       <c r="F11" s="89"/>
@@ -7530,7 +7599,7 @@
       <c r="B5" s="168"/>
       <c r="C5" s="169"/>
       <c r="D5" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5" s="168"/>
       <c r="F5" s="168"/>
@@ -7658,7 +7727,7 @@
       <c r="B15" s="152"/>
       <c r="C15" s="153"/>
       <c r="D15" s="154" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E15" s="152"/>
       <c r="F15" s="152"/>
@@ -7700,7 +7769,7 @@
       <c r="B17" s="152"/>
       <c r="C17" s="153"/>
       <c r="D17" s="54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="54" t="s">
         <v>86</v>
@@ -7709,7 +7778,7 @@
         <v>87</v>
       </c>
       <c r="G17" s="55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H17" s="154"/>
       <c r="I17" s="152"/>
@@ -8894,7 +8963,7 @@
       <c r="B5" s="168"/>
       <c r="C5" s="169"/>
       <c r="D5" s="170" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E5" s="168"/>
       <c r="F5" s="168"/>
@@ -9022,7 +9091,7 @@
       <c r="B15" s="152"/>
       <c r="C15" s="153"/>
       <c r="D15" s="154" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E15" s="152"/>
       <c r="F15" s="152"/>
@@ -9066,7 +9135,7 @@
       <c r="B17" s="152"/>
       <c r="C17" s="153"/>
       <c r="D17" s="54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="54" t="s">
         <v>86</v>
@@ -9075,7 +9144,7 @@
         <v>87</v>
       </c>
       <c r="G17" s="55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H17" s="154"/>
       <c r="I17" s="152"/>
@@ -11766,7 +11835,7 @@
       <c r="E7" s="216"/>
       <c r="F7" s="217"/>
       <c r="G7" s="235" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H7" s="216"/>
       <c r="I7" s="216"/>
@@ -12034,21 +12103,21 @@
       </c>
       <c r="F16" s="288"/>
       <c r="G16" s="290" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H16" s="291"/>
       <c r="I16" s="288"/>
       <c r="J16" s="292" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K16" s="92"/>
       <c r="L16" s="293" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M16" s="291"/>
       <c r="N16" s="288"/>
       <c r="O16" s="293" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P16" s="291"/>
       <c r="Q16" s="288"/>
@@ -12076,21 +12145,21 @@
       </c>
       <c r="F17" s="288"/>
       <c r="G17" s="290" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H17" s="291"/>
       <c r="I17" s="288"/>
       <c r="J17" s="290" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K17" s="288"/>
       <c r="L17" s="293" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M17" s="291"/>
       <c r="N17" s="288"/>
       <c r="O17" s="293" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P17" s="291"/>
       <c r="Q17" s="288"/>
@@ -12114,25 +12183,25 @@
       </c>
       <c r="D18" s="288"/>
       <c r="E18" s="289" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="F18" s="288"/>
       <c r="G18" s="290" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H18" s="291"/>
       <c r="I18" s="288"/>
       <c r="J18" s="290" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="K18" s="288"/>
-      <c r="L18" s="296" t="s">
-        <v>115</v>
+      <c r="L18" s="293" t="s">
+        <v>126</v>
       </c>
       <c r="M18" s="291"/>
       <c r="N18" s="288"/>
       <c r="O18" s="293" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="P18" s="291"/>
       <c r="Q18" s="288"/>
@@ -12156,25 +12225,25 @@
       </c>
       <c r="D19" s="288"/>
       <c r="E19" s="289" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F19" s="288"/>
       <c r="G19" s="290" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H19" s="291"/>
       <c r="I19" s="288"/>
       <c r="J19" s="290" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K19" s="288"/>
-      <c r="L19" s="293" t="s">
-        <v>113</v>
+      <c r="L19" s="296" t="s">
+        <v>114</v>
       </c>
       <c r="M19" s="291"/>
       <c r="N19" s="288"/>
       <c r="O19" s="293" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="P19" s="291"/>
       <c r="Q19" s="288"/>
@@ -12188,27 +12257,41 @@
       <c r="Y19" s="44"/>
       <c r="Z19" s="44"/>
     </row>
-    <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="218"/>
-      <c r="B20" s="217"/>
-      <c r="C20" s="219"/>
-      <c r="D20" s="217"/>
-      <c r="E20" s="219"/>
-      <c r="F20" s="217"/>
-      <c r="G20" s="220"/>
-      <c r="H20" s="216"/>
-      <c r="I20" s="217"/>
-      <c r="J20" s="220"/>
-      <c r="K20" s="217"/>
-      <c r="L20" s="215"/>
-      <c r="M20" s="216"/>
-      <c r="N20" s="217"/>
-      <c r="O20" s="215"/>
-      <c r="P20" s="216"/>
-      <c r="Q20" s="217"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="43"/>
+    <row r="20" spans="1:26" ht="65.25" customHeight="1">
+      <c r="A20" s="287">
+        <v>5</v>
+      </c>
+      <c r="B20" s="288"/>
+      <c r="C20" s="289" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="302"/>
+      <c r="E20" s="289" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="302"/>
+      <c r="G20" s="290" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="301"/>
+      <c r="I20" s="300"/>
+      <c r="J20" s="290" t="s">
+        <v>101</v>
+      </c>
+      <c r="K20" s="300"/>
+      <c r="L20" s="293" t="s">
+        <v>112</v>
+      </c>
+      <c r="M20" s="298"/>
+      <c r="N20" s="299"/>
+      <c r="O20" s="293" t="s">
+        <v>116</v>
+      </c>
+      <c r="P20" s="298"/>
+      <c r="Q20" s="299"/>
+      <c r="R20" s="294"/>
+      <c r="S20" s="294"/>
+      <c r="T20" s="295"/>
       <c r="U20" s="44"/>
       <c r="V20" s="44"/>
       <c r="W20" s="44"/>
@@ -13650,7 +13733,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="L18" r:id="rId1" xr:uid="{901F01D7-F314-4A0A-8CB9-859FDAB1C03C}"/>
+    <hyperlink ref="L19" r:id="rId1" xr:uid="{2AD90381-95C9-4BA1-856D-97E57606DF78}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -13715,7 +13798,7 @@
       <c r="D2" s="268"/>
       <c r="E2" s="269"/>
       <c r="F2" s="270" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G2" s="271"/>
       <c r="H2" s="271"/>
@@ -13798,17 +13881,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" s="260" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" s="260"/>
       <c r="E5" s="260"/>
       <c r="F5" s="260"/>
       <c r="G5" s="260"/>
       <c r="H5" s="260" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I5" s="260"/>
       <c r="J5" s="260"/>
@@ -13816,7 +13899,7 @@
       <c r="L5" s="260"/>
       <c r="M5" s="260"/>
       <c r="N5" s="261" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O5" s="262"/>
       <c r="P5" s="263"/>
@@ -13829,17 +13912,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="260" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="260"/>
       <c r="E6" s="260"/>
       <c r="F6" s="260"/>
       <c r="G6" s="260"/>
       <c r="H6" s="260" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I6" s="260"/>
       <c r="J6" s="260"/>
@@ -13847,7 +13930,7 @@
       <c r="L6" s="260"/>
       <c r="M6" s="260"/>
       <c r="N6" s="261" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O6" s="262"/>
       <c r="P6" s="263"/>
@@ -15159,7 +15242,9 @@
       <c r="D5" s="278"/>
       <c r="E5" s="278"/>
       <c r="F5" s="279"/>
-      <c r="G5" s="283"/>
+      <c r="G5" s="283" t="s">
+        <v>122</v>
+      </c>
       <c r="H5" s="284"/>
       <c r="I5" s="284"/>
       <c r="J5" s="284"/>

--- a/Documents/コメント削除機能設計書.xlsx
+++ b/Documents/コメント削除機能設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F715AA-D96B-4E9F-A592-CB8BD991F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68874495-4769-41D7-8138-9CEAFCAC202A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{73C913ED-0334-40C4-8D2F-5AD7FF49F493}"/>
+    <workbookView minimized="1" xWindow="285" yWindow="585" windowWidth="11415" windowHeight="8955" firstSheet="5" activeTab="6" xr2:uid="{73C913ED-0334-40C4-8D2F-5AD7FF49F493}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="テスト仕様書兼結果報告書" sheetId="5" r:id="rId7"/>
     <sheet name="JUnitテスト仕様書兼報告書" sheetId="7" r:id="rId8"/>
     <sheet name="カバレッジレポート" sheetId="8" r:id="rId9"/>
+    <sheet name="エビデンス" sheetId="19" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="範囲１" localSheetId="7">#REF!</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="138">
   <si>
     <t>ユースケース記述</t>
   </si>
@@ -113,10 +114,6 @@
   </si>
   <si>
     <t>詳細クラス図</t>
-  </si>
-  <si>
-    <t>テスト仕様書兼
-結果報告書</t>
   </si>
   <si>
     <t>テストレベル</t>
@@ -591,22 +588,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>タスク削除成功画面が表示される</t>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>異常系</t>
     <rPh sb="0" eb="3">
       <t>イジョウケイ</t>
@@ -722,10 +703,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>http://localhost:8081/taskUN/comment-delete.jsp</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>はいボタンを押下後、コメント削除成功画面でブラウザバックし、もう一度はいボタンを押下する</t>
     <rPh sb="6" eb="8">
       <t>オウカ</t>
@@ -792,10 +769,6 @@
   </si>
   <si>
     <t>CommentDAOTest</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>deleteComment(CommentBean bean)</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
@@ -866,6 +839,99 @@
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>テスト仕様書兼
+結果報告書</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>タスク削除完了画面が表示される</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/comment-delete.jsp</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>deleteComment(int commentId)</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>テストエビデンス</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>グループ名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>承認印</t>
+    <rPh sb="0" eb="3">
+      <t>ショウニンイン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>機能名称</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイショウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エビデンス</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -1056,7 +1122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="76">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -1945,6 +2011,123 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1964,7 +2147,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="303">
+  <cellXfs count="333">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2871,6 +3054,96 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="12" fillId="0" borderId="62" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -3162,6 +3435,111 @@
         <a:xfrm>
           <a:off x="552450" y="1104900"/>
           <a:ext cx="7772400" cy="4060997"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>155864</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>51955</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>31173</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>38859</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55E39B5E-9162-3997-13A0-09001EF8B732}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1402773" y="2649682"/>
+          <a:ext cx="7772400" cy="5528722"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>121227</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>173181</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>793699</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFCFBFE8-50E0-A014-9A6B-5873F4633CF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2909455" y="28159363"/>
+          <a:ext cx="4745181" cy="2612109"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3554,7 +3932,7 @@
       <c r="B5" s="110"/>
       <c r="C5" s="111"/>
       <c r="D5" s="112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" s="110"/>
       <c r="F5" s="110"/>
@@ -3570,7 +3948,7 @@
       <c r="B6" s="89"/>
       <c r="C6" s="92"/>
       <c r="D6" s="93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" s="89"/>
       <c r="F6" s="89"/>
@@ -3602,7 +3980,7 @@
       <c r="B8" s="89"/>
       <c r="C8" s="92"/>
       <c r="D8" s="93" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8" s="89"/>
       <c r="F8" s="89"/>
@@ -3620,7 +3998,7 @@
       </c>
       <c r="C9" s="92"/>
       <c r="D9" s="88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" s="89"/>
       <c r="F9" s="89"/>
@@ -3650,7 +4028,7 @@
       </c>
       <c r="C11" s="92"/>
       <c r="D11" s="88" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E11" s="89"/>
       <c r="F11" s="89"/>
@@ -3666,7 +4044,7 @@
       <c r="B12" s="89"/>
       <c r="C12" s="92"/>
       <c r="D12" s="93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E12" s="89"/>
       <c r="F12" s="89"/>
@@ -4712,6 +5090,433 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE495DAC-CBB1-4E3A-9D67-856AE306D738}">
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A1" s="305" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="306"/>
+      <c r="C1" s="307"/>
+      <c r="D1" s="308" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="309"/>
+      <c r="F1" s="307"/>
+      <c r="G1" s="310" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1" s="309"/>
+      <c r="I1" s="311" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="312"/>
+      <c r="K1" s="311" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" s="312"/>
+      <c r="M1" s="311" t="s">
+        <v>134</v>
+      </c>
+      <c r="N1" s="313"/>
+      <c r="O1" s="314"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="315"/>
+      <c r="B2" s="316"/>
+      <c r="C2" s="305"/>
+      <c r="D2" s="317"/>
+      <c r="E2" s="306"/>
+      <c r="F2" s="305"/>
+      <c r="G2" s="317"/>
+      <c r="H2" s="306"/>
+      <c r="I2" s="305"/>
+      <c r="J2" s="306"/>
+      <c r="K2" s="305"/>
+      <c r="L2" s="306"/>
+      <c r="M2" s="305"/>
+      <c r="N2" s="306"/>
+      <c r="O2" s="318"/>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A3" s="319"/>
+      <c r="B3" s="320"/>
+      <c r="C3" s="319"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="319"/>
+      <c r="G3" s="321"/>
+      <c r="H3" s="320"/>
+      <c r="I3" s="319"/>
+      <c r="J3" s="320"/>
+      <c r="K3" s="319"/>
+      <c r="L3" s="320"/>
+      <c r="M3" s="319"/>
+      <c r="N3" s="320"/>
+      <c r="O3" s="318"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="305" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="306"/>
+      <c r="C4" s="322"/>
+      <c r="D4" s="323"/>
+      <c r="E4" s="323"/>
+      <c r="F4" s="323"/>
+      <c r="G4" s="323"/>
+      <c r="H4" s="323"/>
+      <c r="I4" s="323"/>
+      <c r="J4" s="323"/>
+      <c r="K4" s="323"/>
+      <c r="L4" s="323"/>
+      <c r="M4" s="323"/>
+      <c r="N4" s="324"/>
+      <c r="O4" s="318"/>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A5" s="319"/>
+      <c r="B5" s="320"/>
+      <c r="C5" s="325"/>
+      <c r="D5" s="326"/>
+      <c r="E5" s="326"/>
+      <c r="F5" s="326"/>
+      <c r="G5" s="326"/>
+      <c r="H5" s="326"/>
+      <c r="I5" s="326"/>
+      <c r="J5" s="326"/>
+      <c r="K5" s="326"/>
+      <c r="L5" s="326"/>
+      <c r="M5" s="326"/>
+      <c r="N5" s="327"/>
+      <c r="O5" s="318"/>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A6" s="311" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="312"/>
+      <c r="C6" s="311" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="313"/>
+      <c r="E6" s="313"/>
+      <c r="F6" s="313"/>
+      <c r="G6" s="313"/>
+      <c r="H6" s="313"/>
+      <c r="I6" s="313"/>
+      <c r="J6" s="313"/>
+      <c r="K6" s="313"/>
+      <c r="L6" s="313"/>
+      <c r="M6" s="313"/>
+      <c r="N6" s="312"/>
+      <c r="O6" s="318"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="305">
+        <v>1</v>
+      </c>
+      <c r="B7" s="306"/>
+      <c r="C7" s="328"/>
+      <c r="D7" s="328"/>
+      <c r="E7" s="328"/>
+      <c r="F7" s="328"/>
+      <c r="G7" s="328"/>
+      <c r="H7" s="328"/>
+      <c r="I7" s="328"/>
+      <c r="J7" s="328"/>
+      <c r="K7" s="328"/>
+      <c r="L7" s="328"/>
+      <c r="M7" s="328"/>
+      <c r="N7" s="328"/>
+      <c r="O7" s="318"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="315"/>
+      <c r="B8" s="316"/>
+      <c r="O8" s="318"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="315"/>
+      <c r="B9" s="316"/>
+      <c r="N9" s="329"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="315"/>
+      <c r="B10" s="316"/>
+      <c r="O10" s="318"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="315"/>
+      <c r="B11" s="316"/>
+      <c r="O11" s="318"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="315"/>
+      <c r="B12" s="316"/>
+      <c r="O12" s="318"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="315"/>
+      <c r="B13" s="316"/>
+      <c r="O13" s="318"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="315"/>
+      <c r="B14" s="316"/>
+      <c r="O14" s="318"/>
+    </row>
+    <row r="15" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A15" s="319"/>
+      <c r="B15" s="320"/>
+      <c r="C15" s="330"/>
+      <c r="D15" s="330"/>
+      <c r="E15" s="330"/>
+      <c r="F15" s="330"/>
+      <c r="G15" s="330"/>
+      <c r="H15" s="330"/>
+      <c r="I15" s="330"/>
+      <c r="J15" s="330"/>
+      <c r="K15" s="330"/>
+      <c r="L15" s="330"/>
+      <c r="M15" s="330"/>
+      <c r="N15" s="331"/>
+      <c r="O15" s="318"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="305">
+        <v>2</v>
+      </c>
+      <c r="B16" s="306"/>
+      <c r="C16" s="328"/>
+      <c r="D16" s="328"/>
+      <c r="E16" s="328"/>
+      <c r="F16" s="328"/>
+      <c r="G16" s="328"/>
+      <c r="H16" s="328"/>
+      <c r="I16" s="328"/>
+      <c r="J16" s="328"/>
+      <c r="K16" s="328"/>
+      <c r="L16" s="328"/>
+      <c r="M16" s="328"/>
+      <c r="N16" s="329"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="315"/>
+      <c r="B17" s="316"/>
+      <c r="N17" s="329"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="315"/>
+      <c r="B18" s="316"/>
+      <c r="N18" s="329"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="315"/>
+      <c r="B19" s="316"/>
+      <c r="N19" s="329"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="315"/>
+      <c r="B20" s="316"/>
+      <c r="N20" s="329"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="315"/>
+      <c r="B21" s="316"/>
+      <c r="N21" s="329"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="315"/>
+      <c r="B22" s="316"/>
+      <c r="N22" s="329"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="315"/>
+      <c r="B23" s="316"/>
+      <c r="N23" s="329"/>
+    </row>
+    <row r="24" spans="1:14" ht="19.5" thickBot="1">
+      <c r="A24" s="319"/>
+      <c r="B24" s="320"/>
+      <c r="C24" s="330"/>
+      <c r="D24" s="330"/>
+      <c r="E24" s="330"/>
+      <c r="F24" s="330"/>
+      <c r="G24" s="330"/>
+      <c r="H24" s="330"/>
+      <c r="I24" s="330"/>
+      <c r="J24" s="330"/>
+      <c r="K24" s="330"/>
+      <c r="L24" s="330"/>
+      <c r="M24" s="330"/>
+      <c r="N24" s="331"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="305">
+        <v>3</v>
+      </c>
+      <c r="B25" s="306"/>
+      <c r="C25" s="328"/>
+      <c r="D25" s="328"/>
+      <c r="E25" s="328"/>
+      <c r="F25" s="328"/>
+      <c r="G25" s="328"/>
+      <c r="H25" s="328"/>
+      <c r="I25" s="328"/>
+      <c r="J25" s="328"/>
+      <c r="K25" s="328"/>
+      <c r="L25" s="328"/>
+      <c r="M25" s="328"/>
+      <c r="N25" s="329"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="315"/>
+      <c r="B26" s="316"/>
+      <c r="N26" s="329"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="315"/>
+      <c r="B27" s="316"/>
+      <c r="N27" s="329"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="315"/>
+      <c r="B28" s="316"/>
+      <c r="N28" s="329"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="315"/>
+      <c r="B29" s="316"/>
+      <c r="N29" s="329"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="315"/>
+      <c r="B30" s="316"/>
+      <c r="N30" s="329"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="315"/>
+      <c r="B31" s="316"/>
+      <c r="N31" s="329"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="315"/>
+      <c r="B32" s="316"/>
+      <c r="N32" s="329"/>
+    </row>
+    <row r="33" spans="1:14" ht="19.5" thickBot="1">
+      <c r="A33" s="319"/>
+      <c r="B33" s="320"/>
+      <c r="C33" s="330"/>
+      <c r="D33" s="330"/>
+      <c r="E33" s="330"/>
+      <c r="F33" s="330"/>
+      <c r="G33" s="330"/>
+      <c r="H33" s="330"/>
+      <c r="I33" s="330"/>
+      <c r="J33" s="330"/>
+      <c r="K33" s="330"/>
+      <c r="L33" s="330"/>
+      <c r="N33" s="329"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="305">
+        <v>4</v>
+      </c>
+      <c r="B34" s="306"/>
+      <c r="C34" s="328"/>
+      <c r="D34" s="328"/>
+      <c r="E34" s="328"/>
+      <c r="F34" s="328"/>
+      <c r="G34" s="328"/>
+      <c r="H34" s="328"/>
+      <c r="I34" s="328"/>
+      <c r="J34" s="328"/>
+      <c r="K34" s="328"/>
+      <c r="L34" s="328"/>
+      <c r="M34" s="328"/>
+      <c r="N34" s="332"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="315"/>
+      <c r="B35" s="316"/>
+      <c r="N35" s="329"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="315"/>
+      <c r="B36" s="316"/>
+      <c r="N36" s="329"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="315"/>
+      <c r="B37" s="316"/>
+      <c r="N37" s="329"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="315"/>
+      <c r="B38" s="316"/>
+      <c r="N38" s="329"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="315"/>
+      <c r="B39" s="316"/>
+      <c r="N39" s="329"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="315"/>
+      <c r="B40" s="316"/>
+      <c r="N40" s="329"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="315"/>
+      <c r="B41" s="316"/>
+      <c r="N41" s="329"/>
+    </row>
+    <row r="42" spans="1:14" ht="19.5" thickBot="1">
+      <c r="A42" s="319"/>
+      <c r="B42" s="320"/>
+      <c r="C42" s="330"/>
+      <c r="D42" s="330"/>
+      <c r="E42" s="330"/>
+      <c r="F42" s="330"/>
+      <c r="G42" s="330"/>
+      <c r="H42" s="330"/>
+      <c r="I42" s="330"/>
+      <c r="J42" s="330"/>
+      <c r="K42" s="330"/>
+      <c r="L42" s="330"/>
+      <c r="M42" s="330"/>
+      <c r="N42" s="331"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A25:B33"/>
+    <mergeCell ref="A34:B42"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="A7:B15"/>
+    <mergeCell ref="A16:B24"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="C2:E3"/>
+    <mergeCell ref="F2:H3"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="M2:N3"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94B549E0-E6DE-4B9D-8E20-4FFD73143070}">
   <dimension ref="A1:J1000"/>
@@ -4752,18 +5557,18 @@
       <c r="B2" s="139"/>
       <c r="C2" s="140"/>
       <c r="D2" s="146" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" s="147"/>
       <c r="F2" s="146" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G2" s="147"/>
       <c r="H2" s="150">
         <v>45827</v>
       </c>
       <c r="I2" s="129" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="132"/>
     </row>
@@ -6151,7 +6956,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="178" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="179"/>
       <c r="C1" s="180"/>
@@ -6189,7 +6994,7 @@
         <v>45827</v>
       </c>
       <c r="I2" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="165"/>
     </row>
@@ -6219,12 +7024,12 @@
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="168"/>
       <c r="C5" s="169"/>
       <c r="D5" s="170" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" s="168"/>
       <c r="F5" s="168"/>
@@ -6235,7 +7040,7 @@
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="161" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="152"/>
       <c r="C6" s="152"/>
@@ -6333,7 +7138,7 @@
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="161" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="152"/>
       <c r="C14" s="152"/>
@@ -6347,41 +7152,41 @@
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="161" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="152"/>
       <c r="C15" s="153"/>
       <c r="D15" s="154" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="152"/>
       <c r="F15" s="152"/>
       <c r="G15" s="152"/>
       <c r="H15" s="153"/>
       <c r="I15" s="52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="161" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="152"/>
       <c r="C16" s="153"/>
       <c r="D16" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="F16" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="G16" s="52" t="s">
         <v>53</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>54</v>
       </c>
       <c r="H16" s="162" t="s">
         <v>19</v>
@@ -6396,16 +7201,16 @@
       <c r="B17" s="152"/>
       <c r="C17" s="153"/>
       <c r="D17" s="54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="F17" s="55" t="s">
+      <c r="G17" s="55" t="s">
         <v>87</v>
-      </c>
-      <c r="G17" s="55" t="s">
-        <v>88</v>
       </c>
       <c r="H17" s="154"/>
       <c r="I17" s="152"/>
@@ -6418,14 +7223,14 @@
       <c r="B18" s="152"/>
       <c r="C18" s="153"/>
       <c r="D18" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="54" t="s">
         <v>85</v>
-      </c>
-      <c r="E18" s="54" t="s">
-        <v>86</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H18" s="154"/>
       <c r="I18" s="152"/>
@@ -7526,7 +8331,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="178" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="179"/>
       <c r="C1" s="180"/>
@@ -7564,7 +8369,7 @@
         <v>45827</v>
       </c>
       <c r="I2" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="165"/>
     </row>
@@ -7594,12 +8399,12 @@
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="168"/>
       <c r="C5" s="169"/>
       <c r="D5" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E5" s="168"/>
       <c r="F5" s="168"/>
@@ -7610,7 +8415,7 @@
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="161" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="152"/>
       <c r="C6" s="152"/>
@@ -7708,7 +8513,7 @@
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="161" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="152"/>
       <c r="C14" s="152"/>
@@ -7722,39 +8527,39 @@
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="161" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="152"/>
       <c r="C15" s="153"/>
       <c r="D15" s="154" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="152"/>
       <c r="F15" s="152"/>
       <c r="G15" s="152"/>
       <c r="H15" s="153"/>
       <c r="I15" s="52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="161" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="152"/>
       <c r="C16" s="153"/>
       <c r="D16" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="F16" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="G16" s="52" t="s">
         <v>53</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>54</v>
       </c>
       <c r="H16" s="162" t="s">
         <v>19</v>
@@ -7769,16 +8574,16 @@
       <c r="B17" s="152"/>
       <c r="C17" s="153"/>
       <c r="D17" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="55" t="s">
         <v>98</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="55" t="s">
-        <v>99</v>
       </c>
       <c r="H17" s="154"/>
       <c r="I17" s="152"/>
@@ -8890,7 +9695,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="178" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="179"/>
       <c r="C1" s="180"/>
@@ -8928,7 +9733,7 @@
         <v>45827</v>
       </c>
       <c r="I2" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="165"/>
     </row>
@@ -8958,12 +9763,12 @@
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="168"/>
       <c r="C5" s="169"/>
       <c r="D5" s="170" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E5" s="168"/>
       <c r="F5" s="168"/>
@@ -8974,7 +9779,7 @@
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="161" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="152"/>
       <c r="C6" s="152"/>
@@ -9072,7 +9877,7 @@
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="161" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="152"/>
       <c r="C14" s="152"/>
@@ -9086,41 +9891,41 @@
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="161" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="152"/>
       <c r="C15" s="153"/>
       <c r="D15" s="154" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="152"/>
       <c r="F15" s="152"/>
       <c r="G15" s="152"/>
       <c r="H15" s="153"/>
       <c r="I15" s="52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="161" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="152"/>
       <c r="C16" s="153"/>
       <c r="D16" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="F16" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="G16" s="52" t="s">
         <v>53</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>54</v>
       </c>
       <c r="H16" s="162" t="s">
         <v>19</v>
@@ -9135,16 +9940,16 @@
       <c r="B17" s="152"/>
       <c r="C17" s="153"/>
       <c r="D17" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="55" t="s">
         <v>98</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="55" t="s">
-        <v>99</v>
       </c>
       <c r="H17" s="154"/>
       <c r="I17" s="152"/>
@@ -10280,18 +11085,18 @@
       <c r="B2" s="197"/>
       <c r="C2" s="198"/>
       <c r="D2" s="204" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" s="205"/>
       <c r="F2" s="204" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G2" s="205"/>
       <c r="H2" s="208">
         <v>45827</v>
       </c>
       <c r="I2" s="187" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="190"/>
     </row>
@@ -11667,7 +12472,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
       <c r="A1" s="237" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="B1" s="238"/>
       <c r="C1" s="238"/>
@@ -11707,13 +12512,13 @@
       <c r="E2" s="241"/>
       <c r="F2" s="242"/>
       <c r="G2" s="224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H2" s="247"/>
       <c r="I2" s="247"/>
       <c r="J2" s="248"/>
       <c r="K2" s="224" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L2" s="247"/>
       <c r="M2" s="247"/>
@@ -11723,7 +12528,7 @@
       </c>
       <c r="P2" s="248"/>
       <c r="Q2" s="224" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R2" s="248"/>
       <c r="S2" s="224"/>
@@ -11775,7 +12580,7 @@
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="230" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="231"/>
       <c r="C5" s="231"/>
@@ -11783,7 +12588,7 @@
       <c r="E5" s="231"/>
       <c r="F5" s="232"/>
       <c r="G5" s="233" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="231"/>
       <c r="I5" s="231"/>
@@ -11801,7 +12606,7 @@
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="222" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="216"/>
       <c r="C6" s="216"/>
@@ -11827,7 +12632,7 @@
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="222" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="216"/>
       <c r="C7" s="216"/>
@@ -11835,7 +12640,7 @@
       <c r="E7" s="216"/>
       <c r="F7" s="217"/>
       <c r="G7" s="235" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H7" s="216"/>
       <c r="I7" s="216"/>
@@ -11877,11 +12682,11 @@
       <c r="A9" s="29"/>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="33"/>
@@ -11911,7 +12716,7 @@
       <c r="C10" s="35"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" s="30"/>
       <c r="G10" s="36"/>
@@ -11941,7 +12746,7 @@
       <c r="C11" s="35"/>
       <c r="D11" s="30"/>
       <c r="E11" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="30"/>
       <c r="G11" s="36"/>
@@ -11971,7 +12776,7 @@
       <c r="C12" s="35"/>
       <c r="D12" s="30"/>
       <c r="E12" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="30"/>
       <c r="G12" s="36"/>
@@ -12001,7 +12806,7 @@
       <c r="C13" s="37"/>
       <c r="D13" s="38"/>
       <c r="E13" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="38"/>
       <c r="G13" s="39"/>
@@ -12049,44 +12854,44 @@
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
       <c r="A15" s="222" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="217"/>
       <c r="C15" s="223" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="217"/>
       <c r="E15" s="221" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="217"/>
       <c r="G15" s="221" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H15" s="216"/>
       <c r="I15" s="217"/>
       <c r="J15" s="221" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K15" s="217"/>
       <c r="L15" s="221" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M15" s="216"/>
       <c r="N15" s="217"/>
       <c r="O15" s="221" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P15" s="216"/>
       <c r="Q15" s="217"/>
       <c r="R15" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="S15" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="S15" s="40" t="s">
+      <c r="T15" s="41" t="s">
         <v>40</v>
-      </c>
-      <c r="T15" s="41" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
@@ -12095,35 +12900,41 @@
       </c>
       <c r="B16" s="288"/>
       <c r="C16" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="288"/>
       <c r="E16" s="289" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" s="288"/>
       <c r="G16" s="290" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H16" s="291"/>
       <c r="I16" s="288"/>
       <c r="J16" s="292" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K16" s="92"/>
       <c r="L16" s="293" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M16" s="291"/>
       <c r="N16" s="288"/>
       <c r="O16" s="293" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P16" s="291"/>
       <c r="Q16" s="288"/>
-      <c r="R16" s="294"/>
-      <c r="S16" s="294"/>
-      <c r="T16" s="295"/>
+      <c r="R16" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S16" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T16" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U16" s="44"/>
       <c r="V16" s="44"/>
       <c r="W16" s="44"/>
@@ -12137,35 +12948,41 @@
       </c>
       <c r="B17" s="288"/>
       <c r="C17" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="288"/>
       <c r="E17" s="289" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" s="288"/>
       <c r="G17" s="290" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H17" s="291"/>
       <c r="I17" s="288"/>
       <c r="J17" s="290" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K17" s="288"/>
       <c r="L17" s="293" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M17" s="291"/>
       <c r="N17" s="288"/>
       <c r="O17" s="293" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="P17" s="291"/>
       <c r="Q17" s="288"/>
-      <c r="R17" s="294"/>
-      <c r="S17" s="294"/>
-      <c r="T17" s="295"/>
+      <c r="R17" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S17" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T17" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U17" s="44"/>
       <c r="V17" s="44"/>
       <c r="W17" s="44"/>
@@ -12179,35 +12996,41 @@
       </c>
       <c r="B18" s="288"/>
       <c r="C18" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="288"/>
       <c r="E18" s="289" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" s="288"/>
       <c r="G18" s="290" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H18" s="291"/>
       <c r="I18" s="288"/>
       <c r="J18" s="290" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K18" s="288"/>
       <c r="L18" s="293" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M18" s="291"/>
       <c r="N18" s="288"/>
       <c r="O18" s="293" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="P18" s="291"/>
       <c r="Q18" s="288"/>
-      <c r="R18" s="294"/>
-      <c r="S18" s="294"/>
-      <c r="T18" s="295"/>
+      <c r="R18" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S18" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T18" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U18" s="44"/>
       <c r="V18" s="44"/>
       <c r="W18" s="44"/>
@@ -12221,35 +13044,41 @@
       </c>
       <c r="B19" s="288"/>
       <c r="C19" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="288"/>
       <c r="E19" s="289" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F19" s="288"/>
       <c r="G19" s="290" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H19" s="291"/>
       <c r="I19" s="288"/>
       <c r="J19" s="290" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K19" s="288"/>
       <c r="L19" s="296" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="M19" s="291"/>
       <c r="N19" s="288"/>
       <c r="O19" s="293" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P19" s="291"/>
       <c r="Q19" s="288"/>
-      <c r="R19" s="294"/>
-      <c r="S19" s="294"/>
-      <c r="T19" s="295"/>
+      <c r="R19" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S19" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T19" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U19" s="44"/>
       <c r="V19" s="44"/>
       <c r="W19" s="44"/>
@@ -12263,35 +13092,41 @@
       </c>
       <c r="B20" s="288"/>
       <c r="C20" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="302"/>
       <c r="E20" s="289" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F20" s="302"/>
       <c r="G20" s="290" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H20" s="301"/>
       <c r="I20" s="300"/>
       <c r="J20" s="290" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K20" s="300"/>
       <c r="L20" s="293" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M20" s="298"/>
       <c r="N20" s="299"/>
       <c r="O20" s="293" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P20" s="298"/>
       <c r="Q20" s="299"/>
-      <c r="R20" s="294"/>
-      <c r="S20" s="294"/>
-      <c r="T20" s="295"/>
+      <c r="R20" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S20" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T20" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U20" s="44"/>
       <c r="V20" s="44"/>
       <c r="W20" s="44"/>
@@ -13756,16 +14591,16 @@
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
       <c r="A1" s="266" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="266"/>
       <c r="C1" s="267" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D1" s="268"/>
       <c r="E1" s="269"/>
       <c r="F1" s="270" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G1" s="271"/>
       <c r="H1" s="271"/>
@@ -13775,17 +14610,17 @@
       <c r="L1" s="271"/>
       <c r="M1" s="272"/>
       <c r="N1" s="58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O1" s="270" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P1" s="272"/>
       <c r="Q1" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="R1" s="270" t="s">
         <v>58</v>
-      </c>
-      <c r="R1" s="270" t="s">
-        <v>59</v>
       </c>
       <c r="S1" s="272"/>
     </row>
@@ -13793,12 +14628,12 @@
       <c r="A2" s="266"/>
       <c r="B2" s="266"/>
       <c r="C2" s="267" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" s="268"/>
       <c r="E2" s="269"/>
       <c r="F2" s="270" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G2" s="271"/>
       <c r="H2" s="271"/>
@@ -13808,14 +14643,14 @@
       <c r="L2" s="271"/>
       <c r="M2" s="272"/>
       <c r="N2" s="58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O2" s="273">
         <v>45827</v>
       </c>
       <c r="P2" s="274"/>
       <c r="Q2" s="60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R2" s="275"/>
       <c r="S2" s="276"/>
@@ -13843,20 +14678,20 @@
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
       <c r="A4" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="64" t="s">
+      <c r="C4" s="257" t="s">
         <v>64</v>
-      </c>
-      <c r="C4" s="257" t="s">
-        <v>65</v>
       </c>
       <c r="D4" s="258"/>
       <c r="E4" s="258"/>
       <c r="F4" s="258"/>
       <c r="G4" s="259"/>
       <c r="H4" s="257" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="258"/>
       <c r="J4" s="258"/>
@@ -13864,15 +14699,15 @@
       <c r="L4" s="258"/>
       <c r="M4" s="259"/>
       <c r="N4" s="257" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O4" s="258"/>
       <c r="P4" s="259"/>
       <c r="Q4" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4" s="257" t="s">
         <v>68</v>
-      </c>
-      <c r="R4" s="257" t="s">
-        <v>69</v>
       </c>
       <c r="S4" s="259"/>
     </row>
@@ -13881,17 +14716,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="260" t="s">
         <v>117</v>
-      </c>
-      <c r="C5" s="260" t="s">
-        <v>120</v>
       </c>
       <c r="D5" s="260"/>
       <c r="E5" s="260"/>
       <c r="F5" s="260"/>
       <c r="G5" s="260"/>
       <c r="H5" s="260" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I5" s="260"/>
       <c r="J5" s="260"/>
@@ -13899,11 +14734,13 @@
       <c r="L5" s="260"/>
       <c r="M5" s="260"/>
       <c r="N5" s="261" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O5" s="262"/>
       <c r="P5" s="263"/>
-      <c r="Q5" s="65"/>
+      <c r="Q5" s="304">
+        <v>45827</v>
+      </c>
       <c r="R5" s="264"/>
       <c r="S5" s="265"/>
     </row>
@@ -13912,17 +14749,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" s="260" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D6" s="260"/>
       <c r="E6" s="260"/>
       <c r="F6" s="260"/>
       <c r="G6" s="260"/>
       <c r="H6" s="260" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I6" s="260"/>
       <c r="J6" s="260"/>
@@ -13930,11 +14767,13 @@
       <c r="L6" s="260"/>
       <c r="M6" s="260"/>
       <c r="N6" s="261" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O6" s="262"/>
       <c r="P6" s="263"/>
-      <c r="Q6" s="69"/>
+      <c r="Q6" s="69">
+        <v>45827</v>
+      </c>
       <c r="R6" s="256"/>
       <c r="S6" s="256"/>
     </row>
@@ -15134,7 +15973,7 @@
     <row r="1" spans="1:53" ht="30" customHeight="1">
       <c r="A1" s="71"/>
       <c r="B1" s="72" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C1" s="73"/>
       <c r="D1" s="71"/>
@@ -15175,7 +16014,7 @@
       <c r="AM1" s="71"/>
       <c r="AN1" s="71"/>
       <c r="AO1" s="280" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AP1" s="280"/>
       <c r="AQ1" s="280"/>
@@ -15194,7 +16033,7 @@
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="4" spans="1:53" ht="18" customHeight="1">
       <c r="A4" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="78"/>
       <c r="C4" s="79"/>
@@ -15235,7 +16074,7 @@
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
       <c r="A5" s="277" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" s="278"/>
       <c r="C5" s="278"/>
@@ -15243,7 +16082,7 @@
       <c r="E5" s="278"/>
       <c r="F5" s="279"/>
       <c r="G5" s="283" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H5" s="284"/>
       <c r="I5" s="284"/>
@@ -15260,14 +16099,16 @@
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
       <c r="A6" s="277" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="278"/>
       <c r="C6" s="278"/>
       <c r="D6" s="278"/>
       <c r="E6" s="278"/>
       <c r="F6" s="279"/>
-      <c r="G6" s="286"/>
+      <c r="G6" s="286">
+        <v>1</v>
+      </c>
       <c r="H6" s="284"/>
       <c r="I6" s="284"/>
       <c r="J6" s="284"/>
@@ -15284,12 +16125,12 @@
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
       <c r="A8" s="78" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
       <c r="A9" s="277" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="278"/>
       <c r="C9" s="278"/>
@@ -19066,7 +19907,7 @@
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
       <c r="A103" s="277" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B103" s="278"/>
       <c r="C103" s="278"/>
@@ -19401,7 +20242,7 @@
       <c r="AK110" s="81"/>
       <c r="BA110" s="82"/>
     </row>
-    <row r="111" spans="1:53" ht="21.95" customHeight="1">
+    <row r="111" spans="1:53" ht="63" customHeight="1">
       <c r="A111" s="85"/>
       <c r="B111" s="86"/>
       <c r="C111" s="86"/>
@@ -19443,7 +20284,7 @@
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
       <c r="A112" s="277" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B112" s="278"/>
       <c r="C112" s="278"/>
@@ -19654,5 +20495,6 @@
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Documents/コメント削除機能設計書.xlsx
+++ b/Documents/コメント削除機能設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F715AA-D96B-4E9F-A592-CB8BD991F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D60A8D-074C-4FE2-BCE2-2A5736FC8D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{73C913ED-0334-40C4-8D2F-5AD7FF49F493}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="8" xr2:uid="{73C913ED-0334-40C4-8D2F-5AD7FF49F493}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="129">
   <si>
     <t>ユースケース記述</t>
   </si>
@@ -113,10 +113,6 @@
   </si>
   <si>
     <t>詳細クラス図</t>
-  </si>
-  <si>
-    <t>テスト仕様書兼
-結果報告書</t>
   </si>
   <si>
     <t>テストレベル</t>
@@ -591,22 +587,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>タスク削除成功画面が表示される</t>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>異常系</t>
     <rPh sb="0" eb="3">
       <t>イジョウケイ</t>
@@ -722,10 +702,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>http://localhost:8081/taskUN/comment-delete.jsp</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>はいボタンを押下後、コメント削除成功画面でブラウザバックし、もう一度はいボタンを押下する</t>
     <rPh sb="6" eb="8">
       <t>オウカ</t>
@@ -795,10 +771,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>deleteComment(CommentBean bean)</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>CommentDAO</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -865,6 +837,39 @@
     <rPh sb="8" eb="10">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>テスト仕様書兼
+結果報告書</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>タスク削除完了画面が表示される</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/comment-delete.jsp</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>deleteComment(int commentId)</t>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -1964,7 +1969,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="303">
+  <cellXfs count="305">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2871,6 +2876,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="12" fillId="0" borderId="62" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -3162,6 +3173,111 @@
         <a:xfrm>
           <a:off x="552450" y="1104900"/>
           <a:ext cx="7772400" cy="4060997"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>155864</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>51955</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>31173</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>38859</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55E39B5E-9162-3997-13A0-09001EF8B732}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1402773" y="2649682"/>
+          <a:ext cx="7772400" cy="5528722"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>121227</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>173181</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>793699</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFCFBFE8-50E0-A014-9A6B-5873F4633CF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2909455" y="28159363"/>
+          <a:ext cx="4745181" cy="2612109"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3554,7 +3670,7 @@
       <c r="B5" s="110"/>
       <c r="C5" s="111"/>
       <c r="D5" s="112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" s="110"/>
       <c r="F5" s="110"/>
@@ -3570,7 +3686,7 @@
       <c r="B6" s="89"/>
       <c r="C6" s="92"/>
       <c r="D6" s="93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" s="89"/>
       <c r="F6" s="89"/>
@@ -3602,7 +3718,7 @@
       <c r="B8" s="89"/>
       <c r="C8" s="92"/>
       <c r="D8" s="93" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8" s="89"/>
       <c r="F8" s="89"/>
@@ -3620,7 +3736,7 @@
       </c>
       <c r="C9" s="92"/>
       <c r="D9" s="88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" s="89"/>
       <c r="F9" s="89"/>
@@ -3650,7 +3766,7 @@
       </c>
       <c r="C11" s="92"/>
       <c r="D11" s="88" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E11" s="89"/>
       <c r="F11" s="89"/>
@@ -3666,7 +3782,7 @@
       <c r="B12" s="89"/>
       <c r="C12" s="92"/>
       <c r="D12" s="93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E12" s="89"/>
       <c r="F12" s="89"/>
@@ -4752,18 +4868,18 @@
       <c r="B2" s="139"/>
       <c r="C2" s="140"/>
       <c r="D2" s="146" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" s="147"/>
       <c r="F2" s="146" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G2" s="147"/>
       <c r="H2" s="150">
         <v>45827</v>
       </c>
       <c r="I2" s="129" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="132"/>
     </row>
@@ -6151,7 +6267,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="178" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="179"/>
       <c r="C1" s="180"/>
@@ -6189,7 +6305,7 @@
         <v>45827</v>
       </c>
       <c r="I2" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="165"/>
     </row>
@@ -6219,12 +6335,12 @@
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="168"/>
       <c r="C5" s="169"/>
       <c r="D5" s="170" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" s="168"/>
       <c r="F5" s="168"/>
@@ -6235,7 +6351,7 @@
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="161" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="152"/>
       <c r="C6" s="152"/>
@@ -6333,7 +6449,7 @@
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="161" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="152"/>
       <c r="C14" s="152"/>
@@ -6347,41 +6463,41 @@
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="161" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="152"/>
       <c r="C15" s="153"/>
       <c r="D15" s="154" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="152"/>
       <c r="F15" s="152"/>
       <c r="G15" s="152"/>
       <c r="H15" s="153"/>
       <c r="I15" s="52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="161" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="152"/>
       <c r="C16" s="153"/>
       <c r="D16" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="F16" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="G16" s="52" t="s">
         <v>53</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>54</v>
       </c>
       <c r="H16" s="162" t="s">
         <v>19</v>
@@ -6396,16 +6512,16 @@
       <c r="B17" s="152"/>
       <c r="C17" s="153"/>
       <c r="D17" s="54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="F17" s="55" t="s">
+      <c r="G17" s="55" t="s">
         <v>87</v>
-      </c>
-      <c r="G17" s="55" t="s">
-        <v>88</v>
       </c>
       <c r="H17" s="154"/>
       <c r="I17" s="152"/>
@@ -6418,14 +6534,14 @@
       <c r="B18" s="152"/>
       <c r="C18" s="153"/>
       <c r="D18" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="54" t="s">
         <v>85</v>
-      </c>
-      <c r="E18" s="54" t="s">
-        <v>86</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H18" s="154"/>
       <c r="I18" s="152"/>
@@ -7526,7 +7642,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="178" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="179"/>
       <c r="C1" s="180"/>
@@ -7564,7 +7680,7 @@
         <v>45827</v>
       </c>
       <c r="I2" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="165"/>
     </row>
@@ -7594,12 +7710,12 @@
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="168"/>
       <c r="C5" s="169"/>
       <c r="D5" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E5" s="168"/>
       <c r="F5" s="168"/>
@@ -7610,7 +7726,7 @@
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="161" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="152"/>
       <c r="C6" s="152"/>
@@ -7708,7 +7824,7 @@
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="161" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="152"/>
       <c r="C14" s="152"/>
@@ -7722,39 +7838,39 @@
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="161" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="152"/>
       <c r="C15" s="153"/>
       <c r="D15" s="154" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="152"/>
       <c r="F15" s="152"/>
       <c r="G15" s="152"/>
       <c r="H15" s="153"/>
       <c r="I15" s="52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="161" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="152"/>
       <c r="C16" s="153"/>
       <c r="D16" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="F16" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="G16" s="52" t="s">
         <v>53</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>54</v>
       </c>
       <c r="H16" s="162" t="s">
         <v>19</v>
@@ -7769,16 +7885,16 @@
       <c r="B17" s="152"/>
       <c r="C17" s="153"/>
       <c r="D17" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="55" t="s">
         <v>98</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="55" t="s">
-        <v>99</v>
       </c>
       <c r="H17" s="154"/>
       <c r="I17" s="152"/>
@@ -8890,7 +9006,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="178" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="179"/>
       <c r="C1" s="180"/>
@@ -8928,7 +9044,7 @@
         <v>45827</v>
       </c>
       <c r="I2" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="165"/>
     </row>
@@ -8958,12 +9074,12 @@
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="168"/>
       <c r="C5" s="169"/>
       <c r="D5" s="170" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E5" s="168"/>
       <c r="F5" s="168"/>
@@ -8974,7 +9090,7 @@
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="161" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="152"/>
       <c r="C6" s="152"/>
@@ -9072,7 +9188,7 @@
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="161" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="152"/>
       <c r="C14" s="152"/>
@@ -9086,41 +9202,41 @@
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="161" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="152"/>
       <c r="C15" s="153"/>
       <c r="D15" s="154" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="152"/>
       <c r="F15" s="152"/>
       <c r="G15" s="152"/>
       <c r="H15" s="153"/>
       <c r="I15" s="52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="161" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="152"/>
       <c r="C16" s="153"/>
       <c r="D16" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="F16" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="G16" s="52" t="s">
         <v>53</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>54</v>
       </c>
       <c r="H16" s="162" t="s">
         <v>19</v>
@@ -9135,16 +9251,16 @@
       <c r="B17" s="152"/>
       <c r="C17" s="153"/>
       <c r="D17" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="55" t="s">
         <v>98</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="55" t="s">
-        <v>99</v>
       </c>
       <c r="H17" s="154"/>
       <c r="I17" s="152"/>
@@ -10280,18 +10396,18 @@
       <c r="B2" s="197"/>
       <c r="C2" s="198"/>
       <c r="D2" s="204" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" s="205"/>
       <c r="F2" s="204" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G2" s="205"/>
       <c r="H2" s="208">
         <v>45827</v>
       </c>
       <c r="I2" s="187" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" s="190"/>
     </row>
@@ -11667,7 +11783,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
       <c r="A1" s="237" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="B1" s="238"/>
       <c r="C1" s="238"/>
@@ -11707,13 +11823,13 @@
       <c r="E2" s="241"/>
       <c r="F2" s="242"/>
       <c r="G2" s="224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H2" s="247"/>
       <c r="I2" s="247"/>
       <c r="J2" s="248"/>
       <c r="K2" s="224" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L2" s="247"/>
       <c r="M2" s="247"/>
@@ -11723,7 +11839,7 @@
       </c>
       <c r="P2" s="248"/>
       <c r="Q2" s="224" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R2" s="248"/>
       <c r="S2" s="224"/>
@@ -11775,7 +11891,7 @@
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="230" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="231"/>
       <c r="C5" s="231"/>
@@ -11783,7 +11899,7 @@
       <c r="E5" s="231"/>
       <c r="F5" s="232"/>
       <c r="G5" s="233" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="231"/>
       <c r="I5" s="231"/>
@@ -11801,7 +11917,7 @@
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="222" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="216"/>
       <c r="C6" s="216"/>
@@ -11827,7 +11943,7 @@
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="222" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="216"/>
       <c r="C7" s="216"/>
@@ -11835,7 +11951,7 @@
       <c r="E7" s="216"/>
       <c r="F7" s="217"/>
       <c r="G7" s="235" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H7" s="216"/>
       <c r="I7" s="216"/>
@@ -11877,11 +11993,11 @@
       <c r="A9" s="29"/>
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="33"/>
@@ -11911,7 +12027,7 @@
       <c r="C10" s="35"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" s="30"/>
       <c r="G10" s="36"/>
@@ -11941,7 +12057,7 @@
       <c r="C11" s="35"/>
       <c r="D11" s="30"/>
       <c r="E11" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="30"/>
       <c r="G11" s="36"/>
@@ -11971,7 +12087,7 @@
       <c r="C12" s="35"/>
       <c r="D12" s="30"/>
       <c r="E12" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="30"/>
       <c r="G12" s="36"/>
@@ -12001,7 +12117,7 @@
       <c r="C13" s="37"/>
       <c r="D13" s="38"/>
       <c r="E13" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="38"/>
       <c r="G13" s="39"/>
@@ -12049,44 +12165,44 @@
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
       <c r="A15" s="222" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="217"/>
       <c r="C15" s="223" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="217"/>
       <c r="E15" s="221" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="217"/>
       <c r="G15" s="221" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H15" s="216"/>
       <c r="I15" s="217"/>
       <c r="J15" s="221" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K15" s="217"/>
       <c r="L15" s="221" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M15" s="216"/>
       <c r="N15" s="217"/>
       <c r="O15" s="221" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P15" s="216"/>
       <c r="Q15" s="217"/>
       <c r="R15" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="S15" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="S15" s="40" t="s">
+      <c r="T15" s="41" t="s">
         <v>40</v>
-      </c>
-      <c r="T15" s="41" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
@@ -12095,35 +12211,41 @@
       </c>
       <c r="B16" s="288"/>
       <c r="C16" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="288"/>
       <c r="E16" s="289" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" s="288"/>
       <c r="G16" s="290" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H16" s="291"/>
       <c r="I16" s="288"/>
       <c r="J16" s="292" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K16" s="92"/>
       <c r="L16" s="293" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M16" s="291"/>
       <c r="N16" s="288"/>
       <c r="O16" s="293" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P16" s="291"/>
       <c r="Q16" s="288"/>
-      <c r="R16" s="294"/>
-      <c r="S16" s="294"/>
-      <c r="T16" s="295"/>
+      <c r="R16" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S16" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T16" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U16" s="44"/>
       <c r="V16" s="44"/>
       <c r="W16" s="44"/>
@@ -12137,35 +12259,41 @@
       </c>
       <c r="B17" s="288"/>
       <c r="C17" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="288"/>
       <c r="E17" s="289" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" s="288"/>
       <c r="G17" s="290" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H17" s="291"/>
       <c r="I17" s="288"/>
       <c r="J17" s="290" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K17" s="288"/>
       <c r="L17" s="293" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M17" s="291"/>
       <c r="N17" s="288"/>
       <c r="O17" s="293" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="P17" s="291"/>
       <c r="Q17" s="288"/>
-      <c r="R17" s="294"/>
-      <c r="S17" s="294"/>
-      <c r="T17" s="295"/>
+      <c r="R17" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S17" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T17" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U17" s="44"/>
       <c r="V17" s="44"/>
       <c r="W17" s="44"/>
@@ -12179,35 +12307,41 @@
       </c>
       <c r="B18" s="288"/>
       <c r="C18" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="288"/>
       <c r="E18" s="289" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" s="288"/>
       <c r="G18" s="290" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H18" s="291"/>
       <c r="I18" s="288"/>
       <c r="J18" s="290" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K18" s="288"/>
       <c r="L18" s="293" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M18" s="291"/>
       <c r="N18" s="288"/>
       <c r="O18" s="293" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="P18" s="291"/>
       <c r="Q18" s="288"/>
-      <c r="R18" s="294"/>
-      <c r="S18" s="294"/>
-      <c r="T18" s="295"/>
+      <c r="R18" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S18" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T18" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U18" s="44"/>
       <c r="V18" s="44"/>
       <c r="W18" s="44"/>
@@ -12221,35 +12355,41 @@
       </c>
       <c r="B19" s="288"/>
       <c r="C19" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="288"/>
       <c r="E19" s="289" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F19" s="288"/>
       <c r="G19" s="290" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H19" s="291"/>
       <c r="I19" s="288"/>
       <c r="J19" s="290" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K19" s="288"/>
       <c r="L19" s="296" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="M19" s="291"/>
       <c r="N19" s="288"/>
       <c r="O19" s="293" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P19" s="291"/>
       <c r="Q19" s="288"/>
-      <c r="R19" s="294"/>
-      <c r="S19" s="294"/>
-      <c r="T19" s="295"/>
+      <c r="R19" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S19" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T19" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U19" s="44"/>
       <c r="V19" s="44"/>
       <c r="W19" s="44"/>
@@ -12263,35 +12403,41 @@
       </c>
       <c r="B20" s="288"/>
       <c r="C20" s="289" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="302"/>
       <c r="E20" s="289" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F20" s="302"/>
       <c r="G20" s="290" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H20" s="301"/>
       <c r="I20" s="300"/>
       <c r="J20" s="290" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K20" s="300"/>
       <c r="L20" s="293" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M20" s="298"/>
       <c r="N20" s="299"/>
       <c r="O20" s="293" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P20" s="298"/>
       <c r="Q20" s="299"/>
-      <c r="R20" s="294"/>
-      <c r="S20" s="294"/>
-      <c r="T20" s="295"/>
+      <c r="R20" s="303">
+        <v>45827</v>
+      </c>
+      <c r="S20" s="294" t="s">
+        <v>79</v>
+      </c>
+      <c r="T20" s="295" t="s">
+        <v>125</v>
+      </c>
       <c r="U20" s="44"/>
       <c r="V20" s="44"/>
       <c r="W20" s="44"/>
@@ -13756,16 +13902,16 @@
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
       <c r="A1" s="266" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="266"/>
       <c r="C1" s="267" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D1" s="268"/>
       <c r="E1" s="269"/>
       <c r="F1" s="270" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G1" s="271"/>
       <c r="H1" s="271"/>
@@ -13775,17 +13921,17 @@
       <c r="L1" s="271"/>
       <c r="M1" s="272"/>
       <c r="N1" s="58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O1" s="270" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P1" s="272"/>
       <c r="Q1" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="R1" s="270" t="s">
         <v>58</v>
-      </c>
-      <c r="R1" s="270" t="s">
-        <v>59</v>
       </c>
       <c r="S1" s="272"/>
     </row>
@@ -13793,12 +13939,12 @@
       <c r="A2" s="266"/>
       <c r="B2" s="266"/>
       <c r="C2" s="267" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" s="268"/>
       <c r="E2" s="269"/>
       <c r="F2" s="270" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G2" s="271"/>
       <c r="H2" s="271"/>
@@ -13808,14 +13954,14 @@
       <c r="L2" s="271"/>
       <c r="M2" s="272"/>
       <c r="N2" s="58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O2" s="273">
         <v>45827</v>
       </c>
       <c r="P2" s="274"/>
       <c r="Q2" s="60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R2" s="275"/>
       <c r="S2" s="276"/>
@@ -13843,20 +13989,20 @@
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
       <c r="A4" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="64" t="s">
+      <c r="C4" s="257" t="s">
         <v>64</v>
-      </c>
-      <c r="C4" s="257" t="s">
-        <v>65</v>
       </c>
       <c r="D4" s="258"/>
       <c r="E4" s="258"/>
       <c r="F4" s="258"/>
       <c r="G4" s="259"/>
       <c r="H4" s="257" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="258"/>
       <c r="J4" s="258"/>
@@ -13864,15 +14010,15 @@
       <c r="L4" s="258"/>
       <c r="M4" s="259"/>
       <c r="N4" s="257" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O4" s="258"/>
       <c r="P4" s="259"/>
       <c r="Q4" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4" s="257" t="s">
         <v>68</v>
-      </c>
-      <c r="R4" s="257" t="s">
-        <v>69</v>
       </c>
       <c r="S4" s="259"/>
     </row>
@@ -13881,17 +14027,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="260" t="s">
         <v>117</v>
-      </c>
-      <c r="C5" s="260" t="s">
-        <v>120</v>
       </c>
       <c r="D5" s="260"/>
       <c r="E5" s="260"/>
       <c r="F5" s="260"/>
       <c r="G5" s="260"/>
       <c r="H5" s="260" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I5" s="260"/>
       <c r="J5" s="260"/>
@@ -13899,11 +14045,13 @@
       <c r="L5" s="260"/>
       <c r="M5" s="260"/>
       <c r="N5" s="261" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O5" s="262"/>
       <c r="P5" s="263"/>
-      <c r="Q5" s="65"/>
+      <c r="Q5" s="304">
+        <v>45827</v>
+      </c>
       <c r="R5" s="264"/>
       <c r="S5" s="265"/>
     </row>
@@ -13912,17 +14060,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" s="260" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D6" s="260"/>
       <c r="E6" s="260"/>
       <c r="F6" s="260"/>
       <c r="G6" s="260"/>
       <c r="H6" s="260" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I6" s="260"/>
       <c r="J6" s="260"/>
@@ -13930,11 +14078,13 @@
       <c r="L6" s="260"/>
       <c r="M6" s="260"/>
       <c r="N6" s="261" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O6" s="262"/>
       <c r="P6" s="263"/>
-      <c r="Q6" s="69"/>
+      <c r="Q6" s="69">
+        <v>45827</v>
+      </c>
       <c r="R6" s="256"/>
       <c r="S6" s="256"/>
     </row>
@@ -15134,7 +15284,7 @@
     <row r="1" spans="1:53" ht="30" customHeight="1">
       <c r="A1" s="71"/>
       <c r="B1" s="72" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C1" s="73"/>
       <c r="D1" s="71"/>
@@ -15175,7 +15325,7 @@
       <c r="AM1" s="71"/>
       <c r="AN1" s="71"/>
       <c r="AO1" s="280" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AP1" s="280"/>
       <c r="AQ1" s="280"/>
@@ -15194,7 +15344,7 @@
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="4" spans="1:53" ht="18" customHeight="1">
       <c r="A4" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="78"/>
       <c r="C4" s="79"/>
@@ -15235,7 +15385,7 @@
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
       <c r="A5" s="277" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" s="278"/>
       <c r="C5" s="278"/>
@@ -15243,7 +15393,7 @@
       <c r="E5" s="278"/>
       <c r="F5" s="279"/>
       <c r="G5" s="283" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H5" s="284"/>
       <c r="I5" s="284"/>
@@ -15260,14 +15410,16 @@
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
       <c r="A6" s="277" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="278"/>
       <c r="C6" s="278"/>
       <c r="D6" s="278"/>
       <c r="E6" s="278"/>
       <c r="F6" s="279"/>
-      <c r="G6" s="286"/>
+      <c r="G6" s="286">
+        <v>1</v>
+      </c>
       <c r="H6" s="284"/>
       <c r="I6" s="284"/>
       <c r="J6" s="284"/>
@@ -15284,12 +15436,12 @@
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
       <c r="A8" s="78" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
       <c r="A9" s="277" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="278"/>
       <c r="C9" s="278"/>
@@ -19066,7 +19218,7 @@
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
       <c r="A103" s="277" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B103" s="278"/>
       <c r="C103" s="278"/>
@@ -19401,7 +19553,7 @@
       <c r="AK110" s="81"/>
       <c r="BA110" s="82"/>
     </row>
-    <row r="111" spans="1:53" ht="21.95" customHeight="1">
+    <row r="111" spans="1:53" ht="63" customHeight="1">
       <c r="A111" s="85"/>
       <c r="B111" s="86"/>
       <c r="C111" s="86"/>
@@ -19443,7 +19595,7 @@
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
       <c r="A112" s="277" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B112" s="278"/>
       <c r="C112" s="278"/>
@@ -19654,5 +19806,6 @@
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Documents/コメント削除機能設計書.xlsx
+++ b/Documents/コメント削除機能設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D60A8D-074C-4FE2-BCE2-2A5736FC8D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4DE3D7-5AC5-4336-8393-6E5E34CA17FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="8" xr2:uid="{73C913ED-0334-40C4-8D2F-5AD7FF49F493}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="9" xr2:uid="{73C913ED-0334-40C4-8D2F-5AD7FF49F493}"/>
   </bookViews>
   <sheets>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="テスト仕様書兼結果報告書" sheetId="5" r:id="rId7"/>
     <sheet name="JUnitテスト仕様書兼報告書" sheetId="7" r:id="rId8"/>
     <sheet name="カバレッジレポート" sheetId="8" r:id="rId9"/>
+    <sheet name="エビデンス" sheetId="11" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="範囲１" localSheetId="7">#REF!</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="137">
   <si>
     <t>ユースケース記述</t>
   </si>
@@ -813,13 +814,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>No.2のテストが成功している</t>
-    <rPh sb="9" eb="11">
-      <t>セイコウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>いいえボタンを押下する</t>
     <rPh sb="7" eb="9">
       <t>オウカ</t>
@@ -871,6 +865,66 @@
   <si>
     <t>deleteComment(int commentId)</t>
     <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>テストエビデンス</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>グループ名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>承認印</t>
+    <rPh sb="0" eb="3">
+      <t>ショウニンイン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>機能名称</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイショウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エビデンス</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -1061,7 +1115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="76">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -1950,6 +2004,123 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1969,7 +2140,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="305">
+  <cellXfs count="334">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2232,24 +2403,126 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="8" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="12" fillId="0" borderId="62" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2265,96 +2538,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2436,6 +2619,84 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2451,84 +2712,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2595,6 +2778,150 @@
     <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="29" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2613,112 +2940,82 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="58" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="59" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="64" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="56" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="57" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="59" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="57" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="66" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="66" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2727,78 +3024,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="66" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="57" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="58" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="59" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="62" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="64" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="56" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="57" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="59" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="57" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="57" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2829,58 +3054,91 @@
     <xf numFmtId="9" fontId="14" fillId="0" borderId="57" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="29" xfId="9" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="12" fillId="0" borderId="62" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3289,6 +3547,554 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>142876</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>90942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>571501</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CC66857-4E74-F6B6-B421-DD1D09858B05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1514476" y="1795917"/>
+          <a:ext cx="3819524" cy="2147434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>390698</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>569366</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{135386DB-ACA0-E86B-2DA2-E8CD02B2B413}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5514975" y="1809750"/>
+          <a:ext cx="3791123" cy="2131466"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>79617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1285875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76CC8888-6853-00B0-FF6C-95FF9849A6D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600200" y="7147167"/>
+          <a:ext cx="3771900" cy="2120658"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>376920</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>120165</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>544680</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>47580</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="8" name="インク 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBE3FBC9-CC4F-B87D-CE15-C9AF8DD0E5A0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1748520" y="7902090"/>
+            <a:ext cx="167760" cy="127440"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="インク 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBE3FBC9-CC4F-B87D-CE15-C9AF8DD0E5A0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1742400" y="7895970"/>
+              <a:ext cx="180000" cy="139680"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123310</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1302792</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B0FC862-0BA4-F37F-65D3-3AB60174DF92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5505450" y="7190860"/>
+          <a:ext cx="3724275" cy="2093882"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>371474</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>158008</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266699</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>507545</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B65DCF8-FFB6-0800-951D-07D22B2E66EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3114674" y="4387108"/>
+          <a:ext cx="4010025" cy="2254537"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>45128</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>292868</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>63787</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A007B671-F27B-477E-B922-0DB15A24006E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409699" y="12580028"/>
+          <a:ext cx="2997969" cy="1685534"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>476249</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>221850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>25158</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C55371F8-1C9E-40FF-A979-7ED224589A57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4591049" y="12518625"/>
+          <a:ext cx="3038475" cy="1708308"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>361950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>214882</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>2341016</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C661E1EA-A5B4-0561-C5AF-5150AB8686A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1495425" y="14563725"/>
+          <a:ext cx="3520057" cy="1979066"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>144932</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>485774</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>695325</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5300E8A-C872-51EC-DA44-6EFA9D87C980}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2888132" y="9658350"/>
+          <a:ext cx="4455642" cy="2505075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-06-20T01:26:07.472"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">37 353 24575,'40'-2'0,"67"-12"0,-42 4 0,-57 8 0,0 0 0,-1 0 0,1-1 0,0 0 0,-1 0 0,0-1 0,0 0 0,0 0 0,8-7 0,-6 5 0,0 0 0,1 0 0,0 1 0,10-4 0,-15 7 0,-1 0 0,0 0 0,0 0 0,0 0 0,0-1 0,0 0 0,-1 1 0,1-1 0,-1-1 0,1 1 0,-1 0 0,0-1 0,-1 0 0,1 0 0,-1 1 0,1-2 0,-1 1 0,0 0 0,1-5 0,0 0 0,-1 0 0,0 0 0,-1 0 0,1-1 0,-2 1 0,1 0 0,-2-1 0,-1-15 0,1 21 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 1 0,-1-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,-1-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,-1 1 0,1 0 0,0 0 0,-7-1 0,-14-2 0,0 0 0,0 2 0,-32 1 0,45 1 0,-21-1 0,12 0 0,1 0 0,-1 2 0,1 0 0,-1 1 0,-29 8 0,47-9 0,0 0 0,0 1 0,0-1 0,1 1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 1 0,-1-1 0,1 1 0,1-1 0,-1 1 0,0 0 0,0-1 0,1 1 0,0 0 0,0 0 0,-1 0 0,2 0 0,-1 1 0,0-1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,1 3 0,0 13 0,1-1 0,1 0 0,9 30 0,-7-26 0,1 10-43,-5-25-104,0-1 0,0 1 0,1-1 1,0 1-1,0-1 0,1 0 0,0 0 0,4 8 0,5 1-6679</inkml:trace>
+</inkml:ink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -3596,19 +4402,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="123" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="111"/>
-      <c r="F1" s="123" t="s">
+      <c r="E1" s="100"/>
+      <c r="F1" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="111"/>
+      <c r="G1" s="100"/>
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3620,190 +4426,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="117"/>
-      <c r="B2" s="118"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="124" t="s">
+      <c r="A2" s="111"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="125"/>
-      <c r="F2" s="124" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="125"/>
-      <c r="H2" s="128">
+      <c r="G2" s="119"/>
+      <c r="H2" s="122">
         <v>45827</v>
       </c>
-      <c r="I2" s="103" t="s">
+      <c r="I2" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="106"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="117"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="107"/>
+      <c r="A3" s="111"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="96"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="120"/>
-      <c r="B4" s="121"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="108"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="109" t="s">
+      <c r="A5" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="110"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="99"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="113"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="102"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="92"/>
-      <c r="D6" s="93" t="s">
+      <c r="B6" s="104"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="106" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="107"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="93" t="s">
+      <c r="B7" s="104"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="89"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="89"/>
-      <c r="J7" s="90"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="107"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="89"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="93" t="s">
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="89"/>
-      <c r="J8" s="90"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="107"/>
     </row>
     <row r="9" spans="1:10" ht="118.5" customHeight="1">
-      <c r="A9" s="99" t="s">
+      <c r="A9" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="126" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="88" t="s">
+      <c r="C9" s="105"/>
+      <c r="D9" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="89"/>
-      <c r="I9" s="89"/>
-      <c r="J9" s="90"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="107"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="100"/>
-      <c r="B10" s="102" t="s">
+      <c r="A10" s="124"/>
+      <c r="B10" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="92"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="90"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="106"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="107"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="101"/>
-      <c r="B11" s="102" t="s">
+      <c r="A11" s="125"/>
+      <c r="B11" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="92"/>
-      <c r="D11" s="88" t="s">
+      <c r="C11" s="105"/>
+      <c r="D11" s="127" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="89"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="89"/>
-      <c r="J11" s="90"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="107"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="91" t="s">
+      <c r="A12" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="89"/>
-      <c r="C12" s="92"/>
-      <c r="D12" s="93" t="s">
+      <c r="B12" s="104"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="106" t="s">
         <v>93</v>
       </c>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="90"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="107"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="94" t="s">
+      <c r="A13" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="95"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="98"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="132"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4794,6 +5600,21 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -4806,25 +5627,518 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{545875A3-B5F9-42B5-9582-EB2FE2CBAF24}">
+  <dimension ref="A1:O51"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A1" s="305" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="306"/>
+      <c r="C1" s="307"/>
+      <c r="D1" s="308" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="309"/>
+      <c r="F1" s="307"/>
+      <c r="G1" s="310" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" s="309"/>
+      <c r="I1" s="311" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" s="312"/>
+      <c r="K1" s="311" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="312"/>
+      <c r="M1" s="311" t="s">
+        <v>133</v>
+      </c>
+      <c r="N1" s="313"/>
+      <c r="O1" s="314"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="315"/>
+      <c r="B2" s="316"/>
+      <c r="C2" s="305" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="317"/>
+      <c r="E2" s="306"/>
+      <c r="F2" s="305" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="317"/>
+      <c r="H2" s="306"/>
+      <c r="I2" s="333">
+        <v>45828</v>
+      </c>
+      <c r="J2" s="306"/>
+      <c r="K2" s="305" t="s">
+        <v>79</v>
+      </c>
+      <c r="L2" s="306"/>
+      <c r="M2" s="305"/>
+      <c r="N2" s="306"/>
+      <c r="O2" s="318"/>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A3" s="319"/>
+      <c r="B3" s="320"/>
+      <c r="C3" s="319"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="319"/>
+      <c r="G3" s="321"/>
+      <c r="H3" s="320"/>
+      <c r="I3" s="319"/>
+      <c r="J3" s="320"/>
+      <c r="K3" s="319"/>
+      <c r="L3" s="320"/>
+      <c r="M3" s="319"/>
+      <c r="N3" s="320"/>
+      <c r="O3" s="318"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="305" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="306"/>
+      <c r="C4" s="322" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="323"/>
+      <c r="E4" s="323"/>
+      <c r="F4" s="323"/>
+      <c r="G4" s="323"/>
+      <c r="H4" s="323"/>
+      <c r="I4" s="323"/>
+      <c r="J4" s="323"/>
+      <c r="K4" s="323"/>
+      <c r="L4" s="323"/>
+      <c r="M4" s="323"/>
+      <c r="N4" s="324"/>
+      <c r="O4" s="318"/>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A5" s="319"/>
+      <c r="B5" s="320"/>
+      <c r="C5" s="325"/>
+      <c r="D5" s="326"/>
+      <c r="E5" s="326"/>
+      <c r="F5" s="326"/>
+      <c r="G5" s="326"/>
+      <c r="H5" s="326"/>
+      <c r="I5" s="326"/>
+      <c r="J5" s="326"/>
+      <c r="K5" s="326"/>
+      <c r="L5" s="326"/>
+      <c r="M5" s="326"/>
+      <c r="N5" s="327"/>
+      <c r="O5" s="318"/>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A6" s="311" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="312"/>
+      <c r="C6" s="311" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="313"/>
+      <c r="E6" s="313"/>
+      <c r="F6" s="313"/>
+      <c r="G6" s="313"/>
+      <c r="H6" s="313"/>
+      <c r="I6" s="313"/>
+      <c r="J6" s="313"/>
+      <c r="K6" s="313"/>
+      <c r="L6" s="313"/>
+      <c r="M6" s="313"/>
+      <c r="N6" s="312"/>
+      <c r="O6" s="318"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="305">
+        <v>1</v>
+      </c>
+      <c r="B7" s="306"/>
+      <c r="C7" s="328"/>
+      <c r="D7" s="328"/>
+      <c r="E7" s="328"/>
+      <c r="F7" s="328"/>
+      <c r="G7" s="328"/>
+      <c r="H7" s="328"/>
+      <c r="I7" s="328"/>
+      <c r="J7" s="328"/>
+      <c r="K7" s="328"/>
+      <c r="L7" s="328"/>
+      <c r="M7" s="328"/>
+      <c r="N7" s="328"/>
+      <c r="O7" s="318"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="315"/>
+      <c r="B8" s="316"/>
+      <c r="O8" s="318"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="315"/>
+      <c r="B9" s="316"/>
+      <c r="N9" s="329"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="315"/>
+      <c r="B10" s="316"/>
+      <c r="O10" s="318"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="315"/>
+      <c r="B11" s="316"/>
+      <c r="O11" s="318"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="315"/>
+      <c r="B12" s="316"/>
+      <c r="O12" s="318"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="315"/>
+      <c r="B13" s="316"/>
+      <c r="O13" s="318"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="315"/>
+      <c r="B14" s="316"/>
+      <c r="O14" s="318"/>
+    </row>
+    <row r="15" spans="1:15" ht="67.5" customHeight="1" thickBot="1">
+      <c r="A15" s="319"/>
+      <c r="B15" s="320"/>
+      <c r="C15" s="330"/>
+      <c r="D15" s="330"/>
+      <c r="E15" s="330"/>
+      <c r="F15" s="330"/>
+      <c r="G15" s="330"/>
+      <c r="H15" s="330"/>
+      <c r="I15" s="330"/>
+      <c r="J15" s="330"/>
+      <c r="K15" s="330"/>
+      <c r="L15" s="330"/>
+      <c r="M15" s="330"/>
+      <c r="N15" s="331"/>
+      <c r="O15" s="318"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="305">
+        <v>2</v>
+      </c>
+      <c r="B16" s="306"/>
+      <c r="C16" s="328"/>
+      <c r="D16" s="328"/>
+      <c r="E16" s="328"/>
+      <c r="F16" s="328"/>
+      <c r="G16" s="328"/>
+      <c r="H16" s="328"/>
+      <c r="I16" s="328"/>
+      <c r="J16" s="328"/>
+      <c r="K16" s="328"/>
+      <c r="L16" s="328"/>
+      <c r="M16" s="328"/>
+      <c r="N16" s="329"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="315"/>
+      <c r="B17" s="316"/>
+      <c r="N17" s="329"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="315"/>
+      <c r="B18" s="316"/>
+      <c r="N18" s="329"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="315"/>
+      <c r="B19" s="316"/>
+      <c r="N19" s="329"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="315"/>
+      <c r="B20" s="316"/>
+      <c r="N20" s="329"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="315"/>
+      <c r="B21" s="316"/>
+      <c r="N21" s="329"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="315"/>
+      <c r="B22" s="316"/>
+      <c r="N22" s="329"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="315"/>
+      <c r="B23" s="316"/>
+      <c r="N23" s="329"/>
+    </row>
+    <row r="24" spans="1:14" ht="54.75" customHeight="1" thickBot="1">
+      <c r="A24" s="319"/>
+      <c r="B24" s="320"/>
+      <c r="C24" s="330"/>
+      <c r="D24" s="330"/>
+      <c r="E24" s="330"/>
+      <c r="F24" s="330"/>
+      <c r="G24" s="330"/>
+      <c r="H24" s="330"/>
+      <c r="I24" s="330"/>
+      <c r="J24" s="330"/>
+      <c r="K24" s="330"/>
+      <c r="L24" s="330"/>
+      <c r="M24" s="330"/>
+      <c r="N24" s="331"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="305">
+        <v>3</v>
+      </c>
+      <c r="B25" s="306"/>
+      <c r="C25" s="328"/>
+      <c r="D25" s="328"/>
+      <c r="E25" s="328"/>
+      <c r="F25" s="328"/>
+      <c r="G25" s="328"/>
+      <c r="H25" s="328"/>
+      <c r="I25" s="328"/>
+      <c r="J25" s="328"/>
+      <c r="K25" s="328"/>
+      <c r="L25" s="328"/>
+      <c r="M25" s="328"/>
+      <c r="N25" s="329"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="315"/>
+      <c r="B26" s="316"/>
+      <c r="N26" s="329"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="315"/>
+      <c r="B27" s="316"/>
+      <c r="N27" s="329"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="315"/>
+      <c r="B28" s="316"/>
+      <c r="N28" s="329"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A29" s="315"/>
+      <c r="B29" s="316"/>
+      <c r="N29" s="329"/>
+    </row>
+    <row r="30" spans="1:14" ht="19.5" hidden="1" thickBot="1">
+      <c r="A30" s="315"/>
+      <c r="B30" s="316"/>
+      <c r="N30" s="329"/>
+    </row>
+    <row r="31" spans="1:14" ht="19.5" hidden="1" thickBot="1">
+      <c r="A31" s="315"/>
+      <c r="B31" s="316"/>
+      <c r="N31" s="329"/>
+    </row>
+    <row r="32" spans="1:14" ht="19.5" hidden="1" thickBot="1">
+      <c r="A32" s="315"/>
+      <c r="B32" s="316"/>
+      <c r="N32" s="329"/>
+    </row>
+    <row r="33" spans="1:14" ht="124.5" customHeight="1" thickBot="1">
+      <c r="A33" s="319"/>
+      <c r="B33" s="320"/>
+      <c r="C33" s="330"/>
+      <c r="D33" s="330"/>
+      <c r="E33" s="330"/>
+      <c r="F33" s="330"/>
+      <c r="G33" s="330"/>
+      <c r="H33" s="330"/>
+      <c r="I33" s="330"/>
+      <c r="J33" s="330"/>
+      <c r="K33" s="330"/>
+      <c r="L33" s="330"/>
+      <c r="N33" s="329"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="305">
+        <v>4</v>
+      </c>
+      <c r="B34" s="306"/>
+      <c r="C34" s="328"/>
+      <c r="D34" s="328"/>
+      <c r="E34" s="328"/>
+      <c r="F34" s="328"/>
+      <c r="G34" s="328"/>
+      <c r="H34" s="328"/>
+      <c r="I34" s="328"/>
+      <c r="J34" s="328"/>
+      <c r="K34" s="328"/>
+      <c r="L34" s="328"/>
+      <c r="M34" s="328"/>
+      <c r="N34" s="332"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="315"/>
+      <c r="B35" s="316"/>
+      <c r="N35" s="329"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="315"/>
+      <c r="B36" s="316"/>
+      <c r="N36" s="329"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="315"/>
+      <c r="B37" s="316"/>
+      <c r="N37" s="329"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="315"/>
+      <c r="B38" s="316"/>
+      <c r="N38" s="329"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="315"/>
+      <c r="B39" s="316"/>
+      <c r="N39" s="329"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="315"/>
+      <c r="B40" s="316"/>
+      <c r="N40" s="329"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="315"/>
+      <c r="B41" s="316"/>
+      <c r="N41" s="329"/>
+    </row>
+    <row r="42" spans="1:14" ht="65.25" customHeight="1" thickBot="1">
+      <c r="A42" s="319"/>
+      <c r="B42" s="320"/>
+      <c r="C42" s="330"/>
+      <c r="D42" s="330"/>
+      <c r="E42" s="330"/>
+      <c r="F42" s="330"/>
+      <c r="G42" s="330"/>
+      <c r="H42" s="330"/>
+      <c r="I42" s="330"/>
+      <c r="J42" s="330"/>
+      <c r="K42" s="330"/>
+      <c r="L42" s="330"/>
+      <c r="M42" s="330"/>
+      <c r="N42" s="331"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="305">
+        <v>5</v>
+      </c>
+      <c r="B43" s="306"/>
+      <c r="C43" s="328"/>
+      <c r="D43" s="328"/>
+      <c r="E43" s="328"/>
+      <c r="F43" s="328"/>
+      <c r="G43" s="328"/>
+      <c r="H43" s="328"/>
+      <c r="I43" s="328"/>
+      <c r="J43" s="328"/>
+      <c r="K43" s="328"/>
+      <c r="L43" s="328"/>
+      <c r="M43" s="328"/>
+      <c r="N43" s="332"/>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="315"/>
+      <c r="B44" s="316"/>
+      <c r="N44" s="329"/>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="315"/>
+      <c r="B45" s="316"/>
+      <c r="N45" s="329"/>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="315"/>
+      <c r="B46" s="316"/>
+      <c r="N46" s="329"/>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="315"/>
+      <c r="B47" s="316"/>
+      <c r="N47" s="329"/>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="315"/>
+      <c r="B48" s="316"/>
+      <c r="N48" s="329"/>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="315"/>
+      <c r="B49" s="316"/>
+      <c r="N49" s="329"/>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="315"/>
+      <c r="B50" s="316"/>
+      <c r="N50" s="329"/>
+    </row>
+    <row r="51" spans="1:14" ht="218.25" customHeight="1" thickBot="1">
+      <c r="A51" s="319"/>
+      <c r="B51" s="320"/>
+      <c r="C51" s="330"/>
+      <c r="D51" s="330"/>
+      <c r="E51" s="330"/>
+      <c r="F51" s="330"/>
+      <c r="G51" s="330"/>
+      <c r="H51" s="330"/>
+      <c r="I51" s="330"/>
+      <c r="J51" s="330"/>
+      <c r="K51" s="330"/>
+      <c r="L51" s="330"/>
+      <c r="M51" s="330"/>
+      <c r="N51" s="331"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A25:B33"/>
+    <mergeCell ref="A34:B42"/>
+    <mergeCell ref="A43:B51"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="A7:B15"/>
+    <mergeCell ref="A16:B24"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="C2:E3"/>
+    <mergeCell ref="F2:H3"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="M2:N3"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4840,19 +6154,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="144" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="145"/>
-      <c r="F1" s="144" t="s">
+      <c r="E1" s="149"/>
+      <c r="F1" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="145"/>
+      <c r="G1" s="149"/>
       <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
@@ -4864,48 +6178,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="138"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="146" t="s">
+      <c r="A2" s="142"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="150" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="147"/>
-      <c r="F2" s="146" t="s">
+      <c r="E2" s="151"/>
+      <c r="F2" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="147"/>
-      <c r="H2" s="150">
+      <c r="G2" s="151"/>
+      <c r="H2" s="154">
         <v>45827</v>
       </c>
-      <c r="I2" s="129" t="s">
+      <c r="I2" s="133" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="132"/>
+      <c r="J2" s="136"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="138"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="133"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="152"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="137"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="141"/>
-      <c r="B4" s="142"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="134"/>
+      <c r="A4" s="145"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="138"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6266,19 +7580,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="176" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="182" t="s">
+      <c r="B1" s="177"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="169"/>
-      <c r="F1" s="182" t="s">
+      <c r="E1" s="166"/>
+      <c r="F1" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="169"/>
+      <c r="G1" s="166"/>
       <c r="H1" s="48" t="s">
         <v>3</v>
       </c>
@@ -6290,190 +7604,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="175"/>
-      <c r="B2" s="176"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="183" t="s">
+      <c r="A2" s="173"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="184"/>
-      <c r="F2" s="183" t="s">
+      <c r="E2" s="182"/>
+      <c r="F2" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="184"/>
-      <c r="H2" s="186">
+      <c r="G2" s="182"/>
+      <c r="H2" s="184">
         <v>45827</v>
       </c>
-      <c r="I2" s="163" t="s">
+      <c r="I2" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="165"/>
+      <c r="J2" s="162"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="175"/>
-      <c r="B3" s="176"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="181"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="166"/>
+      <c r="A3" s="173"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="163"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="175"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="181"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="181"/>
-      <c r="H4" s="164"/>
-      <c r="I4" s="164"/>
-      <c r="J4" s="166"/>
+      <c r="A4" s="173"/>
+      <c r="B4" s="174"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="163"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="164" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="170" t="s">
+      <c r="B5" s="165"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="167" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
-      <c r="J5" s="171"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="165"/>
+      <c r="G5" s="165"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="168"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="161" t="s">
+      <c r="A6" s="169" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="152"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="156"/>
+      <c r="I6" s="156"/>
+      <c r="J6" s="159"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="172"/>
-      <c r="B7" s="173"/>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="173"/>
-      <c r="H7" s="173"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="174"/>
+      <c r="A7" s="170"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="171"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="171"/>
+      <c r="F7" s="171"/>
+      <c r="G7" s="171"/>
+      <c r="H7" s="171"/>
+      <c r="I7" s="171"/>
+      <c r="J7" s="172"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="175"/>
-      <c r="B8" s="176"/>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="176"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="177"/>
+      <c r="A8" s="173"/>
+      <c r="B8" s="174"/>
+      <c r="C8" s="174"/>
+      <c r="D8" s="174"/>
+      <c r="E8" s="174"/>
+      <c r="F8" s="174"/>
+      <c r="G8" s="174"/>
+      <c r="H8" s="174"/>
+      <c r="I8" s="174"/>
+      <c r="J8" s="175"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="175"/>
-      <c r="B9" s="176"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="176"/>
-      <c r="J9" s="177"/>
+      <c r="A9" s="173"/>
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="174"/>
+      <c r="E9" s="174"/>
+      <c r="F9" s="174"/>
+      <c r="G9" s="174"/>
+      <c r="H9" s="174"/>
+      <c r="I9" s="174"/>
+      <c r="J9" s="175"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="175"/>
-      <c r="B10" s="176"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="176"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="177"/>
+      <c r="A10" s="173"/>
+      <c r="B10" s="174"/>
+      <c r="C10" s="174"/>
+      <c r="D10" s="174"/>
+      <c r="E10" s="174"/>
+      <c r="F10" s="174"/>
+      <c r="G10" s="174"/>
+      <c r="H10" s="174"/>
+      <c r="I10" s="174"/>
+      <c r="J10" s="175"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="175"/>
-      <c r="B11" s="176"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="177"/>
+      <c r="A11" s="173"/>
+      <c r="B11" s="174"/>
+      <c r="C11" s="174"/>
+      <c r="D11" s="174"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="174"/>
+      <c r="G11" s="174"/>
+      <c r="H11" s="174"/>
+      <c r="I11" s="174"/>
+      <c r="J11" s="175"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="175"/>
-      <c r="B12" s="176"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="177"/>
+      <c r="A12" s="173"/>
+      <c r="B12" s="174"/>
+      <c r="C12" s="174"/>
+      <c r="D12" s="174"/>
+      <c r="E12" s="174"/>
+      <c r="F12" s="174"/>
+      <c r="G12" s="174"/>
+      <c r="H12" s="174"/>
+      <c r="I12" s="174"/>
+      <c r="J12" s="175"/>
     </row>
     <row r="13" spans="1:10" ht="97.5" customHeight="1">
-      <c r="A13" s="175"/>
-      <c r="B13" s="176"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="176"/>
-      <c r="H13" s="176"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="177"/>
+      <c r="A13" s="173"/>
+      <c r="B13" s="174"/>
+      <c r="C13" s="174"/>
+      <c r="D13" s="174"/>
+      <c r="E13" s="174"/>
+      <c r="F13" s="174"/>
+      <c r="G13" s="174"/>
+      <c r="H13" s="174"/>
+      <c r="I13" s="174"/>
+      <c r="J13" s="175"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="169" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="152"/>
-      <c r="H14" s="152"/>
-      <c r="I14" s="152"/>
-      <c r="J14" s="155"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="156"/>
+      <c r="G14" s="156"/>
+      <c r="H14" s="156"/>
+      <c r="I14" s="156"/>
+      <c r="J14" s="159"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="161" t="s">
+      <c r="A15" s="169" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="152"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="154" t="s">
+      <c r="B15" s="156"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="158" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="152"/>
-      <c r="F15" s="152"/>
-      <c r="G15" s="152"/>
-      <c r="H15" s="153"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="157"/>
       <c r="I15" s="52" t="s">
         <v>48</v>
       </c>
@@ -6482,11 +7796,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="161" t="s">
+      <c r="A16" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="152"/>
-      <c r="C16" s="153"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="157"/>
       <c r="D16" s="52" t="s">
         <v>50</v>
       </c>
@@ -6499,18 +7813,18 @@
       <c r="G16" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="162" t="s">
+      <c r="H16" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="152"/>
-      <c r="J16" s="155"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="159"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="151">
+      <c r="A17" s="155">
         <v>1</v>
       </c>
-      <c r="B17" s="152"/>
-      <c r="C17" s="153"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="157"/>
       <c r="D17" s="54" t="s">
         <v>83</v>
       </c>
@@ -6523,16 +7837,16 @@
       <c r="G17" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="154"/>
-      <c r="I17" s="152"/>
-      <c r="J17" s="155"/>
+      <c r="H17" s="158"/>
+      <c r="I17" s="156"/>
+      <c r="J17" s="159"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="151">
+      <c r="A18" s="155">
         <v>2</v>
       </c>
-      <c r="B18" s="152"/>
-      <c r="C18" s="153"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="157"/>
       <c r="D18" s="54" t="s">
         <v>84</v>
       </c>
@@ -6543,69 +7857,69 @@
       <c r="G18" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="H18" s="154"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="155"/>
+      <c r="H18" s="158"/>
+      <c r="I18" s="156"/>
+      <c r="J18" s="159"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="151"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="153"/>
+      <c r="A19" s="155"/>
+      <c r="B19" s="156"/>
+      <c r="C19" s="157"/>
       <c r="D19" s="54"/>
       <c r="E19" s="54"/>
       <c r="F19" s="55"/>
       <c r="G19" s="55"/>
-      <c r="H19" s="154"/>
-      <c r="I19" s="152"/>
-      <c r="J19" s="155"/>
+      <c r="H19" s="158"/>
+      <c r="I19" s="156"/>
+      <c r="J19" s="159"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="151"/>
-      <c r="B20" s="152"/>
-      <c r="C20" s="153"/>
+      <c r="A20" s="155"/>
+      <c r="B20" s="156"/>
+      <c r="C20" s="157"/>
       <c r="D20" s="54"/>
       <c r="E20" s="54"/>
       <c r="F20" s="55"/>
       <c r="G20" s="55"/>
-      <c r="H20" s="154"/>
-      <c r="I20" s="152"/>
-      <c r="J20" s="155"/>
+      <c r="H20" s="158"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="159"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="152"/>
-      <c r="C21" s="153"/>
+      <c r="A21" s="155"/>
+      <c r="B21" s="156"/>
+      <c r="C21" s="157"/>
       <c r="D21" s="54"/>
       <c r="E21" s="54"/>
       <c r="F21" s="55"/>
       <c r="G21" s="55"/>
-      <c r="H21" s="154"/>
-      <c r="I21" s="152"/>
-      <c r="J21" s="155"/>
+      <c r="H21" s="158"/>
+      <c r="I21" s="156"/>
+      <c r="J21" s="159"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="151"/>
-      <c r="B22" s="152"/>
-      <c r="C22" s="153"/>
+      <c r="A22" s="155"/>
+      <c r="B22" s="156"/>
+      <c r="C22" s="157"/>
       <c r="D22" s="54"/>
       <c r="E22" s="54"/>
       <c r="F22" s="55"/>
       <c r="G22" s="55"/>
-      <c r="H22" s="154"/>
-      <c r="I22" s="152"/>
-      <c r="J22" s="155"/>
+      <c r="H22" s="158"/>
+      <c r="I22" s="156"/>
+      <c r="J22" s="159"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="157"/>
-      <c r="C23" s="158"/>
+      <c r="A23" s="186"/>
+      <c r="B23" s="187"/>
+      <c r="C23" s="188"/>
       <c r="D23" s="56"/>
       <c r="E23" s="56"/>
       <c r="F23" s="57"/>
       <c r="G23" s="57"/>
-      <c r="H23" s="159"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="160"/>
+      <c r="H23" s="189"/>
+      <c r="I23" s="187"/>
+      <c r="J23" s="190"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7586,6 +8900,21 @@
     <row r="1000" s="51" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -7602,21 +8931,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -7641,19 +8955,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="176" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="182" t="s">
+      <c r="B1" s="177"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="169"/>
-      <c r="F1" s="182" t="s">
+      <c r="E1" s="166"/>
+      <c r="F1" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="169"/>
+      <c r="G1" s="166"/>
       <c r="H1" s="48" t="s">
         <v>3</v>
       </c>
@@ -7665,201 +8979,201 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="175"/>
-      <c r="B2" s="176"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="183" t="s">
+      <c r="A2" s="173"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="184"/>
-      <c r="F2" s="183" t="s">
+      <c r="E2" s="182"/>
+      <c r="F2" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="184"/>
-      <c r="H2" s="186">
+      <c r="G2" s="182"/>
+      <c r="H2" s="184">
         <v>45827</v>
       </c>
-      <c r="I2" s="163" t="s">
+      <c r="I2" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="165"/>
+      <c r="J2" s="162"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="175"/>
-      <c r="B3" s="176"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="181"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="166"/>
+      <c r="A3" s="173"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="163"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="175"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="181"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="181"/>
-      <c r="H4" s="164"/>
-      <c r="I4" s="164"/>
-      <c r="J4" s="166"/>
+      <c r="A4" s="173"/>
+      <c r="B4" s="174"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="163"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="164" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="170" t="s">
+      <c r="B5" s="165"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="167" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
-      <c r="J5" s="171"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="165"/>
+      <c r="G5" s="165"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="168"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="161" t="s">
+      <c r="A6" s="169" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="152"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="156"/>
+      <c r="I6" s="156"/>
+      <c r="J6" s="159"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="172"/>
-      <c r="B7" s="173"/>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="173"/>
-      <c r="H7" s="173"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="174"/>
+      <c r="A7" s="170"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="171"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="171"/>
+      <c r="F7" s="171"/>
+      <c r="G7" s="171"/>
+      <c r="H7" s="171"/>
+      <c r="I7" s="171"/>
+      <c r="J7" s="172"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="175"/>
-      <c r="B8" s="176"/>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="176"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="177"/>
+      <c r="A8" s="173"/>
+      <c r="B8" s="174"/>
+      <c r="C8" s="174"/>
+      <c r="D8" s="174"/>
+      <c r="E8" s="174"/>
+      <c r="F8" s="174"/>
+      <c r="G8" s="174"/>
+      <c r="H8" s="174"/>
+      <c r="I8" s="174"/>
+      <c r="J8" s="175"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="175"/>
-      <c r="B9" s="176"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="176"/>
-      <c r="J9" s="177"/>
+      <c r="A9" s="173"/>
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="174"/>
+      <c r="E9" s="174"/>
+      <c r="F9" s="174"/>
+      <c r="G9" s="174"/>
+      <c r="H9" s="174"/>
+      <c r="I9" s="174"/>
+      <c r="J9" s="175"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="175"/>
-      <c r="B10" s="176"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="176"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="177"/>
+      <c r="A10" s="173"/>
+      <c r="B10" s="174"/>
+      <c r="C10" s="174"/>
+      <c r="D10" s="174"/>
+      <c r="E10" s="174"/>
+      <c r="F10" s="174"/>
+      <c r="G10" s="174"/>
+      <c r="H10" s="174"/>
+      <c r="I10" s="174"/>
+      <c r="J10" s="175"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="175"/>
-      <c r="B11" s="176"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="177"/>
+      <c r="A11" s="173"/>
+      <c r="B11" s="174"/>
+      <c r="C11" s="174"/>
+      <c r="D11" s="174"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="174"/>
+      <c r="G11" s="174"/>
+      <c r="H11" s="174"/>
+      <c r="I11" s="174"/>
+      <c r="J11" s="175"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="175"/>
-      <c r="B12" s="176"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="177"/>
+      <c r="A12" s="173"/>
+      <c r="B12" s="174"/>
+      <c r="C12" s="174"/>
+      <c r="D12" s="174"/>
+      <c r="E12" s="174"/>
+      <c r="F12" s="174"/>
+      <c r="G12" s="174"/>
+      <c r="H12" s="174"/>
+      <c r="I12" s="174"/>
+      <c r="J12" s="175"/>
     </row>
     <row r="13" spans="1:10" ht="97.5" customHeight="1">
-      <c r="A13" s="175"/>
-      <c r="B13" s="176"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="176"/>
-      <c r="H13" s="176"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="177"/>
+      <c r="A13" s="173"/>
+      <c r="B13" s="174"/>
+      <c r="C13" s="174"/>
+      <c r="D13" s="174"/>
+      <c r="E13" s="174"/>
+      <c r="F13" s="174"/>
+      <c r="G13" s="174"/>
+      <c r="H13" s="174"/>
+      <c r="I13" s="174"/>
+      <c r="J13" s="175"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="169" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="152"/>
-      <c r="H14" s="152"/>
-      <c r="I14" s="152"/>
-      <c r="J14" s="155"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="156"/>
+      <c r="G14" s="156"/>
+      <c r="H14" s="156"/>
+      <c r="I14" s="156"/>
+      <c r="J14" s="159"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="161" t="s">
+      <c r="A15" s="169" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="152"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="154" t="s">
+      <c r="B15" s="156"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="158" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="152"/>
-      <c r="F15" s="152"/>
-      <c r="G15" s="152"/>
-      <c r="H15" s="153"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="157"/>
       <c r="I15" s="52" t="s">
         <v>48</v>
       </c>
       <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="161" t="s">
+      <c r="A16" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="152"/>
-      <c r="C16" s="153"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="157"/>
       <c r="D16" s="52" t="s">
         <v>50</v>
       </c>
@@ -7872,18 +9186,18 @@
       <c r="G16" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="162" t="s">
+      <c r="H16" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="152"/>
-      <c r="J16" s="155"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="159"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="151">
+      <c r="A17" s="155">
         <v>1</v>
       </c>
-      <c r="B17" s="152"/>
-      <c r="C17" s="153"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="157"/>
       <c r="D17" s="54" t="s">
         <v>97</v>
       </c>
@@ -7896,81 +9210,81 @@
       <c r="G17" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="H17" s="154"/>
-      <c r="I17" s="152"/>
-      <c r="J17" s="155"/>
+      <c r="H17" s="158"/>
+      <c r="I17" s="156"/>
+      <c r="J17" s="159"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="151"/>
-      <c r="B18" s="152"/>
-      <c r="C18" s="153"/>
+      <c r="A18" s="155"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="157"/>
       <c r="D18" s="54"/>
       <c r="E18" s="54"/>
       <c r="F18" s="55"/>
       <c r="G18" s="55"/>
-      <c r="H18" s="154"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="155"/>
+      <c r="H18" s="158"/>
+      <c r="I18" s="156"/>
+      <c r="J18" s="159"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="151"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="153"/>
+      <c r="A19" s="155"/>
+      <c r="B19" s="156"/>
+      <c r="C19" s="157"/>
       <c r="D19" s="54"/>
       <c r="E19" s="54"/>
       <c r="F19" s="55"/>
       <c r="G19" s="55"/>
-      <c r="H19" s="154"/>
-      <c r="I19" s="152"/>
-      <c r="J19" s="155"/>
+      <c r="H19" s="158"/>
+      <c r="I19" s="156"/>
+      <c r="J19" s="159"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="151"/>
-      <c r="B20" s="152"/>
-      <c r="C20" s="153"/>
+      <c r="A20" s="155"/>
+      <c r="B20" s="156"/>
+      <c r="C20" s="157"/>
       <c r="D20" s="54"/>
       <c r="E20" s="54"/>
       <c r="F20" s="55"/>
       <c r="G20" s="55"/>
-      <c r="H20" s="154"/>
-      <c r="I20" s="152"/>
-      <c r="J20" s="155"/>
+      <c r="H20" s="158"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="159"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="152"/>
-      <c r="C21" s="153"/>
+      <c r="A21" s="155"/>
+      <c r="B21" s="156"/>
+      <c r="C21" s="157"/>
       <c r="D21" s="54"/>
       <c r="E21" s="54"/>
       <c r="F21" s="55"/>
       <c r="G21" s="55"/>
-      <c r="H21" s="154"/>
-      <c r="I21" s="152"/>
-      <c r="J21" s="155"/>
+      <c r="H21" s="158"/>
+      <c r="I21" s="156"/>
+      <c r="J21" s="159"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="151"/>
-      <c r="B22" s="152"/>
-      <c r="C22" s="153"/>
+      <c r="A22" s="155"/>
+      <c r="B22" s="156"/>
+      <c r="C22" s="157"/>
       <c r="D22" s="54"/>
       <c r="E22" s="54"/>
       <c r="F22" s="55"/>
       <c r="G22" s="55"/>
-      <c r="H22" s="154"/>
-      <c r="I22" s="152"/>
-      <c r="J22" s="155"/>
+      <c r="H22" s="158"/>
+      <c r="I22" s="156"/>
+      <c r="J22" s="159"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="157"/>
-      <c r="C23" s="158"/>
+      <c r="A23" s="186"/>
+      <c r="B23" s="187"/>
+      <c r="C23" s="188"/>
       <c r="D23" s="56"/>
       <c r="E23" s="56"/>
       <c r="F23" s="57"/>
       <c r="G23" s="57"/>
-      <c r="H23" s="159"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="160"/>
+      <c r="H23" s="189"/>
+      <c r="I23" s="187"/>
+      <c r="J23" s="190"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8951,6 +10265,21 @@
     <row r="1000" s="51" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -8967,21 +10296,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9005,19 +10319,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="176" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="182" t="s">
+      <c r="B1" s="177"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="169"/>
-      <c r="F1" s="182" t="s">
+      <c r="E1" s="166"/>
+      <c r="F1" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="169"/>
+      <c r="G1" s="166"/>
       <c r="H1" s="48" t="s">
         <v>3</v>
       </c>
@@ -9029,190 +10343,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="175"/>
-      <c r="B2" s="176"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="183" t="s">
+      <c r="A2" s="173"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="184"/>
-      <c r="F2" s="183" t="s">
+      <c r="E2" s="182"/>
+      <c r="F2" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="184"/>
-      <c r="H2" s="186">
+      <c r="G2" s="182"/>
+      <c r="H2" s="184">
         <v>45827</v>
       </c>
-      <c r="I2" s="163" t="s">
+      <c r="I2" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="165"/>
+      <c r="J2" s="162"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="175"/>
-      <c r="B3" s="176"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="181"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="166"/>
+      <c r="A3" s="173"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="163"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="175"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="181"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="181"/>
-      <c r="H4" s="164"/>
-      <c r="I4" s="164"/>
-      <c r="J4" s="166"/>
+      <c r="A4" s="173"/>
+      <c r="B4" s="174"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="163"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="164" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="170" t="s">
+      <c r="B5" s="165"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="167" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
-      <c r="J5" s="171"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="165"/>
+      <c r="G5" s="165"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="168"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="161" t="s">
+      <c r="A6" s="169" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="152"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="155"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="156"/>
+      <c r="I6" s="156"/>
+      <c r="J6" s="159"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="172"/>
-      <c r="B7" s="173"/>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="173"/>
-      <c r="H7" s="173"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="174"/>
+      <c r="A7" s="170"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="171"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="171"/>
+      <c r="F7" s="171"/>
+      <c r="G7" s="171"/>
+      <c r="H7" s="171"/>
+      <c r="I7" s="171"/>
+      <c r="J7" s="172"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="175"/>
-      <c r="B8" s="176"/>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="176"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="177"/>
+      <c r="A8" s="173"/>
+      <c r="B8" s="174"/>
+      <c r="C8" s="174"/>
+      <c r="D8" s="174"/>
+      <c r="E8" s="174"/>
+      <c r="F8" s="174"/>
+      <c r="G8" s="174"/>
+      <c r="H8" s="174"/>
+      <c r="I8" s="174"/>
+      <c r="J8" s="175"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="175"/>
-      <c r="B9" s="176"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="176"/>
-      <c r="J9" s="177"/>
+      <c r="A9" s="173"/>
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="174"/>
+      <c r="E9" s="174"/>
+      <c r="F9" s="174"/>
+      <c r="G9" s="174"/>
+      <c r="H9" s="174"/>
+      <c r="I9" s="174"/>
+      <c r="J9" s="175"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="175"/>
-      <c r="B10" s="176"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="176"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="177"/>
+      <c r="A10" s="173"/>
+      <c r="B10" s="174"/>
+      <c r="C10" s="174"/>
+      <c r="D10" s="174"/>
+      <c r="E10" s="174"/>
+      <c r="F10" s="174"/>
+      <c r="G10" s="174"/>
+      <c r="H10" s="174"/>
+      <c r="I10" s="174"/>
+      <c r="J10" s="175"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="175"/>
-      <c r="B11" s="176"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="177"/>
+      <c r="A11" s="173"/>
+      <c r="B11" s="174"/>
+      <c r="C11" s="174"/>
+      <c r="D11" s="174"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="174"/>
+      <c r="G11" s="174"/>
+      <c r="H11" s="174"/>
+      <c r="I11" s="174"/>
+      <c r="J11" s="175"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="175"/>
-      <c r="B12" s="176"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="177"/>
+      <c r="A12" s="173"/>
+      <c r="B12" s="174"/>
+      <c r="C12" s="174"/>
+      <c r="D12" s="174"/>
+      <c r="E12" s="174"/>
+      <c r="F12" s="174"/>
+      <c r="G12" s="174"/>
+      <c r="H12" s="174"/>
+      <c r="I12" s="174"/>
+      <c r="J12" s="175"/>
     </row>
     <row r="13" spans="1:10" ht="97.5" customHeight="1">
-      <c r="A13" s="175"/>
-      <c r="B13" s="176"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="176"/>
-      <c r="H13" s="176"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="177"/>
+      <c r="A13" s="173"/>
+      <c r="B13" s="174"/>
+      <c r="C13" s="174"/>
+      <c r="D13" s="174"/>
+      <c r="E13" s="174"/>
+      <c r="F13" s="174"/>
+      <c r="G13" s="174"/>
+      <c r="H13" s="174"/>
+      <c r="I13" s="174"/>
+      <c r="J13" s="175"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="169" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="152"/>
-      <c r="H14" s="152"/>
-      <c r="I14" s="152"/>
-      <c r="J14" s="155"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="156"/>
+      <c r="G14" s="156"/>
+      <c r="H14" s="156"/>
+      <c r="I14" s="156"/>
+      <c r="J14" s="159"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="161" t="s">
+      <c r="A15" s="169" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="152"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="154" t="s">
+      <c r="B15" s="156"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="158" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="152"/>
-      <c r="F15" s="152"/>
-      <c r="G15" s="152"/>
-      <c r="H15" s="153"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="157"/>
       <c r="I15" s="52" t="s">
         <v>48</v>
       </c>
@@ -9221,11 +10535,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="161" t="s">
+      <c r="A16" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="152"/>
-      <c r="C16" s="153"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="157"/>
       <c r="D16" s="52" t="s">
         <v>50</v>
       </c>
@@ -9238,18 +10552,18 @@
       <c r="G16" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="162" t="s">
+      <c r="H16" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="152"/>
-      <c r="J16" s="155"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="159"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="151">
+      <c r="A17" s="155">
         <v>1</v>
       </c>
-      <c r="B17" s="152"/>
-      <c r="C17" s="153"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="157"/>
       <c r="D17" s="54" t="s">
         <v>97</v>
       </c>
@@ -9262,81 +10576,81 @@
       <c r="G17" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="H17" s="154"/>
-      <c r="I17" s="152"/>
-      <c r="J17" s="155"/>
+      <c r="H17" s="158"/>
+      <c r="I17" s="156"/>
+      <c r="J17" s="159"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="151"/>
-      <c r="B18" s="152"/>
-      <c r="C18" s="153"/>
+      <c r="A18" s="155"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="157"/>
       <c r="D18" s="54"/>
       <c r="E18" s="54"/>
       <c r="F18" s="55"/>
       <c r="G18" s="55"/>
-      <c r="H18" s="154"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="155"/>
+      <c r="H18" s="158"/>
+      <c r="I18" s="156"/>
+      <c r="J18" s="159"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="151"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="153"/>
+      <c r="A19" s="155"/>
+      <c r="B19" s="156"/>
+      <c r="C19" s="157"/>
       <c r="D19" s="54"/>
       <c r="E19" s="54"/>
       <c r="F19" s="55"/>
       <c r="G19" s="55"/>
-      <c r="H19" s="154"/>
-      <c r="I19" s="152"/>
-      <c r="J19" s="155"/>
+      <c r="H19" s="158"/>
+      <c r="I19" s="156"/>
+      <c r="J19" s="159"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="151"/>
-      <c r="B20" s="152"/>
-      <c r="C20" s="153"/>
+      <c r="A20" s="155"/>
+      <c r="B20" s="156"/>
+      <c r="C20" s="157"/>
       <c r="D20" s="54"/>
       <c r="E20" s="54"/>
       <c r="F20" s="55"/>
       <c r="G20" s="55"/>
-      <c r="H20" s="154"/>
-      <c r="I20" s="152"/>
-      <c r="J20" s="155"/>
+      <c r="H20" s="158"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="159"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="152"/>
-      <c r="C21" s="153"/>
+      <c r="A21" s="155"/>
+      <c r="B21" s="156"/>
+      <c r="C21" s="157"/>
       <c r="D21" s="54"/>
       <c r="E21" s="54"/>
       <c r="F21" s="55"/>
       <c r="G21" s="55"/>
-      <c r="H21" s="154"/>
-      <c r="I21" s="152"/>
-      <c r="J21" s="155"/>
+      <c r="H21" s="158"/>
+      <c r="I21" s="156"/>
+      <c r="J21" s="159"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="151"/>
-      <c r="B22" s="152"/>
-      <c r="C22" s="153"/>
+      <c r="A22" s="155"/>
+      <c r="B22" s="156"/>
+      <c r="C22" s="157"/>
       <c r="D22" s="54"/>
       <c r="E22" s="54"/>
       <c r="F22" s="55"/>
       <c r="G22" s="55"/>
-      <c r="H22" s="154"/>
-      <c r="I22" s="152"/>
-      <c r="J22" s="155"/>
+      <c r="H22" s="158"/>
+      <c r="I22" s="156"/>
+      <c r="J22" s="159"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="157"/>
-      <c r="C23" s="158"/>
+      <c r="A23" s="186"/>
+      <c r="B23" s="187"/>
+      <c r="C23" s="188"/>
       <c r="D23" s="56"/>
       <c r="E23" s="56"/>
       <c r="F23" s="57"/>
       <c r="G23" s="57"/>
-      <c r="H23" s="159"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="160"/>
+      <c r="H23" s="189"/>
+      <c r="I23" s="187"/>
+      <c r="J23" s="190"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10317,6 +11631,21 @@
     <row r="1000" s="51" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -10333,21 +11662,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10368,19 +11682,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="197" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="202" t="s">
+      <c r="B1" s="198"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="203"/>
-      <c r="F1" s="202" t="s">
+      <c r="E1" s="207"/>
+      <c r="F1" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="203"/>
+      <c r="G1" s="207"/>
       <c r="H1" s="14" t="s">
         <v>3</v>
       </c>
@@ -10392,48 +11706,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="196"/>
-      <c r="B2" s="197"/>
-      <c r="C2" s="198"/>
-      <c r="D2" s="204" t="s">
+      <c r="A2" s="200"/>
+      <c r="B2" s="201"/>
+      <c r="C2" s="202"/>
+      <c r="D2" s="208" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="204" t="s">
+      <c r="E2" s="209"/>
+      <c r="F2" s="208" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="205"/>
-      <c r="H2" s="208">
+      <c r="G2" s="209"/>
+      <c r="H2" s="212">
         <v>45827</v>
       </c>
-      <c r="I2" s="187" t="s">
+      <c r="I2" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="190"/>
+      <c r="J2" s="194"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="196"/>
-      <c r="B3" s="197"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="206"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="206"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="188"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="191"/>
+      <c r="A3" s="200"/>
+      <c r="B3" s="201"/>
+      <c r="C3" s="202"/>
+      <c r="D3" s="210"/>
+      <c r="E3" s="202"/>
+      <c r="F3" s="210"/>
+      <c r="G3" s="202"/>
+      <c r="H3" s="192"/>
+      <c r="I3" s="192"/>
+      <c r="J3" s="195"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="199"/>
-      <c r="B4" s="200"/>
-      <c r="C4" s="201"/>
-      <c r="D4" s="207"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="201"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="192"/>
+      <c r="A4" s="203"/>
+      <c r="B4" s="204"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="196"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="18"/>
@@ -11782,190 +13096,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="237" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="238"/>
-      <c r="C1" s="238"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="238"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="246" t="s">
+      <c r="A1" s="229" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="230"/>
+      <c r="C1" s="230"/>
+      <c r="D1" s="230"/>
+      <c r="E1" s="230"/>
+      <c r="F1" s="231"/>
+      <c r="G1" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="231"/>
-      <c r="I1" s="231"/>
-      <c r="J1" s="232"/>
-      <c r="K1" s="246" t="s">
+      <c r="H1" s="220"/>
+      <c r="I1" s="220"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="238" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="231"/>
-      <c r="M1" s="231"/>
-      <c r="N1" s="232"/>
-      <c r="O1" s="246" t="s">
+      <c r="L1" s="220"/>
+      <c r="M1" s="220"/>
+      <c r="N1" s="221"/>
+      <c r="O1" s="238" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="232"/>
-      <c r="Q1" s="246" t="s">
+      <c r="P1" s="221"/>
+      <c r="Q1" s="238" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="232"/>
-      <c r="S1" s="246" t="s">
+      <c r="R1" s="221"/>
+      <c r="S1" s="238" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="234"/>
+      <c r="T1" s="223"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="240"/>
-      <c r="B2" s="241"/>
-      <c r="C2" s="241"/>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="224" t="s">
+      <c r="A2" s="232"/>
+      <c r="B2" s="233"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="213" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="247"/>
-      <c r="I2" s="247"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="224" t="s">
+      <c r="H2" s="239"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="L2" s="247"/>
-      <c r="M2" s="247"/>
-      <c r="N2" s="248"/>
-      <c r="O2" s="297">
+      <c r="L2" s="239"/>
+      <c r="M2" s="239"/>
+      <c r="N2" s="240"/>
+      <c r="O2" s="241">
         <v>45827</v>
       </c>
-      <c r="P2" s="248"/>
-      <c r="Q2" s="224" t="s">
+      <c r="P2" s="240"/>
+      <c r="Q2" s="213" t="s">
         <v>79</v>
       </c>
-      <c r="R2" s="248"/>
-      <c r="S2" s="224"/>
-      <c r="T2" s="225"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="213"/>
+      <c r="T2" s="214"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="240"/>
-      <c r="B3" s="241"/>
-      <c r="C3" s="241"/>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="226"/>
-      <c r="H3" s="241"/>
-      <c r="I3" s="241"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="241"/>
-      <c r="M3" s="241"/>
-      <c r="N3" s="242"/>
-      <c r="O3" s="226"/>
-      <c r="P3" s="242"/>
-      <c r="Q3" s="226"/>
-      <c r="R3" s="242"/>
-      <c r="S3" s="226"/>
-      <c r="T3" s="227"/>
+      <c r="A3" s="232"/>
+      <c r="B3" s="233"/>
+      <c r="C3" s="233"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="234"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="233"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="215"/>
+      <c r="L3" s="233"/>
+      <c r="M3" s="233"/>
+      <c r="N3" s="234"/>
+      <c r="O3" s="215"/>
+      <c r="P3" s="234"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="234"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="216"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="243"/>
-      <c r="B4" s="244"/>
-      <c r="C4" s="244"/>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="228"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="228"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="244"/>
-      <c r="N4" s="245"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="245"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="245"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="229"/>
+      <c r="A4" s="235"/>
+      <c r="B4" s="236"/>
+      <c r="C4" s="236"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="237"/>
+      <c r="K4" s="217"/>
+      <c r="L4" s="236"/>
+      <c r="M4" s="236"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="218"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="230" t="s">
+      <c r="A5" s="219" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="231"/>
-      <c r="C5" s="231"/>
-      <c r="D5" s="231"/>
-      <c r="E5" s="231"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="233" t="s">
+      <c r="B5" s="220"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="220"/>
+      <c r="E5" s="220"/>
+      <c r="F5" s="221"/>
+      <c r="G5" s="222" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="231"/>
-      <c r="I5" s="231"/>
-      <c r="J5" s="231"/>
-      <c r="K5" s="231"/>
-      <c r="L5" s="231"/>
-      <c r="M5" s="231"/>
-      <c r="N5" s="231"/>
-      <c r="O5" s="231"/>
-      <c r="P5" s="231"/>
-      <c r="Q5" s="231"/>
-      <c r="R5" s="231"/>
-      <c r="S5" s="231"/>
-      <c r="T5" s="234"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="220"/>
+      <c r="J5" s="220"/>
+      <c r="K5" s="220"/>
+      <c r="L5" s="220"/>
+      <c r="M5" s="220"/>
+      <c r="N5" s="220"/>
+      <c r="O5" s="220"/>
+      <c r="P5" s="220"/>
+      <c r="Q5" s="220"/>
+      <c r="R5" s="220"/>
+      <c r="S5" s="220"/>
+      <c r="T5" s="223"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="222" t="s">
+      <c r="A6" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="216"/>
-      <c r="C6" s="216"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="216"/>
-      <c r="F6" s="217"/>
-      <c r="G6" s="235" t="s">
+      <c r="B6" s="225"/>
+      <c r="C6" s="225"/>
+      <c r="D6" s="225"/>
+      <c r="E6" s="225"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="227" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="216"/>
-      <c r="I6" s="216"/>
-      <c r="J6" s="216"/>
-      <c r="K6" s="216"/>
-      <c r="L6" s="216"/>
-      <c r="M6" s="216"/>
-      <c r="N6" s="216"/>
-      <c r="O6" s="216"/>
-      <c r="P6" s="216"/>
-      <c r="Q6" s="216"/>
-      <c r="R6" s="216"/>
-      <c r="S6" s="216"/>
-      <c r="T6" s="236"/>
+      <c r="H6" s="225"/>
+      <c r="I6" s="225"/>
+      <c r="J6" s="225"/>
+      <c r="K6" s="225"/>
+      <c r="L6" s="225"/>
+      <c r="M6" s="225"/>
+      <c r="N6" s="225"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="225"/>
+      <c r="Q6" s="225"/>
+      <c r="R6" s="225"/>
+      <c r="S6" s="225"/>
+      <c r="T6" s="228"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="222" t="s">
+      <c r="A7" s="224" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="217"/>
-      <c r="G7" s="235" t="s">
+      <c r="B7" s="225"/>
+      <c r="C7" s="225"/>
+      <c r="D7" s="225"/>
+      <c r="E7" s="225"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="227" t="s">
         <v>105</v>
       </c>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="216"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="216"/>
-      <c r="M7" s="216"/>
-      <c r="N7" s="216"/>
-      <c r="O7" s="216"/>
-      <c r="P7" s="216"/>
-      <c r="Q7" s="216"/>
-      <c r="R7" s="216"/>
-      <c r="S7" s="216"/>
-      <c r="T7" s="236"/>
+      <c r="H7" s="225"/>
+      <c r="I7" s="225"/>
+      <c r="J7" s="225"/>
+      <c r="K7" s="225"/>
+      <c r="L7" s="225"/>
+      <c r="M7" s="225"/>
+      <c r="N7" s="225"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="225"/>
+      <c r="Q7" s="225"/>
+      <c r="R7" s="225"/>
+      <c r="S7" s="225"/>
+      <c r="T7" s="228"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="26"/>
@@ -12164,37 +13478,37 @@
       <c r="T14" s="28"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="222" t="s">
+      <c r="A15" s="224" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="217"/>
-      <c r="C15" s="223" t="s">
+      <c r="B15" s="226"/>
+      <c r="C15" s="250" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="217"/>
-      <c r="E15" s="221" t="s">
+      <c r="D15" s="226"/>
+      <c r="E15" s="242" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="217"/>
-      <c r="G15" s="221" t="s">
+      <c r="F15" s="226"/>
+      <c r="G15" s="242" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="216"/>
-      <c r="I15" s="217"/>
-      <c r="J15" s="221" t="s">
+      <c r="H15" s="225"/>
+      <c r="I15" s="226"/>
+      <c r="J15" s="242" t="s">
         <v>35</v>
       </c>
-      <c r="K15" s="217"/>
-      <c r="L15" s="221" t="s">
+      <c r="K15" s="226"/>
+      <c r="L15" s="242" t="s">
         <v>36</v>
       </c>
-      <c r="M15" s="216"/>
-      <c r="N15" s="217"/>
-      <c r="O15" s="221" t="s">
+      <c r="M15" s="225"/>
+      <c r="N15" s="226"/>
+      <c r="O15" s="242" t="s">
         <v>37</v>
       </c>
-      <c r="P15" s="216"/>
-      <c r="Q15" s="217"/>
+      <c r="P15" s="225"/>
+      <c r="Q15" s="226"/>
       <c r="R15" s="40" t="s">
         <v>38</v>
       </c>
@@ -12206,45 +13520,45 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="287">
+      <c r="A16" s="243">
         <v>1</v>
       </c>
-      <c r="B16" s="288"/>
-      <c r="C16" s="289" t="s">
+      <c r="B16" s="244"/>
+      <c r="C16" s="245" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="288"/>
-      <c r="E16" s="289" t="s">
+      <c r="D16" s="244"/>
+      <c r="E16" s="245" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="288"/>
-      <c r="G16" s="290" t="s">
+      <c r="F16" s="244"/>
+      <c r="G16" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="H16" s="291"/>
-      <c r="I16" s="288"/>
-      <c r="J16" s="292" t="s">
+      <c r="H16" s="247"/>
+      <c r="I16" s="244"/>
+      <c r="J16" s="248" t="s">
         <v>100</v>
       </c>
-      <c r="K16" s="92"/>
-      <c r="L16" s="293" t="s">
+      <c r="K16" s="105"/>
+      <c r="L16" s="249" t="s">
         <v>107</v>
       </c>
-      <c r="M16" s="291"/>
-      <c r="N16" s="288"/>
-      <c r="O16" s="293" t="s">
+      <c r="M16" s="247"/>
+      <c r="N16" s="244"/>
+      <c r="O16" s="249" t="s">
         <v>108</v>
       </c>
-      <c r="P16" s="291"/>
-      <c r="Q16" s="288"/>
-      <c r="R16" s="303">
+      <c r="P16" s="247"/>
+      <c r="Q16" s="244"/>
+      <c r="R16" s="90">
         <v>45827</v>
       </c>
-      <c r="S16" s="294" t="s">
+      <c r="S16" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="T16" s="295" t="s">
-        <v>125</v>
+      <c r="T16" s="89" t="s">
+        <v>124</v>
       </c>
       <c r="U16" s="44"/>
       <c r="V16" s="44"/>
@@ -12254,45 +13568,45 @@
       <c r="Z16" s="44"/>
     </row>
     <row r="17" spans="1:26" ht="66" customHeight="1">
-      <c r="A17" s="287">
+      <c r="A17" s="243">
         <v>2</v>
       </c>
-      <c r="B17" s="288"/>
-      <c r="C17" s="289" t="s">
+      <c r="B17" s="244"/>
+      <c r="C17" s="245" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="288"/>
-      <c r="E17" s="289" t="s">
+      <c r="D17" s="244"/>
+      <c r="E17" s="245" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="288"/>
-      <c r="G17" s="290" t="s">
+      <c r="F17" s="244"/>
+      <c r="G17" s="246" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="291"/>
-      <c r="I17" s="288"/>
-      <c r="J17" s="290" t="s">
+      <c r="H17" s="247"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="246" t="s">
         <v>101</v>
       </c>
-      <c r="K17" s="288"/>
-      <c r="L17" s="293" t="s">
+      <c r="K17" s="244"/>
+      <c r="L17" s="249" t="s">
         <v>110</v>
       </c>
-      <c r="M17" s="291"/>
-      <c r="N17" s="288"/>
-      <c r="O17" s="293" t="s">
-        <v>126</v>
-      </c>
-      <c r="P17" s="291"/>
-      <c r="Q17" s="288"/>
-      <c r="R17" s="303">
+      <c r="M17" s="247"/>
+      <c r="N17" s="244"/>
+      <c r="O17" s="249" t="s">
+        <v>125</v>
+      </c>
+      <c r="P17" s="247"/>
+      <c r="Q17" s="244"/>
+      <c r="R17" s="90">
         <v>45827</v>
       </c>
-      <c r="S17" s="294" t="s">
+      <c r="S17" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="T17" s="295" t="s">
-        <v>125</v>
+      <c r="T17" s="89" t="s">
+        <v>124</v>
       </c>
       <c r="U17" s="44"/>
       <c r="V17" s="44"/>
@@ -12302,45 +13616,45 @@
       <c r="Z17" s="44"/>
     </row>
     <row r="18" spans="1:26" ht="66.75" customHeight="1">
-      <c r="A18" s="287">
+      <c r="A18" s="243">
         <v>3</v>
       </c>
-      <c r="B18" s="288"/>
-      <c r="C18" s="289" t="s">
+      <c r="B18" s="244"/>
+      <c r="C18" s="245" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="288"/>
-      <c r="E18" s="289" t="s">
+      <c r="D18" s="244"/>
+      <c r="E18" s="245" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="288"/>
-      <c r="G18" s="290" t="s">
+      <c r="F18" s="244"/>
+      <c r="G18" s="246" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="291"/>
-      <c r="I18" s="288"/>
-      <c r="J18" s="290" t="s">
+      <c r="H18" s="247"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="246" t="s">
+        <v>101</v>
+      </c>
+      <c r="K18" s="244"/>
+      <c r="L18" s="249" t="s">
         <v>121</v>
       </c>
-      <c r="K18" s="288"/>
-      <c r="L18" s="293" t="s">
+      <c r="M18" s="247"/>
+      <c r="N18" s="244"/>
+      <c r="O18" s="249" t="s">
         <v>122</v>
       </c>
-      <c r="M18" s="291"/>
-      <c r="N18" s="288"/>
-      <c r="O18" s="293" t="s">
-        <v>123</v>
-      </c>
-      <c r="P18" s="291"/>
-      <c r="Q18" s="288"/>
-      <c r="R18" s="303">
+      <c r="P18" s="247"/>
+      <c r="Q18" s="244"/>
+      <c r="R18" s="90">
         <v>45827</v>
       </c>
-      <c r="S18" s="294" t="s">
+      <c r="S18" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="T18" s="295" t="s">
-        <v>125</v>
+      <c r="T18" s="89" t="s">
+        <v>124</v>
       </c>
       <c r="U18" s="44"/>
       <c r="V18" s="44"/>
@@ -12350,45 +13664,45 @@
       <c r="Z18" s="44"/>
     </row>
     <row r="19" spans="1:26" ht="76.5" customHeight="1">
-      <c r="A19" s="287">
+      <c r="A19" s="243">
         <v>4</v>
       </c>
-      <c r="B19" s="288"/>
-      <c r="C19" s="289" t="s">
+      <c r="B19" s="244"/>
+      <c r="C19" s="245" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="288"/>
-      <c r="E19" s="289" t="s">
+      <c r="D19" s="244"/>
+      <c r="E19" s="245" t="s">
         <v>102</v>
       </c>
-      <c r="F19" s="288"/>
-      <c r="G19" s="290" t="s">
+      <c r="F19" s="244"/>
+      <c r="G19" s="246" t="s">
         <v>111</v>
       </c>
-      <c r="H19" s="291"/>
-      <c r="I19" s="288"/>
-      <c r="J19" s="290" t="s">
+      <c r="H19" s="247"/>
+      <c r="I19" s="244"/>
+      <c r="J19" s="246" t="s">
         <v>103</v>
       </c>
-      <c r="K19" s="288"/>
-      <c r="L19" s="296" t="s">
-        <v>127</v>
-      </c>
-      <c r="M19" s="291"/>
-      <c r="N19" s="288"/>
-      <c r="O19" s="293" t="s">
+      <c r="K19" s="244"/>
+      <c r="L19" s="256" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="247"/>
+      <c r="N19" s="244"/>
+      <c r="O19" s="249" t="s">
         <v>104</v>
       </c>
-      <c r="P19" s="291"/>
-      <c r="Q19" s="288"/>
-      <c r="R19" s="303">
+      <c r="P19" s="247"/>
+      <c r="Q19" s="244"/>
+      <c r="R19" s="90">
         <v>45827</v>
       </c>
-      <c r="S19" s="294" t="s">
+      <c r="S19" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="T19" s="295" t="s">
-        <v>125</v>
+      <c r="T19" s="89" t="s">
+        <v>124</v>
       </c>
       <c r="U19" s="44"/>
       <c r="V19" s="44"/>
@@ -12398,45 +13712,45 @@
       <c r="Z19" s="44"/>
     </row>
     <row r="20" spans="1:26" ht="65.25" customHeight="1">
-      <c r="A20" s="287">
+      <c r="A20" s="243">
         <v>5</v>
       </c>
-      <c r="B20" s="288"/>
-      <c r="C20" s="289" t="s">
+      <c r="B20" s="244"/>
+      <c r="C20" s="245" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="302"/>
-      <c r="E20" s="289" t="s">
+      <c r="D20" s="251"/>
+      <c r="E20" s="245" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="302"/>
-      <c r="G20" s="290" t="s">
+      <c r="F20" s="251"/>
+      <c r="G20" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="H20" s="301"/>
-      <c r="I20" s="300"/>
-      <c r="J20" s="290" t="s">
+      <c r="H20" s="252"/>
+      <c r="I20" s="253"/>
+      <c r="J20" s="246" t="s">
         <v>100</v>
       </c>
-      <c r="K20" s="300"/>
-      <c r="L20" s="293" t="s">
+      <c r="K20" s="253"/>
+      <c r="L20" s="249" t="s">
         <v>110</v>
       </c>
-      <c r="M20" s="298"/>
-      <c r="N20" s="299"/>
-      <c r="O20" s="293" t="s">
+      <c r="M20" s="254"/>
+      <c r="N20" s="255"/>
+      <c r="O20" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="P20" s="298"/>
-      <c r="Q20" s="299"/>
-      <c r="R20" s="303">
+      <c r="P20" s="254"/>
+      <c r="Q20" s="255"/>
+      <c r="R20" s="90">
         <v>45827</v>
       </c>
-      <c r="S20" s="294" t="s">
+      <c r="S20" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="T20" s="295" t="s">
-        <v>125</v>
+      <c r="T20" s="89" t="s">
+        <v>124</v>
       </c>
       <c r="U20" s="44"/>
       <c r="V20" s="44"/>
@@ -12446,23 +13760,23 @@
       <c r="Z20" s="44"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="218"/>
-      <c r="B21" s="217"/>
-      <c r="C21" s="219"/>
-      <c r="D21" s="217"/>
-      <c r="E21" s="219"/>
-      <c r="F21" s="217"/>
-      <c r="G21" s="220"/>
-      <c r="H21" s="216"/>
-      <c r="I21" s="217"/>
-      <c r="J21" s="220"/>
-      <c r="K21" s="217"/>
-      <c r="L21" s="215"/>
-      <c r="M21" s="216"/>
-      <c r="N21" s="217"/>
-      <c r="O21" s="215"/>
-      <c r="P21" s="216"/>
-      <c r="Q21" s="217"/>
+      <c r="A21" s="258"/>
+      <c r="B21" s="226"/>
+      <c r="C21" s="259"/>
+      <c r="D21" s="226"/>
+      <c r="E21" s="259"/>
+      <c r="F21" s="226"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="225"/>
+      <c r="I21" s="226"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="226"/>
+      <c r="L21" s="257"/>
+      <c r="M21" s="225"/>
+      <c r="N21" s="226"/>
+      <c r="O21" s="257"/>
+      <c r="P21" s="225"/>
+      <c r="Q21" s="226"/>
       <c r="R21" s="42"/>
       <c r="S21" s="42"/>
       <c r="T21" s="43"/>
@@ -12474,23 +13788,23 @@
       <c r="Z21" s="44"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="218"/>
-      <c r="B22" s="217"/>
-      <c r="C22" s="219"/>
-      <c r="D22" s="217"/>
-      <c r="E22" s="219"/>
-      <c r="F22" s="217"/>
-      <c r="G22" s="220"/>
-      <c r="H22" s="216"/>
-      <c r="I22" s="217"/>
-      <c r="J22" s="220"/>
-      <c r="K22" s="217"/>
-      <c r="L22" s="215"/>
-      <c r="M22" s="216"/>
-      <c r="N22" s="217"/>
-      <c r="O22" s="215"/>
-      <c r="P22" s="216"/>
-      <c r="Q22" s="217"/>
+      <c r="A22" s="258"/>
+      <c r="B22" s="226"/>
+      <c r="C22" s="259"/>
+      <c r="D22" s="226"/>
+      <c r="E22" s="259"/>
+      <c r="F22" s="226"/>
+      <c r="G22" s="260"/>
+      <c r="H22" s="225"/>
+      <c r="I22" s="226"/>
+      <c r="J22" s="260"/>
+      <c r="K22" s="226"/>
+      <c r="L22" s="257"/>
+      <c r="M22" s="225"/>
+      <c r="N22" s="226"/>
+      <c r="O22" s="257"/>
+      <c r="P22" s="225"/>
+      <c r="Q22" s="226"/>
       <c r="R22" s="42"/>
       <c r="S22" s="42"/>
       <c r="T22" s="43"/>
@@ -12502,23 +13816,23 @@
       <c r="Z22" s="44"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="218"/>
-      <c r="B23" s="217"/>
-      <c r="C23" s="219"/>
-      <c r="D23" s="217"/>
-      <c r="E23" s="219"/>
-      <c r="F23" s="217"/>
-      <c r="G23" s="220"/>
-      <c r="H23" s="216"/>
-      <c r="I23" s="217"/>
-      <c r="J23" s="220"/>
-      <c r="K23" s="217"/>
-      <c r="L23" s="215"/>
-      <c r="M23" s="216"/>
-      <c r="N23" s="217"/>
-      <c r="O23" s="215"/>
-      <c r="P23" s="216"/>
-      <c r="Q23" s="217"/>
+      <c r="A23" s="258"/>
+      <c r="B23" s="226"/>
+      <c r="C23" s="259"/>
+      <c r="D23" s="226"/>
+      <c r="E23" s="259"/>
+      <c r="F23" s="226"/>
+      <c r="G23" s="260"/>
+      <c r="H23" s="225"/>
+      <c r="I23" s="226"/>
+      <c r="J23" s="260"/>
+      <c r="K23" s="226"/>
+      <c r="L23" s="257"/>
+      <c r="M23" s="225"/>
+      <c r="N23" s="226"/>
+      <c r="O23" s="257"/>
+      <c r="P23" s="225"/>
+      <c r="Q23" s="226"/>
       <c r="R23" s="42"/>
       <c r="S23" s="42"/>
       <c r="T23" s="43"/>
@@ -12530,23 +13844,23 @@
       <c r="Z23" s="44"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="218"/>
-      <c r="B24" s="217"/>
-      <c r="C24" s="219"/>
-      <c r="D24" s="217"/>
-      <c r="E24" s="219"/>
-      <c r="F24" s="217"/>
-      <c r="G24" s="220"/>
-      <c r="H24" s="216"/>
-      <c r="I24" s="217"/>
-      <c r="J24" s="220"/>
-      <c r="K24" s="217"/>
-      <c r="L24" s="215"/>
-      <c r="M24" s="216"/>
-      <c r="N24" s="217"/>
-      <c r="O24" s="215"/>
-      <c r="P24" s="216"/>
-      <c r="Q24" s="217"/>
+      <c r="A24" s="258"/>
+      <c r="B24" s="226"/>
+      <c r="C24" s="259"/>
+      <c r="D24" s="226"/>
+      <c r="E24" s="259"/>
+      <c r="F24" s="226"/>
+      <c r="G24" s="260"/>
+      <c r="H24" s="225"/>
+      <c r="I24" s="226"/>
+      <c r="J24" s="260"/>
+      <c r="K24" s="226"/>
+      <c r="L24" s="257"/>
+      <c r="M24" s="225"/>
+      <c r="N24" s="226"/>
+      <c r="O24" s="257"/>
+      <c r="P24" s="225"/>
+      <c r="Q24" s="226"/>
       <c r="R24" s="42"/>
       <c r="S24" s="42"/>
       <c r="T24" s="43"/>
@@ -12558,23 +13872,23 @@
       <c r="Z24" s="44"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="218"/>
-      <c r="B25" s="217"/>
-      <c r="C25" s="219"/>
-      <c r="D25" s="217"/>
-      <c r="E25" s="219"/>
-      <c r="F25" s="217"/>
-      <c r="G25" s="220"/>
-      <c r="H25" s="216"/>
-      <c r="I25" s="217"/>
-      <c r="J25" s="220"/>
-      <c r="K25" s="217"/>
-      <c r="L25" s="215"/>
-      <c r="M25" s="216"/>
-      <c r="N25" s="217"/>
-      <c r="O25" s="215"/>
-      <c r="P25" s="216"/>
-      <c r="Q25" s="217"/>
+      <c r="A25" s="258"/>
+      <c r="B25" s="226"/>
+      <c r="C25" s="259"/>
+      <c r="D25" s="226"/>
+      <c r="E25" s="259"/>
+      <c r="F25" s="226"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="225"/>
+      <c r="I25" s="226"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="226"/>
+      <c r="L25" s="257"/>
+      <c r="M25" s="225"/>
+      <c r="N25" s="226"/>
+      <c r="O25" s="257"/>
+      <c r="P25" s="225"/>
+      <c r="Q25" s="226"/>
       <c r="R25" s="42"/>
       <c r="S25" s="42"/>
       <c r="T25" s="43"/>
@@ -12586,23 +13900,23 @@
       <c r="Z25" s="44"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="218"/>
-      <c r="B26" s="217"/>
-      <c r="C26" s="219"/>
-      <c r="D26" s="217"/>
-      <c r="E26" s="219"/>
-      <c r="F26" s="217"/>
-      <c r="G26" s="220"/>
-      <c r="H26" s="216"/>
-      <c r="I26" s="217"/>
-      <c r="J26" s="220"/>
-      <c r="K26" s="217"/>
-      <c r="L26" s="215"/>
-      <c r="M26" s="216"/>
-      <c r="N26" s="217"/>
-      <c r="O26" s="215"/>
-      <c r="P26" s="216"/>
-      <c r="Q26" s="217"/>
+      <c r="A26" s="258"/>
+      <c r="B26" s="226"/>
+      <c r="C26" s="259"/>
+      <c r="D26" s="226"/>
+      <c r="E26" s="259"/>
+      <c r="F26" s="226"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="225"/>
+      <c r="I26" s="226"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="226"/>
+      <c r="L26" s="257"/>
+      <c r="M26" s="225"/>
+      <c r="N26" s="226"/>
+      <c r="O26" s="257"/>
+      <c r="P26" s="225"/>
+      <c r="Q26" s="226"/>
       <c r="R26" s="42"/>
       <c r="S26" s="42"/>
       <c r="T26" s="43"/>
@@ -12614,23 +13928,23 @@
       <c r="Z26" s="44"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="218"/>
-      <c r="B27" s="217"/>
-      <c r="C27" s="219"/>
-      <c r="D27" s="217"/>
-      <c r="E27" s="219"/>
-      <c r="F27" s="217"/>
-      <c r="G27" s="220"/>
-      <c r="H27" s="216"/>
-      <c r="I27" s="217"/>
-      <c r="J27" s="220"/>
-      <c r="K27" s="217"/>
-      <c r="L27" s="215"/>
-      <c r="M27" s="216"/>
-      <c r="N27" s="217"/>
-      <c r="O27" s="215"/>
-      <c r="P27" s="216"/>
-      <c r="Q27" s="217"/>
+      <c r="A27" s="258"/>
+      <c r="B27" s="226"/>
+      <c r="C27" s="259"/>
+      <c r="D27" s="226"/>
+      <c r="E27" s="259"/>
+      <c r="F27" s="226"/>
+      <c r="G27" s="260"/>
+      <c r="H27" s="225"/>
+      <c r="I27" s="226"/>
+      <c r="J27" s="260"/>
+      <c r="K27" s="226"/>
+      <c r="L27" s="257"/>
+      <c r="M27" s="225"/>
+      <c r="N27" s="226"/>
+      <c r="O27" s="257"/>
+      <c r="P27" s="225"/>
+      <c r="Q27" s="226"/>
       <c r="R27" s="42"/>
       <c r="S27" s="42"/>
       <c r="T27" s="43"/>
@@ -12642,23 +13956,23 @@
       <c r="Z27" s="44"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="218"/>
-      <c r="B28" s="217"/>
-      <c r="C28" s="219"/>
-      <c r="D28" s="217"/>
-      <c r="E28" s="219"/>
-      <c r="F28" s="217"/>
-      <c r="G28" s="220"/>
-      <c r="H28" s="216"/>
-      <c r="I28" s="217"/>
-      <c r="J28" s="220"/>
-      <c r="K28" s="217"/>
-      <c r="L28" s="215"/>
-      <c r="M28" s="216"/>
-      <c r="N28" s="217"/>
-      <c r="O28" s="215"/>
-      <c r="P28" s="216"/>
-      <c r="Q28" s="217"/>
+      <c r="A28" s="258"/>
+      <c r="B28" s="226"/>
+      <c r="C28" s="259"/>
+      <c r="D28" s="226"/>
+      <c r="E28" s="259"/>
+      <c r="F28" s="226"/>
+      <c r="G28" s="260"/>
+      <c r="H28" s="225"/>
+      <c r="I28" s="226"/>
+      <c r="J28" s="260"/>
+      <c r="K28" s="226"/>
+      <c r="L28" s="257"/>
+      <c r="M28" s="225"/>
+      <c r="N28" s="226"/>
+      <c r="O28" s="257"/>
+      <c r="P28" s="225"/>
+      <c r="Q28" s="226"/>
       <c r="R28" s="42"/>
       <c r="S28" s="42"/>
       <c r="T28" s="43"/>
@@ -12670,23 +13984,23 @@
       <c r="Z28" s="44"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="218"/>
-      <c r="B29" s="217"/>
-      <c r="C29" s="219"/>
-      <c r="D29" s="217"/>
-      <c r="E29" s="219"/>
-      <c r="F29" s="217"/>
-      <c r="G29" s="220"/>
-      <c r="H29" s="216"/>
-      <c r="I29" s="217"/>
-      <c r="J29" s="220"/>
-      <c r="K29" s="217"/>
-      <c r="L29" s="215"/>
-      <c r="M29" s="216"/>
-      <c r="N29" s="217"/>
-      <c r="O29" s="215"/>
-      <c r="P29" s="216"/>
-      <c r="Q29" s="217"/>
+      <c r="A29" s="258"/>
+      <c r="B29" s="226"/>
+      <c r="C29" s="259"/>
+      <c r="D29" s="226"/>
+      <c r="E29" s="259"/>
+      <c r="F29" s="226"/>
+      <c r="G29" s="260"/>
+      <c r="H29" s="225"/>
+      <c r="I29" s="226"/>
+      <c r="J29" s="260"/>
+      <c r="K29" s="226"/>
+      <c r="L29" s="257"/>
+      <c r="M29" s="225"/>
+      <c r="N29" s="226"/>
+      <c r="O29" s="257"/>
+      <c r="P29" s="225"/>
+      <c r="Q29" s="226"/>
       <c r="R29" s="42"/>
       <c r="S29" s="42"/>
       <c r="T29" s="43"/>
@@ -12698,23 +14012,23 @@
       <c r="Z29" s="44"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="218"/>
-      <c r="B30" s="217"/>
-      <c r="C30" s="219"/>
-      <c r="D30" s="217"/>
-      <c r="E30" s="219"/>
-      <c r="F30" s="217"/>
-      <c r="G30" s="220"/>
-      <c r="H30" s="216"/>
-      <c r="I30" s="217"/>
-      <c r="J30" s="220"/>
-      <c r="K30" s="217"/>
-      <c r="L30" s="215"/>
-      <c r="M30" s="216"/>
-      <c r="N30" s="217"/>
-      <c r="O30" s="215"/>
-      <c r="P30" s="216"/>
-      <c r="Q30" s="217"/>
+      <c r="A30" s="258"/>
+      <c r="B30" s="226"/>
+      <c r="C30" s="259"/>
+      <c r="D30" s="226"/>
+      <c r="E30" s="259"/>
+      <c r="F30" s="226"/>
+      <c r="G30" s="260"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="226"/>
+      <c r="J30" s="260"/>
+      <c r="K30" s="226"/>
+      <c r="L30" s="257"/>
+      <c r="M30" s="225"/>
+      <c r="N30" s="226"/>
+      <c r="O30" s="257"/>
+      <c r="P30" s="225"/>
+      <c r="Q30" s="226"/>
       <c r="R30" s="42"/>
       <c r="S30" s="42"/>
       <c r="T30" s="43"/>
@@ -12726,23 +14040,23 @@
       <c r="Z30" s="44"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="212"/>
-      <c r="B31" s="211"/>
-      <c r="C31" s="213"/>
-      <c r="D31" s="211"/>
-      <c r="E31" s="213"/>
-      <c r="F31" s="211"/>
-      <c r="G31" s="214"/>
-      <c r="H31" s="210"/>
-      <c r="I31" s="211"/>
-      <c r="J31" s="214"/>
-      <c r="K31" s="211"/>
-      <c r="L31" s="209"/>
-      <c r="M31" s="210"/>
-      <c r="N31" s="211"/>
-      <c r="O31" s="209"/>
-      <c r="P31" s="210"/>
-      <c r="Q31" s="211"/>
+      <c r="A31" s="264"/>
+      <c r="B31" s="263"/>
+      <c r="C31" s="265"/>
+      <c r="D31" s="263"/>
+      <c r="E31" s="265"/>
+      <c r="F31" s="263"/>
+      <c r="G31" s="266"/>
+      <c r="H31" s="262"/>
+      <c r="I31" s="263"/>
+      <c r="J31" s="266"/>
+      <c r="K31" s="263"/>
+      <c r="L31" s="261"/>
+      <c r="M31" s="262"/>
+      <c r="N31" s="263"/>
+      <c r="O31" s="261"/>
+      <c r="P31" s="262"/>
+      <c r="Q31" s="263"/>
       <c r="R31" s="45"/>
       <c r="S31" s="45"/>
       <c r="T31" s="46"/>
@@ -13740,121 +15054,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
@@ -13876,6 +15075,121 @@
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
@@ -13901,70 +15215,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="266" t="s">
+      <c r="A1" s="276" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="266"/>
-      <c r="C1" s="267" t="s">
+      <c r="B1" s="276"/>
+      <c r="C1" s="277" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="268"/>
-      <c r="E1" s="269"/>
-      <c r="F1" s="270" t="s">
+      <c r="D1" s="278"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="280" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="271"/>
-      <c r="H1" s="271"/>
-      <c r="I1" s="271"/>
-      <c r="J1" s="271"/>
-      <c r="K1" s="271"/>
-      <c r="L1" s="271"/>
-      <c r="M1" s="272"/>
+      <c r="G1" s="281"/>
+      <c r="H1" s="281"/>
+      <c r="I1" s="281"/>
+      <c r="J1" s="281"/>
+      <c r="K1" s="281"/>
+      <c r="L1" s="281"/>
+      <c r="M1" s="282"/>
       <c r="N1" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="O1" s="270" t="s">
+      <c r="O1" s="280" t="s">
         <v>79</v>
       </c>
-      <c r="P1" s="272"/>
+      <c r="P1" s="282"/>
       <c r="Q1" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="270" t="s">
+      <c r="R1" s="280" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="272"/>
+      <c r="S1" s="282"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="266"/>
-      <c r="B2" s="266"/>
-      <c r="C2" s="267" t="s">
+      <c r="A2" s="276"/>
+      <c r="B2" s="276"/>
+      <c r="C2" s="277" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="268"/>
-      <c r="E2" s="269"/>
-      <c r="F2" s="270" t="s">
+      <c r="D2" s="278"/>
+      <c r="E2" s="279"/>
+      <c r="F2" s="280" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="271"/>
-      <c r="H2" s="271"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="271"/>
-      <c r="L2" s="271"/>
-      <c r="M2" s="272"/>
+      <c r="G2" s="281"/>
+      <c r="H2" s="281"/>
+      <c r="I2" s="281"/>
+      <c r="J2" s="281"/>
+      <c r="K2" s="281"/>
+      <c r="L2" s="281"/>
+      <c r="M2" s="282"/>
       <c r="N2" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="O2" s="273">
+      <c r="O2" s="283">
         <v>45827</v>
       </c>
-      <c r="P2" s="274"/>
+      <c r="P2" s="284"/>
       <c r="Q2" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="R2" s="275"/>
-      <c r="S2" s="276"/>
+      <c r="R2" s="285"/>
+      <c r="S2" s="286"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="61"/>
@@ -13994,33 +15308,33 @@
       <c r="B4" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="267" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="257" t="s">
+      <c r="D4" s="268"/>
+      <c r="E4" s="268"/>
+      <c r="F4" s="268"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="267" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="M4" s="259"/>
-      <c r="N4" s="257" t="s">
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
+      <c r="M4" s="269"/>
+      <c r="N4" s="267" t="s">
         <v>66</v>
       </c>
-      <c r="O4" s="258"/>
-      <c r="P4" s="259"/>
+      <c r="O4" s="268"/>
+      <c r="P4" s="269"/>
       <c r="Q4" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="R4" s="257" t="s">
+      <c r="R4" s="267" t="s">
         <v>68</v>
       </c>
-      <c r="S4" s="259"/>
+      <c r="S4" s="269"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="65">
@@ -14029,31 +15343,31 @@
       <c r="B5" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="270" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260" t="s">
-        <v>128</v>
-      </c>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
-      <c r="M5" s="260"/>
-      <c r="N5" s="261" t="s">
+      <c r="D5" s="270"/>
+      <c r="E5" s="270"/>
+      <c r="F5" s="270"/>
+      <c r="G5" s="270"/>
+      <c r="H5" s="270" t="s">
+        <v>127</v>
+      </c>
+      <c r="I5" s="270"/>
+      <c r="J5" s="270"/>
+      <c r="K5" s="270"/>
+      <c r="L5" s="270"/>
+      <c r="M5" s="270"/>
+      <c r="N5" s="271" t="s">
         <v>115</v>
       </c>
-      <c r="O5" s="262"/>
-      <c r="P5" s="263"/>
-      <c r="Q5" s="304">
+      <c r="O5" s="272"/>
+      <c r="P5" s="273"/>
+      <c r="Q5" s="91">
         <v>45827</v>
       </c>
-      <c r="R5" s="264"/>
-      <c r="S5" s="265"/>
+      <c r="R5" s="274"/>
+      <c r="S5" s="275"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="67">
@@ -14062,1000 +15376,1188 @@
       <c r="B6" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="260" t="s">
+      <c r="C6" s="270" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="260"/>
-      <c r="E6" s="260"/>
-      <c r="F6" s="260"/>
-      <c r="G6" s="260"/>
-      <c r="H6" s="260" t="s">
-        <v>128</v>
-      </c>
-      <c r="I6" s="260"/>
-      <c r="J6" s="260"/>
-      <c r="K6" s="260"/>
-      <c r="L6" s="260"/>
-      <c r="M6" s="260"/>
-      <c r="N6" s="261" t="s">
+      <c r="D6" s="270"/>
+      <c r="E6" s="270"/>
+      <c r="F6" s="270"/>
+      <c r="G6" s="270"/>
+      <c r="H6" s="270" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" s="270"/>
+      <c r="J6" s="270"/>
+      <c r="K6" s="270"/>
+      <c r="L6" s="270"/>
+      <c r="M6" s="270"/>
+      <c r="N6" s="271" t="s">
         <v>116</v>
       </c>
-      <c r="O6" s="262"/>
-      <c r="P6" s="263"/>
+      <c r="O6" s="272"/>
+      <c r="P6" s="273"/>
       <c r="Q6" s="69">
         <v>45827</v>
       </c>
-      <c r="R6" s="256"/>
-      <c r="S6" s="256"/>
+      <c r="R6" s="291"/>
+      <c r="S6" s="291"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="67"/>
       <c r="B7" s="67"/>
-      <c r="C7" s="249"/>
-      <c r="D7" s="249"/>
-      <c r="E7" s="249"/>
-      <c r="F7" s="249"/>
-      <c r="G7" s="249"/>
-      <c r="H7" s="249"/>
-      <c r="I7" s="249"/>
-      <c r="J7" s="249"/>
-      <c r="K7" s="249"/>
-      <c r="L7" s="249"/>
-      <c r="M7" s="249"/>
-      <c r="N7" s="253"/>
-      <c r="O7" s="254"/>
-      <c r="P7" s="255"/>
+      <c r="C7" s="287"/>
+      <c r="D7" s="287"/>
+      <c r="E7" s="287"/>
+      <c r="F7" s="287"/>
+      <c r="G7" s="287"/>
+      <c r="H7" s="287"/>
+      <c r="I7" s="287"/>
+      <c r="J7" s="287"/>
+      <c r="K7" s="287"/>
+      <c r="L7" s="287"/>
+      <c r="M7" s="287"/>
+      <c r="N7" s="288"/>
+      <c r="O7" s="289"/>
+      <c r="P7" s="290"/>
       <c r="Q7" s="69"/>
-      <c r="R7" s="256"/>
-      <c r="S7" s="256"/>
+      <c r="R7" s="291"/>
+      <c r="S7" s="291"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="67"/>
       <c r="B8" s="67"/>
-      <c r="C8" s="249"/>
-      <c r="D8" s="249"/>
-      <c r="E8" s="249"/>
-      <c r="F8" s="249"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="249"/>
-      <c r="K8" s="249"/>
-      <c r="L8" s="249"/>
-      <c r="M8" s="249"/>
-      <c r="N8" s="253"/>
-      <c r="O8" s="254"/>
-      <c r="P8" s="255"/>
+      <c r="C8" s="287"/>
+      <c r="D8" s="287"/>
+      <c r="E8" s="287"/>
+      <c r="F8" s="287"/>
+      <c r="G8" s="287"/>
+      <c r="H8" s="287"/>
+      <c r="I8" s="287"/>
+      <c r="J8" s="287"/>
+      <c r="K8" s="287"/>
+      <c r="L8" s="287"/>
+      <c r="M8" s="287"/>
+      <c r="N8" s="288"/>
+      <c r="O8" s="289"/>
+      <c r="P8" s="290"/>
       <c r="Q8" s="69"/>
-      <c r="R8" s="256"/>
-      <c r="S8" s="256"/>
+      <c r="R8" s="291"/>
+      <c r="S8" s="291"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="67"/>
       <c r="B9" s="67"/>
-      <c r="C9" s="249"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
-      <c r="M9" s="249"/>
-      <c r="N9" s="253"/>
-      <c r="O9" s="254"/>
-      <c r="P9" s="255"/>
+      <c r="C9" s="287"/>
+      <c r="D9" s="287"/>
+      <c r="E9" s="287"/>
+      <c r="F9" s="287"/>
+      <c r="G9" s="287"/>
+      <c r="H9" s="287"/>
+      <c r="I9" s="287"/>
+      <c r="J9" s="287"/>
+      <c r="K9" s="287"/>
+      <c r="L9" s="287"/>
+      <c r="M9" s="287"/>
+      <c r="N9" s="288"/>
+      <c r="O9" s="289"/>
+      <c r="P9" s="290"/>
       <c r="Q9" s="67"/>
-      <c r="R9" s="256"/>
-      <c r="S9" s="256"/>
+      <c r="R9" s="291"/>
+      <c r="S9" s="291"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="67"/>
       <c r="B10" s="67"/>
-      <c r="C10" s="249"/>
-      <c r="D10" s="249"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="250"/>
-      <c r="I10" s="251"/>
-      <c r="J10" s="251"/>
-      <c r="K10" s="251"/>
-      <c r="L10" s="251"/>
-      <c r="M10" s="252"/>
-      <c r="N10" s="253"/>
-      <c r="O10" s="254"/>
-      <c r="P10" s="255"/>
+      <c r="C10" s="287"/>
+      <c r="D10" s="287"/>
+      <c r="E10" s="287"/>
+      <c r="F10" s="287"/>
+      <c r="G10" s="287"/>
+      <c r="H10" s="292"/>
+      <c r="I10" s="293"/>
+      <c r="J10" s="293"/>
+      <c r="K10" s="293"/>
+      <c r="L10" s="293"/>
+      <c r="M10" s="294"/>
+      <c r="N10" s="288"/>
+      <c r="O10" s="289"/>
+      <c r="P10" s="290"/>
       <c r="Q10" s="69"/>
-      <c r="R10" s="256"/>
-      <c r="S10" s="256"/>
+      <c r="R10" s="291"/>
+      <c r="S10" s="291"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="67"/>
       <c r="B11" s="67"/>
-      <c r="C11" s="249"/>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="250"/>
-      <c r="I11" s="251"/>
-      <c r="J11" s="251"/>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
-      <c r="M11" s="252"/>
-      <c r="N11" s="253"/>
-      <c r="O11" s="254"/>
-      <c r="P11" s="255"/>
+      <c r="C11" s="287"/>
+      <c r="D11" s="287"/>
+      <c r="E11" s="287"/>
+      <c r="F11" s="287"/>
+      <c r="G11" s="287"/>
+      <c r="H11" s="292"/>
+      <c r="I11" s="293"/>
+      <c r="J11" s="293"/>
+      <c r="K11" s="293"/>
+      <c r="L11" s="293"/>
+      <c r="M11" s="294"/>
+      <c r="N11" s="288"/>
+      <c r="O11" s="289"/>
+      <c r="P11" s="290"/>
       <c r="Q11" s="67"/>
-      <c r="R11" s="256"/>
-      <c r="S11" s="256"/>
+      <c r="R11" s="291"/>
+      <c r="S11" s="291"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="67"/>
       <c r="B12" s="67"/>
-      <c r="C12" s="249"/>
-      <c r="D12" s="249"/>
-      <c r="E12" s="249"/>
-      <c r="F12" s="249"/>
-      <c r="G12" s="249"/>
-      <c r="H12" s="250"/>
-      <c r="I12" s="251"/>
-      <c r="J12" s="251"/>
-      <c r="K12" s="251"/>
-      <c r="L12" s="251"/>
-      <c r="M12" s="252"/>
-      <c r="N12" s="253"/>
-      <c r="O12" s="254"/>
-      <c r="P12" s="255"/>
+      <c r="C12" s="287"/>
+      <c r="D12" s="287"/>
+      <c r="E12" s="287"/>
+      <c r="F12" s="287"/>
+      <c r="G12" s="287"/>
+      <c r="H12" s="292"/>
+      <c r="I12" s="293"/>
+      <c r="J12" s="293"/>
+      <c r="K12" s="293"/>
+      <c r="L12" s="293"/>
+      <c r="M12" s="294"/>
+      <c r="N12" s="288"/>
+      <c r="O12" s="289"/>
+      <c r="P12" s="290"/>
       <c r="Q12" s="67"/>
-      <c r="R12" s="256"/>
-      <c r="S12" s="256"/>
+      <c r="R12" s="291"/>
+      <c r="S12" s="291"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="67"/>
       <c r="B13" s="67"/>
-      <c r="C13" s="249"/>
-      <c r="D13" s="249"/>
-      <c r="E13" s="249"/>
-      <c r="F13" s="249"/>
-      <c r="G13" s="249"/>
-      <c r="H13" s="250"/>
-      <c r="I13" s="251"/>
-      <c r="J13" s="251"/>
-      <c r="K13" s="251"/>
-      <c r="L13" s="251"/>
-      <c r="M13" s="252"/>
-      <c r="N13" s="253"/>
-      <c r="O13" s="254"/>
-      <c r="P13" s="255"/>
+      <c r="C13" s="287"/>
+      <c r="D13" s="287"/>
+      <c r="E13" s="287"/>
+      <c r="F13" s="287"/>
+      <c r="G13" s="287"/>
+      <c r="H13" s="292"/>
+      <c r="I13" s="293"/>
+      <c r="J13" s="293"/>
+      <c r="K13" s="293"/>
+      <c r="L13" s="293"/>
+      <c r="M13" s="294"/>
+      <c r="N13" s="288"/>
+      <c r="O13" s="289"/>
+      <c r="P13" s="290"/>
       <c r="Q13" s="67"/>
-      <c r="R13" s="256"/>
-      <c r="S13" s="256"/>
+      <c r="R13" s="291"/>
+      <c r="S13" s="291"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="67"/>
       <c r="B14" s="67"/>
-      <c r="C14" s="249"/>
-      <c r="D14" s="249"/>
-      <c r="E14" s="249"/>
-      <c r="F14" s="249"/>
-      <c r="G14" s="249"/>
-      <c r="H14" s="250"/>
-      <c r="I14" s="251"/>
-      <c r="J14" s="251"/>
-      <c r="K14" s="251"/>
-      <c r="L14" s="251"/>
-      <c r="M14" s="252"/>
-      <c r="N14" s="253"/>
-      <c r="O14" s="254"/>
-      <c r="P14" s="255"/>
+      <c r="C14" s="287"/>
+      <c r="D14" s="287"/>
+      <c r="E14" s="287"/>
+      <c r="F14" s="287"/>
+      <c r="G14" s="287"/>
+      <c r="H14" s="292"/>
+      <c r="I14" s="293"/>
+      <c r="J14" s="293"/>
+      <c r="K14" s="293"/>
+      <c r="L14" s="293"/>
+      <c r="M14" s="294"/>
+      <c r="N14" s="288"/>
+      <c r="O14" s="289"/>
+      <c r="P14" s="290"/>
       <c r="Q14" s="67"/>
-      <c r="R14" s="256"/>
-      <c r="S14" s="256"/>
+      <c r="R14" s="291"/>
+      <c r="S14" s="291"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="67"/>
       <c r="B15" s="67"/>
-      <c r="C15" s="249"/>
-      <c r="D15" s="249"/>
-      <c r="E15" s="249"/>
-      <c r="F15" s="249"/>
-      <c r="G15" s="249"/>
-      <c r="H15" s="250"/>
-      <c r="I15" s="251"/>
-      <c r="J15" s="251"/>
-      <c r="K15" s="251"/>
-      <c r="L15" s="251"/>
-      <c r="M15" s="252"/>
-      <c r="N15" s="253"/>
-      <c r="O15" s="254"/>
-      <c r="P15" s="255"/>
+      <c r="C15" s="287"/>
+      <c r="D15" s="287"/>
+      <c r="E15" s="287"/>
+      <c r="F15" s="287"/>
+      <c r="G15" s="287"/>
+      <c r="H15" s="292"/>
+      <c r="I15" s="293"/>
+      <c r="J15" s="293"/>
+      <c r="K15" s="293"/>
+      <c r="L15" s="293"/>
+      <c r="M15" s="294"/>
+      <c r="N15" s="288"/>
+      <c r="O15" s="289"/>
+      <c r="P15" s="290"/>
       <c r="Q15" s="67"/>
-      <c r="R15" s="256"/>
-      <c r="S15" s="256"/>
+      <c r="R15" s="291"/>
+      <c r="S15" s="291"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="67"/>
       <c r="B16" s="67"/>
-      <c r="C16" s="249"/>
-      <c r="D16" s="249"/>
-      <c r="E16" s="249"/>
-      <c r="F16" s="249"/>
-      <c r="G16" s="249"/>
-      <c r="H16" s="250"/>
-      <c r="I16" s="251"/>
-      <c r="J16" s="251"/>
-      <c r="K16" s="251"/>
-      <c r="L16" s="251"/>
-      <c r="M16" s="252"/>
-      <c r="N16" s="253"/>
-      <c r="O16" s="254"/>
-      <c r="P16" s="255"/>
+      <c r="C16" s="287"/>
+      <c r="D16" s="287"/>
+      <c r="E16" s="287"/>
+      <c r="F16" s="287"/>
+      <c r="G16" s="287"/>
+      <c r="H16" s="292"/>
+      <c r="I16" s="293"/>
+      <c r="J16" s="293"/>
+      <c r="K16" s="293"/>
+      <c r="L16" s="293"/>
+      <c r="M16" s="294"/>
+      <c r="N16" s="288"/>
+      <c r="O16" s="289"/>
+      <c r="P16" s="290"/>
       <c r="Q16" s="67"/>
-      <c r="R16" s="256"/>
-      <c r="S16" s="256"/>
+      <c r="R16" s="291"/>
+      <c r="S16" s="291"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="67"/>
       <c r="B17" s="67"/>
-      <c r="C17" s="249"/>
-      <c r="D17" s="249"/>
-      <c r="E17" s="249"/>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="251"/>
-      <c r="J17" s="251"/>
-      <c r="K17" s="251"/>
-      <c r="L17" s="251"/>
-      <c r="M17" s="252"/>
-      <c r="N17" s="253"/>
-      <c r="O17" s="254"/>
-      <c r="P17" s="255"/>
+      <c r="C17" s="287"/>
+      <c r="D17" s="287"/>
+      <c r="E17" s="287"/>
+      <c r="F17" s="287"/>
+      <c r="G17" s="287"/>
+      <c r="H17" s="292"/>
+      <c r="I17" s="293"/>
+      <c r="J17" s="293"/>
+      <c r="K17" s="293"/>
+      <c r="L17" s="293"/>
+      <c r="M17" s="294"/>
+      <c r="N17" s="288"/>
+      <c r="O17" s="289"/>
+      <c r="P17" s="290"/>
       <c r="Q17" s="67"/>
-      <c r="R17" s="256"/>
-      <c r="S17" s="256"/>
+      <c r="R17" s="291"/>
+      <c r="S17" s="291"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="67"/>
       <c r="B18" s="67"/>
-      <c r="C18" s="249"/>
-      <c r="D18" s="249"/>
-      <c r="E18" s="249"/>
-      <c r="F18" s="249"/>
-      <c r="G18" s="249"/>
-      <c r="H18" s="250"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
-      <c r="M18" s="252"/>
-      <c r="N18" s="253"/>
-      <c r="O18" s="254"/>
-      <c r="P18" s="255"/>
+      <c r="C18" s="287"/>
+      <c r="D18" s="287"/>
+      <c r="E18" s="287"/>
+      <c r="F18" s="287"/>
+      <c r="G18" s="287"/>
+      <c r="H18" s="292"/>
+      <c r="I18" s="293"/>
+      <c r="J18" s="293"/>
+      <c r="K18" s="293"/>
+      <c r="L18" s="293"/>
+      <c r="M18" s="294"/>
+      <c r="N18" s="288"/>
+      <c r="O18" s="289"/>
+      <c r="P18" s="290"/>
       <c r="Q18" s="67"/>
-      <c r="R18" s="256"/>
-      <c r="S18" s="256"/>
+      <c r="R18" s="291"/>
+      <c r="S18" s="291"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="67"/>
       <c r="B19" s="67"/>
-      <c r="C19" s="249"/>
-      <c r="D19" s="249"/>
-      <c r="E19" s="249"/>
-      <c r="F19" s="249"/>
-      <c r="G19" s="249"/>
-      <c r="H19" s="250"/>
-      <c r="I19" s="251"/>
-      <c r="J19" s="251"/>
-      <c r="K19" s="251"/>
-      <c r="L19" s="251"/>
-      <c r="M19" s="252"/>
-      <c r="N19" s="253"/>
-      <c r="O19" s="254"/>
-      <c r="P19" s="255"/>
+      <c r="C19" s="287"/>
+      <c r="D19" s="287"/>
+      <c r="E19" s="287"/>
+      <c r="F19" s="287"/>
+      <c r="G19" s="287"/>
+      <c r="H19" s="292"/>
+      <c r="I19" s="293"/>
+      <c r="J19" s="293"/>
+      <c r="K19" s="293"/>
+      <c r="L19" s="293"/>
+      <c r="M19" s="294"/>
+      <c r="N19" s="288"/>
+      <c r="O19" s="289"/>
+      <c r="P19" s="290"/>
       <c r="Q19" s="67"/>
-      <c r="R19" s="256"/>
-      <c r="S19" s="256"/>
+      <c r="R19" s="291"/>
+      <c r="S19" s="291"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="67"/>
       <c r="B20" s="67"/>
-      <c r="C20" s="249"/>
-      <c r="D20" s="249"/>
-      <c r="E20" s="249"/>
-      <c r="F20" s="249"/>
-      <c r="G20" s="249"/>
-      <c r="H20" s="250"/>
-      <c r="I20" s="251"/>
-      <c r="J20" s="251"/>
-      <c r="K20" s="251"/>
-      <c r="L20" s="251"/>
-      <c r="M20" s="252"/>
-      <c r="N20" s="253"/>
-      <c r="O20" s="254"/>
-      <c r="P20" s="255"/>
+      <c r="C20" s="287"/>
+      <c r="D20" s="287"/>
+      <c r="E20" s="287"/>
+      <c r="F20" s="287"/>
+      <c r="G20" s="287"/>
+      <c r="H20" s="292"/>
+      <c r="I20" s="293"/>
+      <c r="J20" s="293"/>
+      <c r="K20" s="293"/>
+      <c r="L20" s="293"/>
+      <c r="M20" s="294"/>
+      <c r="N20" s="288"/>
+      <c r="O20" s="289"/>
+      <c r="P20" s="290"/>
       <c r="Q20" s="67"/>
-      <c r="R20" s="256"/>
-      <c r="S20" s="256"/>
+      <c r="R20" s="291"/>
+      <c r="S20" s="291"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="67"/>
       <c r="B21" s="67"/>
-      <c r="C21" s="249"/>
-      <c r="D21" s="249"/>
-      <c r="E21" s="249"/>
-      <c r="F21" s="249"/>
-      <c r="G21" s="249"/>
-      <c r="H21" s="250"/>
-      <c r="I21" s="251"/>
-      <c r="J21" s="251"/>
-      <c r="K21" s="251"/>
-      <c r="L21" s="251"/>
-      <c r="M21" s="252"/>
-      <c r="N21" s="253"/>
-      <c r="O21" s="254"/>
-      <c r="P21" s="255"/>
+      <c r="C21" s="287"/>
+      <c r="D21" s="287"/>
+      <c r="E21" s="287"/>
+      <c r="F21" s="287"/>
+      <c r="G21" s="287"/>
+      <c r="H21" s="292"/>
+      <c r="I21" s="293"/>
+      <c r="J21" s="293"/>
+      <c r="K21" s="293"/>
+      <c r="L21" s="293"/>
+      <c r="M21" s="294"/>
+      <c r="N21" s="288"/>
+      <c r="O21" s="289"/>
+      <c r="P21" s="290"/>
       <c r="Q21" s="67"/>
-      <c r="R21" s="256"/>
-      <c r="S21" s="256"/>
+      <c r="R21" s="291"/>
+      <c r="S21" s="291"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="67"/>
       <c r="B22" s="67"/>
-      <c r="C22" s="249"/>
-      <c r="D22" s="249"/>
-      <c r="E22" s="249"/>
-      <c r="F22" s="249"/>
-      <c r="G22" s="249"/>
-      <c r="H22" s="250"/>
-      <c r="I22" s="251"/>
-      <c r="J22" s="251"/>
-      <c r="K22" s="251"/>
-      <c r="L22" s="251"/>
-      <c r="M22" s="252"/>
-      <c r="N22" s="253"/>
-      <c r="O22" s="254"/>
-      <c r="P22" s="255"/>
+      <c r="C22" s="287"/>
+      <c r="D22" s="287"/>
+      <c r="E22" s="287"/>
+      <c r="F22" s="287"/>
+      <c r="G22" s="287"/>
+      <c r="H22" s="292"/>
+      <c r="I22" s="293"/>
+      <c r="J22" s="293"/>
+      <c r="K22" s="293"/>
+      <c r="L22" s="293"/>
+      <c r="M22" s="294"/>
+      <c r="N22" s="288"/>
+      <c r="O22" s="289"/>
+      <c r="P22" s="290"/>
       <c r="Q22" s="67"/>
-      <c r="R22" s="256"/>
-      <c r="S22" s="256"/>
+      <c r="R22" s="291"/>
+      <c r="S22" s="291"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="67"/>
       <c r="B23" s="67"/>
-      <c r="C23" s="249"/>
-      <c r="D23" s="249"/>
-      <c r="E23" s="249"/>
-      <c r="F23" s="249"/>
-      <c r="G23" s="249"/>
-      <c r="H23" s="250"/>
-      <c r="I23" s="251"/>
-      <c r="J23" s="251"/>
-      <c r="K23" s="251"/>
-      <c r="L23" s="251"/>
-      <c r="M23" s="252"/>
-      <c r="N23" s="253"/>
-      <c r="O23" s="254"/>
-      <c r="P23" s="255"/>
+      <c r="C23" s="287"/>
+      <c r="D23" s="287"/>
+      <c r="E23" s="287"/>
+      <c r="F23" s="287"/>
+      <c r="G23" s="287"/>
+      <c r="H23" s="292"/>
+      <c r="I23" s="293"/>
+      <c r="J23" s="293"/>
+      <c r="K23" s="293"/>
+      <c r="L23" s="293"/>
+      <c r="M23" s="294"/>
+      <c r="N23" s="288"/>
+      <c r="O23" s="289"/>
+      <c r="P23" s="290"/>
       <c r="Q23" s="67"/>
-      <c r="R23" s="256"/>
-      <c r="S23" s="256"/>
+      <c r="R23" s="291"/>
+      <c r="S23" s="291"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="67"/>
       <c r="B24" s="67"/>
-      <c r="C24" s="249"/>
-      <c r="D24" s="249"/>
-      <c r="E24" s="249"/>
-      <c r="F24" s="249"/>
-      <c r="G24" s="249"/>
-      <c r="H24" s="250"/>
-      <c r="I24" s="251"/>
-      <c r="J24" s="251"/>
-      <c r="K24" s="251"/>
-      <c r="L24" s="251"/>
-      <c r="M24" s="252"/>
-      <c r="N24" s="253"/>
-      <c r="O24" s="254"/>
-      <c r="P24" s="255"/>
+      <c r="C24" s="287"/>
+      <c r="D24" s="287"/>
+      <c r="E24" s="287"/>
+      <c r="F24" s="287"/>
+      <c r="G24" s="287"/>
+      <c r="H24" s="292"/>
+      <c r="I24" s="293"/>
+      <c r="J24" s="293"/>
+      <c r="K24" s="293"/>
+      <c r="L24" s="293"/>
+      <c r="M24" s="294"/>
+      <c r="N24" s="288"/>
+      <c r="O24" s="289"/>
+      <c r="P24" s="290"/>
       <c r="Q24" s="67"/>
-      <c r="R24" s="256"/>
-      <c r="S24" s="256"/>
+      <c r="R24" s="291"/>
+      <c r="S24" s="291"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="67"/>
       <c r="B25" s="67"/>
-      <c r="C25" s="249"/>
-      <c r="D25" s="249"/>
-      <c r="E25" s="249"/>
-      <c r="F25" s="249"/>
-      <c r="G25" s="249"/>
-      <c r="H25" s="250"/>
-      <c r="I25" s="251"/>
-      <c r="J25" s="251"/>
-      <c r="K25" s="251"/>
-      <c r="L25" s="251"/>
-      <c r="M25" s="252"/>
-      <c r="N25" s="253"/>
-      <c r="O25" s="254"/>
-      <c r="P25" s="255"/>
+      <c r="C25" s="287"/>
+      <c r="D25" s="287"/>
+      <c r="E25" s="287"/>
+      <c r="F25" s="287"/>
+      <c r="G25" s="287"/>
+      <c r="H25" s="292"/>
+      <c r="I25" s="293"/>
+      <c r="J25" s="293"/>
+      <c r="K25" s="293"/>
+      <c r="L25" s="293"/>
+      <c r="M25" s="294"/>
+      <c r="N25" s="288"/>
+      <c r="O25" s="289"/>
+      <c r="P25" s="290"/>
       <c r="Q25" s="67"/>
-      <c r="R25" s="256"/>
-      <c r="S25" s="256"/>
+      <c r="R25" s="291"/>
+      <c r="S25" s="291"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="67"/>
       <c r="B26" s="67"/>
-      <c r="C26" s="249"/>
-      <c r="D26" s="249"/>
-      <c r="E26" s="249"/>
-      <c r="F26" s="249"/>
-      <c r="G26" s="249"/>
-      <c r="H26" s="250"/>
-      <c r="I26" s="251"/>
-      <c r="J26" s="251"/>
-      <c r="K26" s="251"/>
-      <c r="L26" s="251"/>
-      <c r="M26" s="252"/>
-      <c r="N26" s="253"/>
-      <c r="O26" s="254"/>
-      <c r="P26" s="255"/>
+      <c r="C26" s="287"/>
+      <c r="D26" s="287"/>
+      <c r="E26" s="287"/>
+      <c r="F26" s="287"/>
+      <c r="G26" s="287"/>
+      <c r="H26" s="292"/>
+      <c r="I26" s="293"/>
+      <c r="J26" s="293"/>
+      <c r="K26" s="293"/>
+      <c r="L26" s="293"/>
+      <c r="M26" s="294"/>
+      <c r="N26" s="288"/>
+      <c r="O26" s="289"/>
+      <c r="P26" s="290"/>
       <c r="Q26" s="67"/>
-      <c r="R26" s="256"/>
-      <c r="S26" s="256"/>
+      <c r="R26" s="291"/>
+      <c r="S26" s="291"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="67"/>
       <c r="B27" s="67"/>
-      <c r="C27" s="249"/>
-      <c r="D27" s="249"/>
-      <c r="E27" s="249"/>
-      <c r="F27" s="249"/>
-      <c r="G27" s="249"/>
-      <c r="H27" s="250"/>
-      <c r="I27" s="251"/>
-      <c r="J27" s="251"/>
-      <c r="K27" s="251"/>
-      <c r="L27" s="251"/>
-      <c r="M27" s="252"/>
-      <c r="N27" s="253"/>
-      <c r="O27" s="254"/>
-      <c r="P27" s="255"/>
+      <c r="C27" s="287"/>
+      <c r="D27" s="287"/>
+      <c r="E27" s="287"/>
+      <c r="F27" s="287"/>
+      <c r="G27" s="287"/>
+      <c r="H27" s="292"/>
+      <c r="I27" s="293"/>
+      <c r="J27" s="293"/>
+      <c r="K27" s="293"/>
+      <c r="L27" s="293"/>
+      <c r="M27" s="294"/>
+      <c r="N27" s="288"/>
+      <c r="O27" s="289"/>
+      <c r="P27" s="290"/>
       <c r="Q27" s="67"/>
-      <c r="R27" s="256"/>
-      <c r="S27" s="256"/>
+      <c r="R27" s="291"/>
+      <c r="S27" s="291"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="67"/>
       <c r="B28" s="67"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
-      <c r="F28" s="249"/>
-      <c r="G28" s="249"/>
-      <c r="H28" s="250"/>
-      <c r="I28" s="251"/>
-      <c r="J28" s="251"/>
-      <c r="K28" s="251"/>
-      <c r="L28" s="251"/>
-      <c r="M28" s="252"/>
-      <c r="N28" s="253"/>
-      <c r="O28" s="254"/>
-      <c r="P28" s="255"/>
+      <c r="C28" s="287"/>
+      <c r="D28" s="287"/>
+      <c r="E28" s="287"/>
+      <c r="F28" s="287"/>
+      <c r="G28" s="287"/>
+      <c r="H28" s="292"/>
+      <c r="I28" s="293"/>
+      <c r="J28" s="293"/>
+      <c r="K28" s="293"/>
+      <c r="L28" s="293"/>
+      <c r="M28" s="294"/>
+      <c r="N28" s="288"/>
+      <c r="O28" s="289"/>
+      <c r="P28" s="290"/>
       <c r="Q28" s="67"/>
-      <c r="R28" s="256"/>
-      <c r="S28" s="256"/>
+      <c r="R28" s="291"/>
+      <c r="S28" s="291"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="67"/>
       <c r="B29" s="67"/>
-      <c r="C29" s="249"/>
-      <c r="D29" s="249"/>
-      <c r="E29" s="249"/>
-      <c r="F29" s="249"/>
-      <c r="G29" s="249"/>
-      <c r="H29" s="250"/>
-      <c r="I29" s="251"/>
-      <c r="J29" s="251"/>
-      <c r="K29" s="251"/>
-      <c r="L29" s="251"/>
-      <c r="M29" s="252"/>
-      <c r="N29" s="253"/>
-      <c r="O29" s="254"/>
-      <c r="P29" s="255"/>
+      <c r="C29" s="287"/>
+      <c r="D29" s="287"/>
+      <c r="E29" s="287"/>
+      <c r="F29" s="287"/>
+      <c r="G29" s="287"/>
+      <c r="H29" s="292"/>
+      <c r="I29" s="293"/>
+      <c r="J29" s="293"/>
+      <c r="K29" s="293"/>
+      <c r="L29" s="293"/>
+      <c r="M29" s="294"/>
+      <c r="N29" s="288"/>
+      <c r="O29" s="289"/>
+      <c r="P29" s="290"/>
       <c r="Q29" s="67"/>
-      <c r="R29" s="256"/>
-      <c r="S29" s="256"/>
+      <c r="R29" s="291"/>
+      <c r="S29" s="291"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
-      <c r="C30" s="249"/>
-      <c r="D30" s="249"/>
-      <c r="E30" s="249"/>
-      <c r="F30" s="249"/>
-      <c r="G30" s="249"/>
-      <c r="H30" s="250"/>
-      <c r="I30" s="251"/>
-      <c r="J30" s="251"/>
-      <c r="K30" s="251"/>
-      <c r="L30" s="251"/>
-      <c r="M30" s="252"/>
-      <c r="N30" s="253"/>
-      <c r="O30" s="254"/>
-      <c r="P30" s="255"/>
+      <c r="C30" s="287"/>
+      <c r="D30" s="287"/>
+      <c r="E30" s="287"/>
+      <c r="F30" s="287"/>
+      <c r="G30" s="287"/>
+      <c r="H30" s="292"/>
+      <c r="I30" s="293"/>
+      <c r="J30" s="293"/>
+      <c r="K30" s="293"/>
+      <c r="L30" s="293"/>
+      <c r="M30" s="294"/>
+      <c r="N30" s="288"/>
+      <c r="O30" s="289"/>
+      <c r="P30" s="290"/>
       <c r="Q30" s="67"/>
-      <c r="R30" s="256"/>
-      <c r="S30" s="256"/>
+      <c r="R30" s="291"/>
+      <c r="S30" s="291"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="67"/>
       <c r="B31" s="67"/>
-      <c r="C31" s="249"/>
-      <c r="D31" s="249"/>
-      <c r="E31" s="249"/>
-      <c r="F31" s="249"/>
-      <c r="G31" s="249"/>
-      <c r="H31" s="250"/>
-      <c r="I31" s="251"/>
-      <c r="J31" s="251"/>
-      <c r="K31" s="251"/>
-      <c r="L31" s="251"/>
-      <c r="M31" s="252"/>
-      <c r="N31" s="253"/>
-      <c r="O31" s="254"/>
-      <c r="P31" s="255"/>
+      <c r="C31" s="287"/>
+      <c r="D31" s="287"/>
+      <c r="E31" s="287"/>
+      <c r="F31" s="287"/>
+      <c r="G31" s="287"/>
+      <c r="H31" s="292"/>
+      <c r="I31" s="293"/>
+      <c r="J31" s="293"/>
+      <c r="K31" s="293"/>
+      <c r="L31" s="293"/>
+      <c r="M31" s="294"/>
+      <c r="N31" s="288"/>
+      <c r="O31" s="289"/>
+      <c r="P31" s="290"/>
       <c r="Q31" s="67"/>
-      <c r="R31" s="256"/>
-      <c r="S31" s="256"/>
+      <c r="R31" s="291"/>
+      <c r="S31" s="291"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="67"/>
       <c r="B32" s="67"/>
-      <c r="C32" s="249"/>
-      <c r="D32" s="249"/>
-      <c r="E32" s="249"/>
-      <c r="F32" s="249"/>
-      <c r="G32" s="249"/>
-      <c r="H32" s="250"/>
-      <c r="I32" s="251"/>
-      <c r="J32" s="251"/>
-      <c r="K32" s="251"/>
-      <c r="L32" s="251"/>
-      <c r="M32" s="252"/>
-      <c r="N32" s="253"/>
-      <c r="O32" s="254"/>
-      <c r="P32" s="255"/>
+      <c r="C32" s="287"/>
+      <c r="D32" s="287"/>
+      <c r="E32" s="287"/>
+      <c r="F32" s="287"/>
+      <c r="G32" s="287"/>
+      <c r="H32" s="292"/>
+      <c r="I32" s="293"/>
+      <c r="J32" s="293"/>
+      <c r="K32" s="293"/>
+      <c r="L32" s="293"/>
+      <c r="M32" s="294"/>
+      <c r="N32" s="288"/>
+      <c r="O32" s="289"/>
+      <c r="P32" s="290"/>
       <c r="Q32" s="67"/>
-      <c r="R32" s="256"/>
-      <c r="S32" s="256"/>
+      <c r="R32" s="291"/>
+      <c r="S32" s="291"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="67"/>
       <c r="B33" s="67"/>
-      <c r="C33" s="249"/>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="250"/>
-      <c r="I33" s="251"/>
-      <c r="J33" s="251"/>
-      <c r="K33" s="251"/>
-      <c r="L33" s="251"/>
-      <c r="M33" s="252"/>
-      <c r="N33" s="253"/>
-      <c r="O33" s="254"/>
-      <c r="P33" s="255"/>
+      <c r="C33" s="287"/>
+      <c r="D33" s="287"/>
+      <c r="E33" s="287"/>
+      <c r="F33" s="287"/>
+      <c r="G33" s="287"/>
+      <c r="H33" s="292"/>
+      <c r="I33" s="293"/>
+      <c r="J33" s="293"/>
+      <c r="K33" s="293"/>
+      <c r="L33" s="293"/>
+      <c r="M33" s="294"/>
+      <c r="N33" s="288"/>
+      <c r="O33" s="289"/>
+      <c r="P33" s="290"/>
       <c r="Q33" s="67"/>
-      <c r="R33" s="256"/>
-      <c r="S33" s="256"/>
+      <c r="R33" s="291"/>
+      <c r="S33" s="291"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="67"/>
       <c r="B34" s="67"/>
-      <c r="C34" s="249"/>
-      <c r="D34" s="249"/>
-      <c r="E34" s="249"/>
-      <c r="F34" s="249"/>
-      <c r="G34" s="249"/>
-      <c r="H34" s="250"/>
-      <c r="I34" s="251"/>
-      <c r="J34" s="251"/>
-      <c r="K34" s="251"/>
-      <c r="L34" s="251"/>
-      <c r="M34" s="252"/>
-      <c r="N34" s="253"/>
-      <c r="O34" s="254"/>
-      <c r="P34" s="255"/>
+      <c r="C34" s="287"/>
+      <c r="D34" s="287"/>
+      <c r="E34" s="287"/>
+      <c r="F34" s="287"/>
+      <c r="G34" s="287"/>
+      <c r="H34" s="292"/>
+      <c r="I34" s="293"/>
+      <c r="J34" s="293"/>
+      <c r="K34" s="293"/>
+      <c r="L34" s="293"/>
+      <c r="M34" s="294"/>
+      <c r="N34" s="288"/>
+      <c r="O34" s="289"/>
+      <c r="P34" s="290"/>
       <c r="Q34" s="67"/>
-      <c r="R34" s="256"/>
-      <c r="S34" s="256"/>
+      <c r="R34" s="291"/>
+      <c r="S34" s="291"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="67"/>
       <c r="B35" s="67"/>
-      <c r="C35" s="249"/>
-      <c r="D35" s="249"/>
-      <c r="E35" s="249"/>
-      <c r="F35" s="249"/>
-      <c r="G35" s="249"/>
-      <c r="H35" s="250"/>
-      <c r="I35" s="251"/>
-      <c r="J35" s="251"/>
-      <c r="K35" s="251"/>
-      <c r="L35" s="251"/>
-      <c r="M35" s="252"/>
-      <c r="N35" s="253"/>
-      <c r="O35" s="254"/>
-      <c r="P35" s="255"/>
+      <c r="C35" s="287"/>
+      <c r="D35" s="287"/>
+      <c r="E35" s="287"/>
+      <c r="F35" s="287"/>
+      <c r="G35" s="287"/>
+      <c r="H35" s="292"/>
+      <c r="I35" s="293"/>
+      <c r="J35" s="293"/>
+      <c r="K35" s="293"/>
+      <c r="L35" s="293"/>
+      <c r="M35" s="294"/>
+      <c r="N35" s="288"/>
+      <c r="O35" s="289"/>
+      <c r="P35" s="290"/>
       <c r="Q35" s="67"/>
-      <c r="R35" s="256"/>
-      <c r="S35" s="256"/>
+      <c r="R35" s="291"/>
+      <c r="S35" s="291"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="67"/>
       <c r="B36" s="67"/>
-      <c r="C36" s="249"/>
-      <c r="D36" s="249"/>
-      <c r="E36" s="249"/>
-      <c r="F36" s="249"/>
-      <c r="G36" s="249"/>
-      <c r="H36" s="250"/>
-      <c r="I36" s="251"/>
-      <c r="J36" s="251"/>
-      <c r="K36" s="251"/>
-      <c r="L36" s="251"/>
-      <c r="M36" s="252"/>
-      <c r="N36" s="253"/>
-      <c r="O36" s="254"/>
-      <c r="P36" s="255"/>
+      <c r="C36" s="287"/>
+      <c r="D36" s="287"/>
+      <c r="E36" s="287"/>
+      <c r="F36" s="287"/>
+      <c r="G36" s="287"/>
+      <c r="H36" s="292"/>
+      <c r="I36" s="293"/>
+      <c r="J36" s="293"/>
+      <c r="K36" s="293"/>
+      <c r="L36" s="293"/>
+      <c r="M36" s="294"/>
+      <c r="N36" s="288"/>
+      <c r="O36" s="289"/>
+      <c r="P36" s="290"/>
       <c r="Q36" s="67"/>
-      <c r="R36" s="256"/>
-      <c r="S36" s="256"/>
+      <c r="R36" s="291"/>
+      <c r="S36" s="291"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="67"/>
       <c r="B37" s="67"/>
-      <c r="C37" s="249"/>
-      <c r="D37" s="249"/>
-      <c r="E37" s="249"/>
-      <c r="F37" s="249"/>
-      <c r="G37" s="249"/>
-      <c r="H37" s="250"/>
-      <c r="I37" s="251"/>
-      <c r="J37" s="251"/>
-      <c r="K37" s="251"/>
-      <c r="L37" s="251"/>
-      <c r="M37" s="252"/>
-      <c r="N37" s="253"/>
-      <c r="O37" s="254"/>
-      <c r="P37" s="255"/>
+      <c r="C37" s="287"/>
+      <c r="D37" s="287"/>
+      <c r="E37" s="287"/>
+      <c r="F37" s="287"/>
+      <c r="G37" s="287"/>
+      <c r="H37" s="292"/>
+      <c r="I37" s="293"/>
+      <c r="J37" s="293"/>
+      <c r="K37" s="293"/>
+      <c r="L37" s="293"/>
+      <c r="M37" s="294"/>
+      <c r="N37" s="288"/>
+      <c r="O37" s="289"/>
+      <c r="P37" s="290"/>
       <c r="Q37" s="67"/>
-      <c r="R37" s="256"/>
-      <c r="S37" s="256"/>
+      <c r="R37" s="291"/>
+      <c r="S37" s="291"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="67"/>
       <c r="B38" s="67"/>
-      <c r="C38" s="249"/>
-      <c r="D38" s="249"/>
-      <c r="E38" s="249"/>
-      <c r="F38" s="249"/>
-      <c r="G38" s="249"/>
-      <c r="H38" s="250"/>
-      <c r="I38" s="251"/>
-      <c r="J38" s="251"/>
-      <c r="K38" s="251"/>
-      <c r="L38" s="251"/>
-      <c r="M38" s="252"/>
-      <c r="N38" s="253"/>
-      <c r="O38" s="254"/>
-      <c r="P38" s="255"/>
+      <c r="C38" s="287"/>
+      <c r="D38" s="287"/>
+      <c r="E38" s="287"/>
+      <c r="F38" s="287"/>
+      <c r="G38" s="287"/>
+      <c r="H38" s="292"/>
+      <c r="I38" s="293"/>
+      <c r="J38" s="293"/>
+      <c r="K38" s="293"/>
+      <c r="L38" s="293"/>
+      <c r="M38" s="294"/>
+      <c r="N38" s="288"/>
+      <c r="O38" s="289"/>
+      <c r="P38" s="290"/>
       <c r="Q38" s="67"/>
-      <c r="R38" s="256"/>
-      <c r="S38" s="256"/>
+      <c r="R38" s="291"/>
+      <c r="S38" s="291"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="67"/>
       <c r="B39" s="67"/>
-      <c r="C39" s="249"/>
-      <c r="D39" s="249"/>
-      <c r="E39" s="249"/>
-      <c r="F39" s="249"/>
-      <c r="G39" s="249"/>
-      <c r="H39" s="250"/>
-      <c r="I39" s="251"/>
-      <c r="J39" s="251"/>
-      <c r="K39" s="251"/>
-      <c r="L39" s="251"/>
-      <c r="M39" s="252"/>
-      <c r="N39" s="253"/>
-      <c r="O39" s="254"/>
-      <c r="P39" s="255"/>
+      <c r="C39" s="287"/>
+      <c r="D39" s="287"/>
+      <c r="E39" s="287"/>
+      <c r="F39" s="287"/>
+      <c r="G39" s="287"/>
+      <c r="H39" s="292"/>
+      <c r="I39" s="293"/>
+      <c r="J39" s="293"/>
+      <c r="K39" s="293"/>
+      <c r="L39" s="293"/>
+      <c r="M39" s="294"/>
+      <c r="N39" s="288"/>
+      <c r="O39" s="289"/>
+      <c r="P39" s="290"/>
       <c r="Q39" s="67"/>
-      <c r="R39" s="256"/>
-      <c r="S39" s="256"/>
+      <c r="R39" s="291"/>
+      <c r="S39" s="291"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="67"/>
       <c r="B40" s="67"/>
-      <c r="C40" s="249"/>
-      <c r="D40" s="249"/>
-      <c r="E40" s="249"/>
-      <c r="F40" s="249"/>
-      <c r="G40" s="249"/>
-      <c r="H40" s="250"/>
-      <c r="I40" s="251"/>
-      <c r="J40" s="251"/>
-      <c r="K40" s="251"/>
-      <c r="L40" s="251"/>
-      <c r="M40" s="252"/>
-      <c r="N40" s="253"/>
-      <c r="O40" s="254"/>
-      <c r="P40" s="255"/>
+      <c r="C40" s="287"/>
+      <c r="D40" s="287"/>
+      <c r="E40" s="287"/>
+      <c r="F40" s="287"/>
+      <c r="G40" s="287"/>
+      <c r="H40" s="292"/>
+      <c r="I40" s="293"/>
+      <c r="J40" s="293"/>
+      <c r="K40" s="293"/>
+      <c r="L40" s="293"/>
+      <c r="M40" s="294"/>
+      <c r="N40" s="288"/>
+      <c r="O40" s="289"/>
+      <c r="P40" s="290"/>
       <c r="Q40" s="67"/>
-      <c r="R40" s="256"/>
-      <c r="S40" s="256"/>
+      <c r="R40" s="291"/>
+      <c r="S40" s="291"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="67"/>
       <c r="B41" s="67"/>
-      <c r="C41" s="249"/>
-      <c r="D41" s="249"/>
-      <c r="E41" s="249"/>
-      <c r="F41" s="249"/>
-      <c r="G41" s="249"/>
-      <c r="H41" s="250"/>
-      <c r="I41" s="251"/>
-      <c r="J41" s="251"/>
-      <c r="K41" s="251"/>
-      <c r="L41" s="251"/>
-      <c r="M41" s="252"/>
-      <c r="N41" s="253"/>
-      <c r="O41" s="254"/>
-      <c r="P41" s="255"/>
+      <c r="C41" s="287"/>
+      <c r="D41" s="287"/>
+      <c r="E41" s="287"/>
+      <c r="F41" s="287"/>
+      <c r="G41" s="287"/>
+      <c r="H41" s="292"/>
+      <c r="I41" s="293"/>
+      <c r="J41" s="293"/>
+      <c r="K41" s="293"/>
+      <c r="L41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="289"/>
+      <c r="P41" s="290"/>
       <c r="Q41" s="67"/>
-      <c r="R41" s="256"/>
-      <c r="S41" s="256"/>
+      <c r="R41" s="291"/>
+      <c r="S41" s="291"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="67"/>
       <c r="B42" s="67"/>
-      <c r="C42" s="249"/>
-      <c r="D42" s="249"/>
-      <c r="E42" s="249"/>
-      <c r="F42" s="249"/>
-      <c r="G42" s="249"/>
-      <c r="H42" s="250"/>
-      <c r="I42" s="251"/>
-      <c r="J42" s="251"/>
-      <c r="K42" s="251"/>
-      <c r="L42" s="251"/>
-      <c r="M42" s="252"/>
-      <c r="N42" s="253"/>
-      <c r="O42" s="254"/>
-      <c r="P42" s="255"/>
+      <c r="C42" s="287"/>
+      <c r="D42" s="287"/>
+      <c r="E42" s="287"/>
+      <c r="F42" s="287"/>
+      <c r="G42" s="287"/>
+      <c r="H42" s="292"/>
+      <c r="I42" s="293"/>
+      <c r="J42" s="293"/>
+      <c r="K42" s="293"/>
+      <c r="L42" s="293"/>
+      <c r="M42" s="294"/>
+      <c r="N42" s="288"/>
+      <c r="O42" s="289"/>
+      <c r="P42" s="290"/>
       <c r="Q42" s="67"/>
-      <c r="R42" s="256"/>
-      <c r="S42" s="256"/>
+      <c r="R42" s="291"/>
+      <c r="S42" s="291"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="67"/>
       <c r="B43" s="67"/>
-      <c r="C43" s="249"/>
-      <c r="D43" s="249"/>
-      <c r="E43" s="249"/>
-      <c r="F43" s="249"/>
-      <c r="G43" s="249"/>
-      <c r="H43" s="250"/>
-      <c r="I43" s="251"/>
-      <c r="J43" s="251"/>
-      <c r="K43" s="251"/>
-      <c r="L43" s="251"/>
-      <c r="M43" s="252"/>
-      <c r="N43" s="253"/>
-      <c r="O43" s="254"/>
-      <c r="P43" s="255"/>
+      <c r="C43" s="287"/>
+      <c r="D43" s="287"/>
+      <c r="E43" s="287"/>
+      <c r="F43" s="287"/>
+      <c r="G43" s="287"/>
+      <c r="H43" s="292"/>
+      <c r="I43" s="293"/>
+      <c r="J43" s="293"/>
+      <c r="K43" s="293"/>
+      <c r="L43" s="293"/>
+      <c r="M43" s="294"/>
+      <c r="N43" s="288"/>
+      <c r="O43" s="289"/>
+      <c r="P43" s="290"/>
       <c r="Q43" s="67"/>
-      <c r="R43" s="256"/>
-      <c r="S43" s="256"/>
+      <c r="R43" s="291"/>
+      <c r="S43" s="291"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="67"/>
       <c r="B44" s="67"/>
-      <c r="C44" s="249"/>
-      <c r="D44" s="249"/>
-      <c r="E44" s="249"/>
-      <c r="F44" s="249"/>
-      <c r="G44" s="249"/>
-      <c r="H44" s="250"/>
-      <c r="I44" s="251"/>
-      <c r="J44" s="251"/>
-      <c r="K44" s="251"/>
-      <c r="L44" s="251"/>
-      <c r="M44" s="252"/>
-      <c r="N44" s="253"/>
-      <c r="O44" s="254"/>
-      <c r="P44" s="255"/>
+      <c r="C44" s="287"/>
+      <c r="D44" s="287"/>
+      <c r="E44" s="287"/>
+      <c r="F44" s="287"/>
+      <c r="G44" s="287"/>
+      <c r="H44" s="292"/>
+      <c r="I44" s="293"/>
+      <c r="J44" s="293"/>
+      <c r="K44" s="293"/>
+      <c r="L44" s="293"/>
+      <c r="M44" s="294"/>
+      <c r="N44" s="288"/>
+      <c r="O44" s="289"/>
+      <c r="P44" s="290"/>
       <c r="Q44" s="67"/>
-      <c r="R44" s="256"/>
-      <c r="S44" s="256"/>
+      <c r="R44" s="291"/>
+      <c r="S44" s="291"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="67"/>
       <c r="B45" s="67"/>
-      <c r="C45" s="249"/>
-      <c r="D45" s="249"/>
-      <c r="E45" s="249"/>
-      <c r="F45" s="249"/>
-      <c r="G45" s="249"/>
-      <c r="H45" s="250"/>
-      <c r="I45" s="251"/>
-      <c r="J45" s="251"/>
-      <c r="K45" s="251"/>
-      <c r="L45" s="251"/>
-      <c r="M45" s="252"/>
-      <c r="N45" s="253"/>
-      <c r="O45" s="254"/>
-      <c r="P45" s="255"/>
+      <c r="C45" s="287"/>
+      <c r="D45" s="287"/>
+      <c r="E45" s="287"/>
+      <c r="F45" s="287"/>
+      <c r="G45" s="287"/>
+      <c r="H45" s="292"/>
+      <c r="I45" s="293"/>
+      <c r="J45" s="293"/>
+      <c r="K45" s="293"/>
+      <c r="L45" s="293"/>
+      <c r="M45" s="294"/>
+      <c r="N45" s="288"/>
+      <c r="O45" s="289"/>
+      <c r="P45" s="290"/>
       <c r="Q45" s="67"/>
-      <c r="R45" s="256"/>
-      <c r="S45" s="256"/>
+      <c r="R45" s="291"/>
+      <c r="S45" s="291"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="67"/>
       <c r="B46" s="67"/>
-      <c r="C46" s="249"/>
-      <c r="D46" s="249"/>
-      <c r="E46" s="249"/>
-      <c r="F46" s="249"/>
-      <c r="G46" s="249"/>
-      <c r="H46" s="250"/>
-      <c r="I46" s="251"/>
-      <c r="J46" s="251"/>
-      <c r="K46" s="251"/>
-      <c r="L46" s="251"/>
-      <c r="M46" s="252"/>
-      <c r="N46" s="253"/>
-      <c r="O46" s="254"/>
-      <c r="P46" s="255"/>
+      <c r="C46" s="287"/>
+      <c r="D46" s="287"/>
+      <c r="E46" s="287"/>
+      <c r="F46" s="287"/>
+      <c r="G46" s="287"/>
+      <c r="H46" s="292"/>
+      <c r="I46" s="293"/>
+      <c r="J46" s="293"/>
+      <c r="K46" s="293"/>
+      <c r="L46" s="293"/>
+      <c r="M46" s="294"/>
+      <c r="N46" s="288"/>
+      <c r="O46" s="289"/>
+      <c r="P46" s="290"/>
       <c r="Q46" s="67"/>
-      <c r="R46" s="256"/>
-      <c r="S46" s="256"/>
+      <c r="R46" s="291"/>
+      <c r="S46" s="291"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="67"/>
       <c r="B47" s="67"/>
-      <c r="C47" s="249"/>
-      <c r="D47" s="249"/>
-      <c r="E47" s="249"/>
-      <c r="F47" s="249"/>
-      <c r="G47" s="249"/>
-      <c r="H47" s="250"/>
-      <c r="I47" s="251"/>
-      <c r="J47" s="251"/>
-      <c r="K47" s="251"/>
-      <c r="L47" s="251"/>
-      <c r="M47" s="252"/>
-      <c r="N47" s="253"/>
-      <c r="O47" s="254"/>
-      <c r="P47" s="255"/>
+      <c r="C47" s="287"/>
+      <c r="D47" s="287"/>
+      <c r="E47" s="287"/>
+      <c r="F47" s="287"/>
+      <c r="G47" s="287"/>
+      <c r="H47" s="292"/>
+      <c r="I47" s="293"/>
+      <c r="J47" s="293"/>
+      <c r="K47" s="293"/>
+      <c r="L47" s="293"/>
+      <c r="M47" s="294"/>
+      <c r="N47" s="288"/>
+      <c r="O47" s="289"/>
+      <c r="P47" s="290"/>
       <c r="Q47" s="67"/>
-      <c r="R47" s="256"/>
-      <c r="S47" s="256"/>
+      <c r="R47" s="291"/>
+      <c r="S47" s="291"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="67"/>
       <c r="B48" s="67"/>
-      <c r="C48" s="249"/>
-      <c r="D48" s="249"/>
-      <c r="E48" s="249"/>
-      <c r="F48" s="249"/>
-      <c r="G48" s="249"/>
-      <c r="H48" s="250"/>
-      <c r="I48" s="251"/>
-      <c r="J48" s="251"/>
-      <c r="K48" s="251"/>
-      <c r="L48" s="251"/>
-      <c r="M48" s="252"/>
-      <c r="N48" s="253"/>
-      <c r="O48" s="254"/>
-      <c r="P48" s="255"/>
+      <c r="C48" s="287"/>
+      <c r="D48" s="287"/>
+      <c r="E48" s="287"/>
+      <c r="F48" s="287"/>
+      <c r="G48" s="287"/>
+      <c r="H48" s="292"/>
+      <c r="I48" s="293"/>
+      <c r="J48" s="293"/>
+      <c r="K48" s="293"/>
+      <c r="L48" s="293"/>
+      <c r="M48" s="294"/>
+      <c r="N48" s="288"/>
+      <c r="O48" s="289"/>
+      <c r="P48" s="290"/>
       <c r="Q48" s="67"/>
-      <c r="R48" s="256"/>
-      <c r="S48" s="256"/>
+      <c r="R48" s="291"/>
+      <c r="S48" s="291"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="67"/>
       <c r="B49" s="67"/>
-      <c r="C49" s="249"/>
-      <c r="D49" s="249"/>
-      <c r="E49" s="249"/>
-      <c r="F49" s="249"/>
-      <c r="G49" s="249"/>
-      <c r="H49" s="250"/>
-      <c r="I49" s="251"/>
-      <c r="J49" s="251"/>
-      <c r="K49" s="251"/>
-      <c r="L49" s="251"/>
-      <c r="M49" s="252"/>
-      <c r="N49" s="253"/>
-      <c r="O49" s="254"/>
-      <c r="P49" s="255"/>
+      <c r="C49" s="287"/>
+      <c r="D49" s="287"/>
+      <c r="E49" s="287"/>
+      <c r="F49" s="287"/>
+      <c r="G49" s="287"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="293"/>
+      <c r="J49" s="293"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="293"/>
+      <c r="M49" s="294"/>
+      <c r="N49" s="288"/>
+      <c r="O49" s="289"/>
+      <c r="P49" s="290"/>
       <c r="Q49" s="67"/>
-      <c r="R49" s="256"/>
-      <c r="S49" s="256"/>
+      <c r="R49" s="291"/>
+      <c r="S49" s="291"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="67"/>
       <c r="B50" s="67"/>
-      <c r="C50" s="249"/>
-      <c r="D50" s="249"/>
-      <c r="E50" s="249"/>
-      <c r="F50" s="249"/>
-      <c r="G50" s="249"/>
-      <c r="H50" s="250"/>
-      <c r="I50" s="251"/>
-      <c r="J50" s="251"/>
-      <c r="K50" s="251"/>
-      <c r="L50" s="251"/>
-      <c r="M50" s="252"/>
-      <c r="N50" s="253"/>
-      <c r="O50" s="254"/>
-      <c r="P50" s="255"/>
+      <c r="C50" s="287"/>
+      <c r="D50" s="287"/>
+      <c r="E50" s="287"/>
+      <c r="F50" s="287"/>
+      <c r="G50" s="287"/>
+      <c r="H50" s="292"/>
+      <c r="I50" s="293"/>
+      <c r="J50" s="293"/>
+      <c r="K50" s="293"/>
+      <c r="L50" s="293"/>
+      <c r="M50" s="294"/>
+      <c r="N50" s="288"/>
+      <c r="O50" s="289"/>
+      <c r="P50" s="290"/>
       <c r="Q50" s="67"/>
-      <c r="R50" s="256"/>
-      <c r="S50" s="256"/>
+      <c r="R50" s="291"/>
+      <c r="S50" s="291"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="67"/>
       <c r="B51" s="67"/>
-      <c r="C51" s="249"/>
-      <c r="D51" s="249"/>
-      <c r="E51" s="249"/>
-      <c r="F51" s="249"/>
-      <c r="G51" s="249"/>
-      <c r="H51" s="250"/>
-      <c r="I51" s="251"/>
-      <c r="J51" s="251"/>
-      <c r="K51" s="251"/>
-      <c r="L51" s="251"/>
-      <c r="M51" s="252"/>
-      <c r="N51" s="253"/>
-      <c r="O51" s="254"/>
-      <c r="P51" s="255"/>
+      <c r="C51" s="287"/>
+      <c r="D51" s="287"/>
+      <c r="E51" s="287"/>
+      <c r="F51" s="287"/>
+      <c r="G51" s="287"/>
+      <c r="H51" s="292"/>
+      <c r="I51" s="293"/>
+      <c r="J51" s="293"/>
+      <c r="K51" s="293"/>
+      <c r="L51" s="293"/>
+      <c r="M51" s="294"/>
+      <c r="N51" s="288"/>
+      <c r="O51" s="289"/>
+      <c r="P51" s="290"/>
       <c r="Q51" s="67"/>
-      <c r="R51" s="256"/>
-      <c r="S51" s="256"/>
+      <c r="R51" s="291"/>
+      <c r="S51" s="291"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="67"/>
       <c r="B52" s="67"/>
-      <c r="C52" s="249"/>
-      <c r="D52" s="249"/>
-      <c r="E52" s="249"/>
-      <c r="F52" s="249"/>
-      <c r="G52" s="249"/>
-      <c r="H52" s="250"/>
-      <c r="I52" s="251"/>
-      <c r="J52" s="251"/>
-      <c r="K52" s="251"/>
-      <c r="L52" s="251"/>
-      <c r="M52" s="252"/>
-      <c r="N52" s="253"/>
-      <c r="O52" s="254"/>
-      <c r="P52" s="255"/>
+      <c r="C52" s="287"/>
+      <c r="D52" s="287"/>
+      <c r="E52" s="287"/>
+      <c r="F52" s="287"/>
+      <c r="G52" s="287"/>
+      <c r="H52" s="292"/>
+      <c r="I52" s="293"/>
+      <c r="J52" s="293"/>
+      <c r="K52" s="293"/>
+      <c r="L52" s="293"/>
+      <c r="M52" s="294"/>
+      <c r="N52" s="288"/>
+      <c r="O52" s="289"/>
+      <c r="P52" s="290"/>
       <c r="Q52" s="67"/>
-      <c r="R52" s="256"/>
-      <c r="S52" s="256"/>
+      <c r="R52" s="291"/>
+      <c r="S52" s="291"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -15073,194 +16575,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
@@ -15324,21 +16638,21 @@
       <c r="AL1" s="71"/>
       <c r="AM1" s="71"/>
       <c r="AN1" s="71"/>
-      <c r="AO1" s="280" t="s">
+      <c r="AO1" s="298" t="s">
         <v>70</v>
       </c>
-      <c r="AP1" s="280"/>
-      <c r="AQ1" s="280"/>
-      <c r="AR1" s="280"/>
-      <c r="AS1" s="280"/>
-      <c r="AT1" s="281"/>
-      <c r="AU1" s="282"/>
-      <c r="AV1" s="282"/>
-      <c r="AW1" s="282"/>
-      <c r="AX1" s="282"/>
-      <c r="AY1" s="282"/>
-      <c r="AZ1" s="282"/>
-      <c r="BA1" s="282"/>
+      <c r="AP1" s="298"/>
+      <c r="AQ1" s="298"/>
+      <c r="AR1" s="298"/>
+      <c r="AS1" s="298"/>
+      <c r="AT1" s="299"/>
+      <c r="AU1" s="300"/>
+      <c r="AV1" s="300"/>
+      <c r="AW1" s="300"/>
+      <c r="AX1" s="300"/>
+      <c r="AY1" s="300"/>
+      <c r="AZ1" s="300"/>
+      <c r="BA1" s="300"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -15384,54 +16698,54 @@
       <c r="AK4" s="78"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="277" t="s">
+      <c r="A5" s="295" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="278"/>
-      <c r="C5" s="278"/>
-      <c r="D5" s="278"/>
-      <c r="E5" s="278"/>
-      <c r="F5" s="279"/>
-      <c r="G5" s="283" t="s">
+      <c r="B5" s="296"/>
+      <c r="C5" s="296"/>
+      <c r="D5" s="296"/>
+      <c r="E5" s="296"/>
+      <c r="F5" s="297"/>
+      <c r="G5" s="301" t="s">
         <v>118</v>
       </c>
-      <c r="H5" s="284"/>
-      <c r="I5" s="284"/>
-      <c r="J5" s="284"/>
-      <c r="K5" s="284"/>
-      <c r="L5" s="284"/>
-      <c r="M5" s="284"/>
-      <c r="N5" s="284"/>
-      <c r="O5" s="284"/>
-      <c r="P5" s="284"/>
-      <c r="Q5" s="284"/>
-      <c r="R5" s="284"/>
-      <c r="S5" s="285"/>
+      <c r="H5" s="302"/>
+      <c r="I5" s="302"/>
+      <c r="J5" s="302"/>
+      <c r="K5" s="302"/>
+      <c r="L5" s="302"/>
+      <c r="M5" s="302"/>
+      <c r="N5" s="302"/>
+      <c r="O5" s="302"/>
+      <c r="P5" s="302"/>
+      <c r="Q5" s="302"/>
+      <c r="R5" s="302"/>
+      <c r="S5" s="303"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="277" t="s">
+      <c r="A6" s="295" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="278"/>
-      <c r="C6" s="278"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="279"/>
-      <c r="G6" s="286">
+      <c r="B6" s="296"/>
+      <c r="C6" s="296"/>
+      <c r="D6" s="296"/>
+      <c r="E6" s="296"/>
+      <c r="F6" s="297"/>
+      <c r="G6" s="304">
         <v>1</v>
       </c>
-      <c r="H6" s="284"/>
-      <c r="I6" s="284"/>
-      <c r="J6" s="284"/>
-      <c r="K6" s="284"/>
-      <c r="L6" s="284"/>
-      <c r="M6" s="284"/>
-      <c r="N6" s="284"/>
-      <c r="O6" s="284"/>
-      <c r="P6" s="284"/>
-      <c r="Q6" s="284"/>
-      <c r="R6" s="284"/>
-      <c r="S6" s="285"/>
+      <c r="H6" s="302"/>
+      <c r="I6" s="302"/>
+      <c r="J6" s="302"/>
+      <c r="K6" s="302"/>
+      <c r="L6" s="302"/>
+      <c r="M6" s="302"/>
+      <c r="N6" s="302"/>
+      <c r="O6" s="302"/>
+      <c r="P6" s="302"/>
+      <c r="Q6" s="302"/>
+      <c r="R6" s="302"/>
+      <c r="S6" s="303"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -15440,61 +16754,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="277" t="s">
+      <c r="A9" s="295" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="278"/>
-      <c r="C9" s="278"/>
-      <c r="D9" s="278"/>
-      <c r="E9" s="278"/>
-      <c r="F9" s="278"/>
-      <c r="G9" s="278"/>
-      <c r="H9" s="278"/>
-      <c r="I9" s="278"/>
-      <c r="J9" s="278"/>
-      <c r="K9" s="278"/>
-      <c r="L9" s="278"/>
-      <c r="M9" s="278"/>
-      <c r="N9" s="278"/>
-      <c r="O9" s="278"/>
-      <c r="P9" s="278"/>
-      <c r="Q9" s="278"/>
-      <c r="R9" s="278"/>
-      <c r="S9" s="278"/>
-      <c r="T9" s="278"/>
-      <c r="U9" s="278"/>
-      <c r="V9" s="278"/>
-      <c r="W9" s="278"/>
-      <c r="X9" s="278"/>
-      <c r="Y9" s="278"/>
-      <c r="Z9" s="278"/>
-      <c r="AA9" s="278"/>
-      <c r="AB9" s="278"/>
-      <c r="AC9" s="278"/>
-      <c r="AD9" s="278"/>
-      <c r="AE9" s="278"/>
-      <c r="AF9" s="278"/>
-      <c r="AG9" s="278"/>
-      <c r="AH9" s="278"/>
-      <c r="AI9" s="278"/>
-      <c r="AJ9" s="278"/>
-      <c r="AK9" s="278"/>
-      <c r="AL9" s="278"/>
-      <c r="AM9" s="278"/>
-      <c r="AN9" s="278"/>
-      <c r="AO9" s="278"/>
-      <c r="AP9" s="278"/>
-      <c r="AQ9" s="278"/>
-      <c r="AR9" s="278"/>
-      <c r="AS9" s="278"/>
-      <c r="AT9" s="278"/>
-      <c r="AU9" s="278"/>
-      <c r="AV9" s="278"/>
-      <c r="AW9" s="278"/>
-      <c r="AX9" s="278"/>
-      <c r="AY9" s="278"/>
-      <c r="AZ9" s="278"/>
-      <c r="BA9" s="279"/>
+      <c r="B9" s="296"/>
+      <c r="C9" s="296"/>
+      <c r="D9" s="296"/>
+      <c r="E9" s="296"/>
+      <c r="F9" s="296"/>
+      <c r="G9" s="296"/>
+      <c r="H9" s="296"/>
+      <c r="I9" s="296"/>
+      <c r="J9" s="296"/>
+      <c r="K9" s="296"/>
+      <c r="L9" s="296"/>
+      <c r="M9" s="296"/>
+      <c r="N9" s="296"/>
+      <c r="O9" s="296"/>
+      <c r="P9" s="296"/>
+      <c r="Q9" s="296"/>
+      <c r="R9" s="296"/>
+      <c r="S9" s="296"/>
+      <c r="T9" s="296"/>
+      <c r="U9" s="296"/>
+      <c r="V9" s="296"/>
+      <c r="W9" s="296"/>
+      <c r="X9" s="296"/>
+      <c r="Y9" s="296"/>
+      <c r="Z9" s="296"/>
+      <c r="AA9" s="296"/>
+      <c r="AB9" s="296"/>
+      <c r="AC9" s="296"/>
+      <c r="AD9" s="296"/>
+      <c r="AE9" s="296"/>
+      <c r="AF9" s="296"/>
+      <c r="AG9" s="296"/>
+      <c r="AH9" s="296"/>
+      <c r="AI9" s="296"/>
+      <c r="AJ9" s="296"/>
+      <c r="AK9" s="296"/>
+      <c r="AL9" s="296"/>
+      <c r="AM9" s="296"/>
+      <c r="AN9" s="296"/>
+      <c r="AO9" s="296"/>
+      <c r="AP9" s="296"/>
+      <c r="AQ9" s="296"/>
+      <c r="AR9" s="296"/>
+      <c r="AS9" s="296"/>
+      <c r="AT9" s="296"/>
+      <c r="AU9" s="296"/>
+      <c r="AV9" s="296"/>
+      <c r="AW9" s="296"/>
+      <c r="AX9" s="296"/>
+      <c r="AY9" s="296"/>
+      <c r="AZ9" s="296"/>
+      <c r="BA9" s="297"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="80"/>
@@ -19217,61 +20531,61 @@
       <c r="BA102" s="82"/>
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
-      <c r="A103" s="277" t="s">
+      <c r="A103" s="295" t="s">
         <v>76</v>
       </c>
-      <c r="B103" s="278"/>
-      <c r="C103" s="278"/>
-      <c r="D103" s="278"/>
-      <c r="E103" s="278"/>
-      <c r="F103" s="278"/>
-      <c r="G103" s="278"/>
-      <c r="H103" s="278"/>
-      <c r="I103" s="278"/>
-      <c r="J103" s="278"/>
-      <c r="K103" s="278"/>
-      <c r="L103" s="278"/>
-      <c r="M103" s="278"/>
-      <c r="N103" s="278"/>
-      <c r="O103" s="278"/>
-      <c r="P103" s="278"/>
-      <c r="Q103" s="278"/>
-      <c r="R103" s="278"/>
-      <c r="S103" s="278"/>
-      <c r="T103" s="278"/>
-      <c r="U103" s="278"/>
-      <c r="V103" s="278"/>
-      <c r="W103" s="278"/>
-      <c r="X103" s="278"/>
-      <c r="Y103" s="278"/>
-      <c r="Z103" s="278"/>
-      <c r="AA103" s="278"/>
-      <c r="AB103" s="278"/>
-      <c r="AC103" s="278"/>
-      <c r="AD103" s="278"/>
-      <c r="AE103" s="278"/>
-      <c r="AF103" s="278"/>
-      <c r="AG103" s="278"/>
-      <c r="AH103" s="278"/>
-      <c r="AI103" s="278"/>
-      <c r="AJ103" s="278"/>
-      <c r="AK103" s="278"/>
-      <c r="AL103" s="278"/>
-      <c r="AM103" s="278"/>
-      <c r="AN103" s="278"/>
-      <c r="AO103" s="278"/>
-      <c r="AP103" s="278"/>
-      <c r="AQ103" s="278"/>
-      <c r="AR103" s="278"/>
-      <c r="AS103" s="278"/>
-      <c r="AT103" s="278"/>
-      <c r="AU103" s="278"/>
-      <c r="AV103" s="278"/>
-      <c r="AW103" s="278"/>
-      <c r="AX103" s="278"/>
-      <c r="AY103" s="278"/>
-      <c r="AZ103" s="278"/>
-      <c r="BA103" s="279"/>
+      <c r="B103" s="296"/>
+      <c r="C103" s="296"/>
+      <c r="D103" s="296"/>
+      <c r="E103" s="296"/>
+      <c r="F103" s="296"/>
+      <c r="G103" s="296"/>
+      <c r="H103" s="296"/>
+      <c r="I103" s="296"/>
+      <c r="J103" s="296"/>
+      <c r="K103" s="296"/>
+      <c r="L103" s="296"/>
+      <c r="M103" s="296"/>
+      <c r="N103" s="296"/>
+      <c r="O103" s="296"/>
+      <c r="P103" s="296"/>
+      <c r="Q103" s="296"/>
+      <c r="R103" s="296"/>
+      <c r="S103" s="296"/>
+      <c r="T103" s="296"/>
+      <c r="U103" s="296"/>
+      <c r="V103" s="296"/>
+      <c r="W103" s="296"/>
+      <c r="X103" s="296"/>
+      <c r="Y103" s="296"/>
+      <c r="Z103" s="296"/>
+      <c r="AA103" s="296"/>
+      <c r="AB103" s="296"/>
+      <c r="AC103" s="296"/>
+      <c r="AD103" s="296"/>
+      <c r="AE103" s="296"/>
+      <c r="AF103" s="296"/>
+      <c r="AG103" s="296"/>
+      <c r="AH103" s="296"/>
+      <c r="AI103" s="296"/>
+      <c r="AJ103" s="296"/>
+      <c r="AK103" s="296"/>
+      <c r="AL103" s="296"/>
+      <c r="AM103" s="296"/>
+      <c r="AN103" s="296"/>
+      <c r="AO103" s="296"/>
+      <c r="AP103" s="296"/>
+      <c r="AQ103" s="296"/>
+      <c r="AR103" s="296"/>
+      <c r="AS103" s="296"/>
+      <c r="AT103" s="296"/>
+      <c r="AU103" s="296"/>
+      <c r="AV103" s="296"/>
+      <c r="AW103" s="296"/>
+      <c r="AX103" s="296"/>
+      <c r="AY103" s="296"/>
+      <c r="AZ103" s="296"/>
+      <c r="BA103" s="297"/>
     </row>
     <row r="104" spans="1:53" ht="21.95" customHeight="1">
       <c r="A104" s="83"/>
@@ -19594,61 +20908,61 @@
       <c r="BA111" s="82"/>
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
-      <c r="A112" s="277" t="s">
+      <c r="A112" s="295" t="s">
         <v>77</v>
       </c>
-      <c r="B112" s="278"/>
-      <c r="C112" s="278"/>
-      <c r="D112" s="278"/>
-      <c r="E112" s="278"/>
-      <c r="F112" s="278"/>
-      <c r="G112" s="278"/>
-      <c r="H112" s="278"/>
-      <c r="I112" s="278"/>
-      <c r="J112" s="278"/>
-      <c r="K112" s="278"/>
-      <c r="L112" s="278"/>
-      <c r="M112" s="278"/>
-      <c r="N112" s="278"/>
-      <c r="O112" s="278"/>
-      <c r="P112" s="278"/>
-      <c r="Q112" s="278"/>
-      <c r="R112" s="278"/>
-      <c r="S112" s="278"/>
-      <c r="T112" s="278"/>
-      <c r="U112" s="278"/>
-      <c r="V112" s="278"/>
-      <c r="W112" s="278"/>
-      <c r="X112" s="278"/>
-      <c r="Y112" s="278"/>
-      <c r="Z112" s="278"/>
-      <c r="AA112" s="278"/>
-      <c r="AB112" s="278"/>
-      <c r="AC112" s="278"/>
-      <c r="AD112" s="278"/>
-      <c r="AE112" s="278"/>
-      <c r="AF112" s="278"/>
-      <c r="AG112" s="278"/>
-      <c r="AH112" s="278"/>
-      <c r="AI112" s="278"/>
-      <c r="AJ112" s="278"/>
-      <c r="AK112" s="278"/>
-      <c r="AL112" s="278"/>
-      <c r="AM112" s="278"/>
-      <c r="AN112" s="278"/>
-      <c r="AO112" s="278"/>
-      <c r="AP112" s="278"/>
-      <c r="AQ112" s="278"/>
-      <c r="AR112" s="278"/>
-      <c r="AS112" s="278"/>
-      <c r="AT112" s="278"/>
-      <c r="AU112" s="278"/>
-      <c r="AV112" s="278"/>
-      <c r="AW112" s="278"/>
-      <c r="AX112" s="278"/>
-      <c r="AY112" s="278"/>
-      <c r="AZ112" s="278"/>
-      <c r="BA112" s="278"/>
+      <c r="B112" s="296"/>
+      <c r="C112" s="296"/>
+      <c r="D112" s="296"/>
+      <c r="E112" s="296"/>
+      <c r="F112" s="296"/>
+      <c r="G112" s="296"/>
+      <c r="H112" s="296"/>
+      <c r="I112" s="296"/>
+      <c r="J112" s="296"/>
+      <c r="K112" s="296"/>
+      <c r="L112" s="296"/>
+      <c r="M112" s="296"/>
+      <c r="N112" s="296"/>
+      <c r="O112" s="296"/>
+      <c r="P112" s="296"/>
+      <c r="Q112" s="296"/>
+      <c r="R112" s="296"/>
+      <c r="S112" s="296"/>
+      <c r="T112" s="296"/>
+      <c r="U112" s="296"/>
+      <c r="V112" s="296"/>
+      <c r="W112" s="296"/>
+      <c r="X112" s="296"/>
+      <c r="Y112" s="296"/>
+      <c r="Z112" s="296"/>
+      <c r="AA112" s="296"/>
+      <c r="AB112" s="296"/>
+      <c r="AC112" s="296"/>
+      <c r="AD112" s="296"/>
+      <c r="AE112" s="296"/>
+      <c r="AF112" s="296"/>
+      <c r="AG112" s="296"/>
+      <c r="AH112" s="296"/>
+      <c r="AI112" s="296"/>
+      <c r="AJ112" s="296"/>
+      <c r="AK112" s="296"/>
+      <c r="AL112" s="296"/>
+      <c r="AM112" s="296"/>
+      <c r="AN112" s="296"/>
+      <c r="AO112" s="296"/>
+      <c r="AP112" s="296"/>
+      <c r="AQ112" s="296"/>
+      <c r="AR112" s="296"/>
+      <c r="AS112" s="296"/>
+      <c r="AT112" s="296"/>
+      <c r="AU112" s="296"/>
+      <c r="AV112" s="296"/>
+      <c r="AW112" s="296"/>
+      <c r="AX112" s="296"/>
+      <c r="AY112" s="296"/>
+      <c r="AZ112" s="296"/>
+      <c r="BA112" s="296"/>
     </row>
     <row r="113" spans="1:53" ht="21.95" customHeight="1">
       <c r="A113" s="83"/>
